--- a/доки/lab_3/lab_3.xlsx
+++ b/доки/lab_3/lab_3.xlsx
@@ -4,7 +4,7 @@
   <workbookPr hidePivotFieldList="0"/>
   <workbookProtection lockStructure="0" lockWindows="0" workbookPassword="0000"/>
   <bookViews>
-    <workbookView xWindow="360" yWindow="15" windowWidth="20955" windowHeight="9720" activeTab="10"/>
+    <workbookView xWindow="360" yWindow="15" windowWidth="20955" windowHeight="9720" activeTab="6"/>
   </bookViews>
   <sheets>
     <sheet name="Паспорт проекта" sheetId="1" state="visible" r:id="rId2"/>
@@ -14,10 +14,11 @@
     <sheet name="Внедрение" sheetId="5" state="visible" r:id="rId6"/>
     <sheet name="Временные ограничения" sheetId="6" state="visible" r:id="rId7"/>
     <sheet name="Трудовые ограничения" sheetId="7" state="visible" r:id="rId8"/>
-    <sheet name="Технические ограничения" sheetId="8" state="visible" r:id="rId9"/>
-    <sheet name="Смета (финансовые ограничения)" sheetId="9" state="visible" r:id="rId10"/>
-    <sheet name="Реестр рисков" sheetId="10" state="visible" r:id="rId11"/>
-    <sheet name="RACI-матрица" sheetId="11" state="visible" r:id="rId12"/>
+    <sheet name="Лист1" sheetId="8" state="visible" r:id="rId9"/>
+    <sheet name="Технические ограничения" sheetId="9" state="visible" r:id="rId10"/>
+    <sheet name="Смета (финансовые ограничения)" sheetId="10" state="visible" r:id="rId11"/>
+    <sheet name="Реестр рисков" sheetId="11" state="visible" r:id="rId12"/>
+    <sheet name="RACI-матрица" sheetId="12" state="visible" r:id="rId13"/>
   </sheets>
   <calcPr/>
   <extLst>
@@ -83,32 +84,10 @@
 <file path=xl/comments2.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
-    <author>tc={00970021-002F-40A7-896F-008300EB00FE}</author>
     <author>tc={20CCCDD9-EC7C-F606-D4A3-A95821014B27}</author>
   </authors>
   <commentList>
-    <comment ref="A1" authorId="0" xr:uid="{00970021-002F-40A7-896F-008300EB00FE}">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <rFont val="Tahoma"/>
-          </rPr>
-          <t xml:space="preserve">Наталья Заборовская:</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <rFont val="Tahoma"/>
-          </rPr>
-          <t xml:space="preserve">
-Перечислить состав команды, з/п в месяц и продолжительность задействования в проекте по каждому сотруднику
-</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="A2" authorId="1" xr:uid="{20CCCDD9-EC7C-F606-D4A3-A95821014B27}">
+    <comment ref="A1" authorId="0" xr:uid="{20CCCDD9-EC7C-F606-D4A3-A95821014B27}">
       <text>
         <r>
           <rPr>
@@ -233,8 +212,6 @@
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
     <author>tc={8F1EE7AD-C0EB-361C-4E54-B55280C05304}</author>
-    <author>tc={ED43C0E1-48CA-A1F8-C1C2-108C10E8F6D5}</author>
-    <author>tc={0F5FC66B-F851-3881-4D6E-72A035FE278D}</author>
     <author>tc={CE67BEAA-F6E7-B978-580A-2B7893C61786}</author>
     <author>tc={F968B835-7612-6291-F8F8-FC6D823E7EF7}</author>
     <author>tc={417785EC-4884-ACCE-72AA-0B7219B998D7}</author>
@@ -242,7 +219,6 @@
     <author>tc={7A2408D7-D9B4-4ABD-3B83-06D41BA8E58A}</author>
     <author>tc={F1DED64E-D08E-B5AE-C6CD-A85C8671A463}</author>
     <author>tc={7CB5543B-36F0-4F6C-C70C-074B6F2AA6B2}</author>
-    <author>tc={83B2669F-6FAD-1EEF-D66E-0F968B3E4855}</author>
   </authors>
   <commentList>
     <comment ref="B5" authorId="0" xr:uid="{8F1EE7AD-C0EB-361C-4E54-B55280C05304}">
@@ -266,49 +242,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="K5" authorId="1" xr:uid="{ED43C0E1-48CA-A1F8-C1C2-108C10E8F6D5}">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <rFont val="Tahoma"/>
-          </rPr>
-          <t xml:space="preserve">Наталья Заборовская:</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <rFont val="Tahoma"/>
-          </rPr>
-          <t xml:space="preserve">
-Разъясняет бизнес-цели и приоритеты, утверждает ключевые границы продукта
-</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="L5" authorId="2" xr:uid="{0F5FC66B-F851-3881-4D6E-72A035FE278D}">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <rFont val="Tahoma"/>
-          </rPr>
-          <t xml:space="preserve">Наталья Заборовская:</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <rFont val="Tahoma"/>
-          </rPr>
-          <t xml:space="preserve">
-Предоставляет информацию о текущих бизнес-процессах, данных и технических ограничениях со стороны заказчика
-</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="C5" authorId="3" xr:uid="{CE67BEAA-F6E7-B978-580A-2B7893C61786}">
+    <comment ref="C5" authorId="1" xr:uid="{CE67BEAA-F6E7-B978-580A-2B7893C61786}">
       <text>
         <r>
           <rPr>
@@ -329,7 +263,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="D5" authorId="4" xr:uid="{F968B835-7612-6291-F8F8-FC6D823E7EF7}">
+    <comment ref="D5" authorId="2" xr:uid="{F968B835-7612-6291-F8F8-FC6D823E7EF7}">
       <text>
         <r>
           <rPr>
@@ -350,7 +284,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E5" authorId="5" xr:uid="{417785EC-4884-ACCE-72AA-0B7219B998D7}">
+    <comment ref="E5" authorId="3" xr:uid="{417785EC-4884-ACCE-72AA-0B7219B998D7}">
       <text>
         <r>
           <rPr>
@@ -371,7 +305,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F5" authorId="6" xr:uid="{6C417BF5-DE07-0698-AAF2-F8C13C1BFC5C}">
+    <comment ref="F5" authorId="4" xr:uid="{6C417BF5-DE07-0698-AAF2-F8C13C1BFC5C}">
       <text>
         <r>
           <rPr>
@@ -392,7 +326,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G5" authorId="7" xr:uid="{7A2408D7-D9B4-4ABD-3B83-06D41BA8E58A}">
+    <comment ref="G5" authorId="5" xr:uid="{7A2408D7-D9B4-4ABD-3B83-06D41BA8E58A}">
       <text>
         <r>
           <rPr>
@@ -413,7 +347,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H5" authorId="8" xr:uid="{F1DED64E-D08E-B5AE-C6CD-A85C8671A463}">
+    <comment ref="H5" authorId="6" xr:uid="{F1DED64E-D08E-B5AE-C6CD-A85C8671A463}">
       <text>
         <r>
           <rPr>
@@ -434,7 +368,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I5" authorId="9" xr:uid="{7CB5543B-36F0-4F6C-C70C-074B6F2AA6B2}">
+    <comment ref="I5" authorId="7" xr:uid="{7CB5543B-36F0-4F6C-C70C-074B6F2AA6B2}">
       <text>
         <r>
           <rPr>
@@ -455,33 +389,12 @@
         </r>
       </text>
     </comment>
-    <comment ref="J5" authorId="10" xr:uid="{83B2669F-6FAD-1EEF-D66E-0F968B3E4855}">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <rFont val="Tahoma"/>
-          </rPr>
-          <t xml:space="preserve">Наталья Заборовская:</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <rFont val="Tahoma"/>
-          </rPr>
-          <t xml:space="preserve">
-Информируется о завершении этапа сбора требований
-</t>
-        </r>
-      </text>
-    </comment>
   </commentList>
 </comments>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="357" uniqueCount="357">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="389" uniqueCount="389">
   <si>
     <t xml:space="preserve">Рабочее название проекта</t>
   </si>
@@ -893,25 +806,97 @@
     <t xml:space="preserve">Время работы в проекте, мес</t>
   </si>
   <si>
+    <t xml:space="preserve">Роль в проекте</t>
+  </si>
+  <si>
+    <t>Обязанности</t>
+  </si>
+  <si>
+    <t>ФИО</t>
+  </si>
+  <si>
     <t xml:space="preserve">Руководитель проекта</t>
   </si>
   <si>
+    <t xml:space="preserve">Спонсор проекта</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Принимает решение о запуске и поддержке проекта. 2. Определяет приоритетность проекта и подтверждает необходимость его реализации. 3. Утверждает ключевые изменения по срокам, бюджету и составу работ. 4. Обеспечивает ресурсную и организационную поддержку проекта.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Иванов Иван Иванович</t>
+  </si>
+  <si>
     <t xml:space="preserve">Бизнес-аналитик / системный аналитик</t>
   </si>
   <si>
+    <t xml:space="preserve">1. Обеспечивает общее руководство проектом и контроль его выполнения. 2. Разрабатывает план проекта и контролирует соблюдение сроков. 3. Организует взаимодействие между участниками команды. 4. Управляет рисками, изменениями и коммуникациями проекта. 5. Контролирует выполнение задач и качество промежуточных результатов. 6. Подготавливает отчетность по проекту.</t>
+  </si>
+  <si>
     <t>Backend-разработчик</t>
   </si>
   <si>
+    <t xml:space="preserve">1. Собирает и формализует требования к системе. 2. Уточняет ожидания пользователей и заказчика. 3. Описывает функциональные и нефункциональные требования. 4. Участвует в постановке задач на разработку. 5. Консультирует команду по вопросам бизнес-логики и сценариев использования сервиса.</t>
+  </si>
+  <si>
     <t>Frontend-разработчик</t>
   </si>
   <si>
+    <t xml:space="preserve">1. Реализует серверную логику приложения. 2. Разрабатывает API для работы frontend и ML-модуля. 3. Реализует обработку загрузки изображений и референсов. 4. Настраивает хранение данных и историю обработок. 5. Обеспечивает корректную интеграцию серверной части с другими компонентами системы.</t>
+  </si>
+  <si>
     <t>ML-инженер</t>
   </si>
   <si>
+    <t xml:space="preserve">1. Разрабатывает пользовательский интерфейс сервиса. 2. Реализует формы регистрации и авторизации. 3. Обеспечивает интерфейс загрузки изображений и референсов. 4. Реализует предпросмотр результатов обработки и скачивание файлов. 5. Обеспечивает удобство и корректность взаимодействия пользователя с системой.</t>
+  </si>
+  <si>
     <t>UX/UI-дизайнер</t>
   </si>
   <si>
+    <t xml:space="preserve">1. Настраивает и интегрирует модуль ИИ-обработки изображений. 2. Отвечает за перенос пользовательского стиля и базовые AI-функции. 3. Оптимизирует качество и производительность обработки изображений. 4. Участвует в тестировании качества результатов модели. 5. Консультирует команду по ограничениям и возможностям ML-компонента.</t>
+  </si>
+  <si>
     <t>Тестировщик</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Проектирует пользовательские сценарии и интерфейсы системы. 2. Разрабатывает макеты экранов и визуальную структуру интерфейса. 3. Участвует в проектировании удобного пользовательского пути. 4. Консультирует команду по вопросам визуального представления и удобства использования.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Проводит тестирование пользовательских сценариев. 2. Проверяет корректность работы интерфейса, backend-логики и ML-модуля. 3. Фиксирует ошибки и замечания. 4. Контролирует устранение выявленных дефектов. 5. Подготавливает результаты тестирования и участвует в приемке решения.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Принимает решение о запуске и поддержке проекта</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2. Определяет приоритетность проекта и подтверждает необходимость его реализации. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">3. Утверждает ключевые изменения по срокам, бюджету и составу работ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4. Обеспечивает ресурсную и организационную поддержку проекта.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Обеспечивает общее руководство проектом и контроль его выполнения</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2. Разрабатывает план проекта и контролирует соблюдение сроков</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3. Организует взаимодействие между участниками команды</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4. Управляет рисками, изменениями и коммуникациями проекта</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5. Контролирует выполнение задач и качество промежуточных результатов</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6. Подготавливает отчетность по проекту</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Собирает и формализует требования к системе</t>
   </si>
   <si>
     <t xml:space="preserve">Компьютеры, оборудование, средства связи и прочее. 
@@ -1546,13 +1531,7 @@
     <t xml:space="preserve">Очень высокое</t>
   </si>
   <si>
-    <t>Риск</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Заказчик / представитель пользователя</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Спонсор проекта</t>
+    <t>Задача</t>
   </si>
   <si>
     <r>
@@ -1562,7 +1541,6 @@
       <rPr>
         <b/>
         <sz val="12"/>
-        <color indexed="64"/>
         <rFont val="Times New Roman"/>
       </rPr>
       <t xml:space="preserve">Функции RACI-матрицы:</t>
@@ -1570,7 +1548,6 @@
     <r>
       <rPr>
         <sz val="12"/>
-        <color indexed="64"/>
         <rFont val="Times New Roman"/>
       </rPr>
       <t xml:space="preserve">
@@ -1581,19 +1558,49 @@
     </r>
   </si>
   <si>
+    <t xml:space="preserve">Спроектировать экран регистрации</t>
+  </si>
+  <si>
+    <t>I</t>
+  </si>
+  <si>
     <t>A</t>
   </si>
   <si>
+    <t>C</t>
+  </si>
+  <si>
     <t>R</t>
   </si>
   <si>
-    <t>I</t>
-  </si>
-  <si>
-    <t>C</t>
-  </si>
-  <si>
-    <t>A/R</t>
+    <t xml:space="preserve">Реализовать форму авторизации</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Реализовать загрузку исходного изображения</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Реализовать валидацию форматов изображений</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Реализовать загрузку референсов</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Настроить модуль стилизации</t>
+  </si>
+  <si>
+    <t>R/A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Реализовать предпросмотр результата</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Реализовать скачивание итогового файла</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Реализовать хранение истории обработок</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Провести тестирование пользовательских сценариев</t>
   </si>
 </sst>
 </file>
@@ -1779,12 +1786,17 @@
       <name val="Times New Roman"/>
     </font>
     <font>
-      <b/>
       <sz val="12.000000"/>
       <color theme="1" tint="0"/>
       <name val="Times New Roman"/>
     </font>
     <font>
+      <sz val="12.000000"/>
+      <color indexed="64"/>
+      <name val="Times New Roman"/>
+    </font>
+    <font>
+      <b/>
       <sz val="12.000000"/>
       <color theme="1" tint="0"/>
       <name val="Times New Roman"/>
@@ -1808,11 +1820,6 @@
     </font>
     <font>
       <sz val="11.000000"/>
-      <name val="Times New Roman"/>
-    </font>
-    <font>
-      <sz val="12.000000"/>
-      <color indexed="64"/>
       <name val="Times New Roman"/>
     </font>
     <font>
@@ -2037,7 +2044,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="60">
+  <borders count="61">
     <border>
       <left style="none"/>
       <right style="none"/>
@@ -2326,6 +2333,13 @@
       <diagonal style="none"/>
     </border>
     <border>
+      <left/>
+      <right/>
+      <top style="none"/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
       <left style="thin">
         <color theme="1"/>
       </left>
@@ -2824,7 +2838,7 @@
     <xf fontId="7" fillId="0" borderId="0" numFmtId="167" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf fontId="20" fillId="31" borderId="0" numFmtId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellStyleXfs>
-  <cellXfs count="151">
+  <cellXfs count="169">
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0"/>
     <xf fontId="21" fillId="0" borderId="10" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2924,35 +2938,88 @@
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf fontId="28" fillId="0" borderId="13" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
     <xf fontId="27" fillId="0" borderId="10" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf fontId="28" fillId="0" borderId="10" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf fontId="29" fillId="0" borderId="10" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf fontId="25" fillId="0" borderId="12" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf fontId="28" fillId="0" borderId="10" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf fontId="29" fillId="0" borderId="10" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf fontId="25" fillId="0" borderId="23" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf fontId="25" fillId="0" borderId="24" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf fontId="25" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf fontId="28" fillId="0" borderId="25" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf fontId="28" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf fontId="28" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf fontId="29" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
     <xf fontId="29" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf fontId="29" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0"/>
+    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0"/>
+    <xf fontId="0" fillId="0" borderId="15" numFmtId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf fontId="29" fillId="0" borderId="15" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf fontId="29" fillId="0" borderId="15" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf fontId="0" fillId="0" borderId="15" numFmtId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf fontId="29" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf fontId="25" fillId="0" borderId="21" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf fontId="27" fillId="0" borderId="25" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf fontId="27" fillId="0" borderId="26" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf fontId="25" fillId="0" borderId="26" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf fontId="25" fillId="0" borderId="27" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf fontId="27" fillId="0" borderId="27" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
     </xf>
     <xf fontId="27" fillId="0" borderId="28" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -2960,19 +3027,22 @@
     <xf fontId="27" fillId="0" borderId="29" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf fontId="28" fillId="0" borderId="30" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf fontId="27" fillId="0" borderId="30" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf fontId="30" fillId="0" borderId="31" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf fontId="30" fillId="0" borderId="32" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf fontId="31" fillId="0" borderId="32" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf fontId="29" fillId="0" borderId="12" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf fontId="31" fillId="0" borderId="33" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf fontId="29" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1"/>
+    <xf fontId="28" fillId="0" borderId="12" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf fontId="28" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1"/>
     <xf fontId="25" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1"/>
     <xf fontId="25" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
@@ -2984,15 +3054,12 @@
     <xf fontId="27" fillId="0" borderId="21" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf fontId="31" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf fontId="32" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf fontId="25" fillId="0" borderId="33" numFmtId="0" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf fontId="29" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf fontId="25" fillId="0" borderId="34" numFmtId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf fontId="28" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf fontId="27" fillId="0" borderId="34" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf fontId="27" fillId="0" borderId="35" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -3000,14 +3067,14 @@
     <xf fontId="27" fillId="0" borderId="36" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf fontId="32" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf fontId="27" fillId="0" borderId="37" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf fontId="33" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf fontId="27" fillId="0" borderId="38" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf fontId="27" fillId="0" borderId="39" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
@@ -3015,11 +3082,14 @@
     <xf fontId="27" fillId="0" borderId="40" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf fontId="32" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1"/>
+    <xf fontId="27" fillId="0" borderId="41" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf fontId="33" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1"/>
     <xf fontId="25" fillId="0" borderId="10" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf fontId="25" fillId="0" borderId="41" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf fontId="25" fillId="0" borderId="42" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf fontId="25" fillId="0" borderId="10" numFmtId="171" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -3034,78 +3104,75 @@
     <xf fontId="25" fillId="0" borderId="10" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf fontId="32" fillId="0" borderId="0" numFmtId="3" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf fontId="33" fillId="0" borderId="0" numFmtId="3" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf fontId="25" fillId="0" borderId="10" numFmtId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf fontId="25" fillId="0" borderId="42" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf fontId="25" fillId="0" borderId="43" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf fontId="25" fillId="0" borderId="0" numFmtId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf fontId="25" fillId="0" borderId="43" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
     <xf fontId="25" fillId="0" borderId="44" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf fontId="25" fillId="0" borderId="41" numFmtId="171" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf fontId="25" fillId="0" borderId="45" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf fontId="25" fillId="0" borderId="42" numFmtId="171" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf fontId="33" fillId="34" borderId="10" numFmtId="171" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf fontId="34" fillId="34" borderId="10" numFmtId="171" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf fontId="25" fillId="0" borderId="10" numFmtId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf fontId="25" fillId="0" borderId="45" numFmtId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf fontId="25" fillId="0" borderId="46" numFmtId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf fontId="25" fillId="0" borderId="46" numFmtId="171" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf fontId="25" fillId="0" borderId="47" numFmtId="171" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf fontId="25" fillId="0" borderId="39" numFmtId="171" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf fontId="25" fillId="0" borderId="40" numFmtId="171" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf fontId="25" fillId="0" borderId="47" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="top" wrapText="1"/>
     </xf>
     <xf fontId="25" fillId="0" borderId="48" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="justify" vertical="top" wrapText="1"/>
     </xf>
-    <xf fontId="25" fillId="0" borderId="48" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf fontId="25" fillId="0" borderId="49" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="top" wrapText="1"/>
+    </xf>
+    <xf fontId="25" fillId="0" borderId="49" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf fontId="25" fillId="0" borderId="48" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf fontId="25" fillId="0" borderId="49" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf fontId="25" fillId="0" borderId="48" numFmtId="171" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf fontId="25" fillId="0" borderId="49" numFmtId="171" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf fontId="33" fillId="34" borderId="48" numFmtId="171" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf fontId="34" fillId="34" borderId="49" numFmtId="171" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf fontId="25" fillId="0" borderId="48" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf fontId="25" fillId="0" borderId="49" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf fontId="25" fillId="0" borderId="49" numFmtId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf fontId="25" fillId="0" borderId="50" numFmtId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf fontId="27" fillId="0" borderId="35" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top" wrapText="1"/>
-    </xf>
-    <xf fontId="27" fillId="0" borderId="50" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top" wrapText="1"/>
     </xf>
     <xf fontId="27" fillId="0" borderId="36" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top" wrapText="1"/>
     </xf>
-    <xf fontId="27" fillId="0" borderId="37" numFmtId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf fontId="27" fillId="0" borderId="51" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top" wrapText="1"/>
     </xf>
-    <xf fontId="25" fillId="34" borderId="51" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
+    <xf fontId="27" fillId="0" borderId="37" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
+    </xf>
+    <xf fontId="27" fillId="0" borderId="38" numFmtId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
     </xf>
     <xf fontId="25" fillId="34" borderId="52" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -3113,129 +3180,123 @@
     <xf fontId="25" fillId="34" borderId="53" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf fontId="25" fillId="34" borderId="40" numFmtId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf fontId="25" fillId="34" borderId="54" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf fontId="25" fillId="34" borderId="43" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf fontId="25" fillId="34" borderId="41" numFmtId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
+    </xf>
+    <xf fontId="25" fillId="34" borderId="44" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf fontId="25" fillId="34" borderId="29" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf fontId="25" fillId="34" borderId="30" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf fontId="27" fillId="34" borderId="46" numFmtId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf fontId="27" fillId="34" borderId="0" numFmtId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf fontId="25" fillId="34" borderId="46" numFmtId="172" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf fontId="33" fillId="0" borderId="0" numFmtId="4" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf fontId="25" fillId="34" borderId="0" numFmtId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf fontId="25" fillId="34" borderId="44" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf fontId="25" fillId="34" borderId="29" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf fontId="25" fillId="34" borderId="30" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf fontId="25" fillId="34" borderId="46" numFmtId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf fontId="27" fillId="34" borderId="44" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf fontId="27" fillId="34" borderId="29" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf fontId="27" fillId="34" borderId="30" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf fontId="27" fillId="34" borderId="44" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf fontId="27" fillId="34" borderId="29" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf fontId="27" fillId="34" borderId="30" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf fontId="28" fillId="0" borderId="0" numFmtId="4" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf fontId="27" fillId="34" borderId="55" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf fontId="27" fillId="34" borderId="15" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf fontId="27" fillId="34" borderId="17" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf fontId="27" fillId="34" borderId="56" numFmtId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf fontId="25" fillId="34" borderId="28" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf fontId="25" fillId="34" borderId="29" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf fontId="27" fillId="34" borderId="45" numFmtId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf fontId="27" fillId="34" borderId="0" numFmtId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf fontId="25" fillId="34" borderId="45" numFmtId="172" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf fontId="32" fillId="0" borderId="0" numFmtId="4" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf fontId="25" fillId="34" borderId="0" numFmtId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf fontId="25" fillId="34" borderId="43" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf fontId="25" fillId="34" borderId="28" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf fontId="25" fillId="34" borderId="29" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf fontId="25" fillId="34" borderId="45" numFmtId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf fontId="27" fillId="34" borderId="43" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf fontId="27" fillId="34" borderId="28" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf fontId="27" fillId="34" borderId="29" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf fontId="27" fillId="34" borderId="43" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf fontId="27" fillId="34" borderId="28" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf fontId="27" fillId="34" borderId="29" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf fontId="29" fillId="0" borderId="0" numFmtId="4" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf fontId="27" fillId="34" borderId="54" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf fontId="27" fillId="34" borderId="15" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf fontId="27" fillId="34" borderId="17" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf fontId="27" fillId="34" borderId="55" numFmtId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf fontId="25" fillId="34" borderId="27" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf fontId="27" fillId="34" borderId="47" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
     <xf fontId="27" fillId="34" borderId="48" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf fontId="27" fillId="34" borderId="56" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf fontId="27" fillId="34" borderId="49" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf fontId="27" fillId="0" borderId="57" numFmtId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf fontId="27" fillId="34" borderId="57" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf fontId="27" fillId="0" borderId="58" numFmtId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf fontId="29" fillId="0" borderId="23" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf fontId="28" fillId="0" borderId="23" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf fontId="34" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf fontId="34" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf fontId="25" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
       <protection hidden="0" locked="1"/>
     </xf>
     <xf fontId="0" fillId="35" borderId="0" numFmtId="0" xfId="0" applyFill="1"/>
     <xf fontId="0" fillId="0" borderId="10" numFmtId="0" xfId="0" applyBorder="1"/>
-    <xf fontId="34" fillId="0" borderId="10" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf fontId="25" fillId="0" borderId="10" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf fontId="34" fillId="0" borderId="10" numFmtId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf fontId="25" fillId="0" borderId="10" numFmtId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf fontId="35" fillId="0" borderId="58" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf fontId="35" fillId="0" borderId="59" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf fontId="36" fillId="0" borderId="58" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf fontId="36" fillId="0" borderId="59" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="justify" vertical="center"/>
     </xf>
-    <xf fontId="0" fillId="0" borderId="59" numFmtId="0" xfId="0" applyBorder="1">
+    <xf fontId="0" fillId="0" borderId="60" numFmtId="0" xfId="0" applyBorder="1">
       <protection hidden="0" locked="1"/>
     </xf>
-    <xf fontId="34" fillId="0" borderId="10" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf fontId="25" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf fontId="29" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf fontId="29" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf fontId="28" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf fontId="34" fillId="0" borderId="10" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf fontId="29" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf fontId="28" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
     <xf fontId="36" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -3244,11 +3305,15 @@
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf fontId="34" fillId="0" borderId="10" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf fontId="29" fillId="0" borderId="10" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
       <protection hidden="0" locked="1"/>
     </xf>
-    <xf fontId="34" fillId="0" borderId="10" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf fontId="29" fillId="0" borderId="10" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="0" locked="1"/>
+    </xf>
+    <xf fontId="25" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection hidden="0" locked="1"/>
     </xf>
@@ -3355,8 +3420,8 @@
 
 <file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
 <personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <person displayName="Unknown Author" id="{6B34384E-47AA-1713-4363-85C49D5AA4DE}"/>
-  <person displayName="Наталья Заборовская" id="{55C010E3-CD73-0CAD-46BE-B156B742904C}"/>
+  <person displayName="Unknown Author" id="{5E1DE1F7-AD23-04D3-64A6-620D7E714F40}"/>
+  <person displayName="Наталья Заборовская" id="{6F937CC8-61BE-D0EE-F4A9-6B5B9699B9D3}"/>
 </personList>
 </file>
 
@@ -3865,12 +3930,12 @@
 
 <file path=xl/threadedComments/threadedComment1.xml><?xml version="1.0" encoding="utf-8"?>
 <ThreadedComments xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <threadedComment ref="A21" personId="{6B34384E-47AA-1713-4363-85C49D5AA4DE}" id="{3AAECF60-C511-EB79-8549-2CEA0DEA6E71}" done="0">
+  <threadedComment ref="A21" personId="{5E1DE1F7-AD23-04D3-64A6-620D7E714F40}" id="{3AAECF60-C511-EB79-8549-2CEA0DEA6E71}" done="0">
     <text xml:space="preserve">Наталья Заборовская:
 пречислить верхнеуровневые риски - 3-5
 </text>
   </threadedComment>
-  <threadedComment ref="A6" personId="{55C010E3-CD73-0CAD-46BE-B156B742904C}" id="{008B0096-002F-4BB6-B692-00D2002F006B}" done="0">
+  <threadedComment ref="A6" personId="{6F937CC8-61BE-D0EE-F4A9-6B5B9699B9D3}" id="{008B0096-002F-4BB6-B692-00D2002F006B}" done="0">
     <text xml:space="preserve">Определяем достижение цели через количественные показатели - минимум 3
 </text>
   </threadedComment>
@@ -3879,11 +3944,7 @@
 
 <file path=xl/threadedComments/threadedComment2.xml><?xml version="1.0" encoding="utf-8"?>
 <ThreadedComments xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <threadedComment ref="A1" personId="{55C010E3-CD73-0CAD-46BE-B156B742904C}" id="{00970021-002F-40A7-896F-008300EB00FE}" done="0">
-    <text xml:space="preserve">Перечислить состав команды, з/п в месяц и продолжительность задействования в проекте по каждому сотруднику
-</text>
-  </threadedComment>
-  <threadedComment ref="A2" personId="{6B34384E-47AA-1713-4363-85C49D5AA4DE}" id="{20CCCDD9-EC7C-F606-D4A3-A95821014B27}" done="0">
+  <threadedComment ref="A1" personId="{5E1DE1F7-AD23-04D3-64A6-620D7E714F40}" id="{20CCCDD9-EC7C-F606-D4A3-A95821014B27}" done="0">
     <text xml:space="preserve">Наталья Заборовская:
 Перечислить состав команды, з/п в месяц и продолжительность задействования в проекте по каждому сотруднику
 </text>
@@ -3893,7 +3954,7 @@
 
 <file path=xl/threadedComments/threadedComment3.xml><?xml version="1.0" encoding="utf-8"?>
 <ThreadedComments xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <threadedComment ref="E3" personId="{6B34384E-47AA-1713-4363-85C49D5AA4DE}" id="{59873D8E-AC83-C4A9-EE0E-167176948FCD}" done="0">
+  <threadedComment ref="E3" personId="{5E1DE1F7-AD23-04D3-64A6-620D7E714F40}" id="{59873D8E-AC83-C4A9-EE0E-167176948FCD}" done="0">
     <text xml:space="preserve">Наталья Заборовская:
 (Количество × Стоимость) × коэффициент удорожания
 </text>
@@ -3903,7 +3964,7 @@
 
 <file path=xl/threadedComments/threadedComment4.xml><?xml version="1.0" encoding="utf-8"?>
 <ThreadedComments xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <threadedComment ref="A27" personId="{6B34384E-47AA-1713-4363-85C49D5AA4DE}" id="{079DEF54-F22F-7756-67A8-D357A9051819}" done="0">
+  <threadedComment ref="A27" personId="{5E1DE1F7-AD23-04D3-64A6-620D7E714F40}" id="{079DEF54-F22F-7756-67A8-D357A9051819}" done="0">
     <text xml:space="preserve">Наталья Заборовская:
 Итоговая стоимость по техническим ограничениям
 </text>
@@ -3913,7 +3974,7 @@
 
 <file path=xl/threadedComments/threadedComment5.xml><?xml version="1.0" encoding="utf-8"?>
 <ThreadedComments xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <threadedComment ref="C1" personId="{55C010E3-CD73-0CAD-46BE-B156B742904C}" id="{9DBA13F6-54AE-24C8-3D54-9DE274BD5EC5}" done="0">
+  <threadedComment ref="C1" personId="{6F937CC8-61BE-D0EE-F4A9-6B5B9699B9D3}" id="{9DBA13F6-54AE-24C8-3D54-9DE274BD5EC5}" done="0">
     <text xml:space="preserve">почему это может произойти?
 </text>
   </threadedComment>
@@ -3922,48 +3983,36 @@
 
 <file path=xl/threadedComments/threadedComment6.xml><?xml version="1.0" encoding="utf-8"?>
 <ThreadedComments xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <threadedComment ref="B5" personId="{55C010E3-CD73-0CAD-46BE-B156B742904C}" id="{8F1EE7AD-C0EB-361C-4E54-B55280C05304}" done="0">
+  <threadedComment ref="B5" personId="{6F937CC8-61BE-D0EE-F4A9-6B5B9699B9D3}" id="{8F1EE7AD-C0EB-361C-4E54-B55280C05304}" done="0">
     <text xml:space="preserve">Получает регулярные обновления о статусе уточнения требований для корректировки планов
 </text>
   </threadedComment>
-  <threadedComment ref="K5" personId="{55C010E3-CD73-0CAD-46BE-B156B742904C}" id="{ED43C0E1-48CA-A1F8-C1C2-108C10E8F6D5}" done="0">
-    <text xml:space="preserve">Разъясняет бизнес-цели и приоритеты, утверждает ключевые границы продукта
-</text>
-  </threadedComment>
-  <threadedComment ref="L5" personId="{55C010E3-CD73-0CAD-46BE-B156B742904C}" id="{0F5FC66B-F851-3881-4D6E-72A035FE278D}" done="0">
-    <text xml:space="preserve">Предоставляет информацию о текущих бизнес-процессах, данных и технических ограничениях со стороны заказчика
-</text>
-  </threadedComment>
-  <threadedComment ref="C5" personId="{55C010E3-CD73-0CAD-46BE-B156B742904C}" id="{CE67BEAA-F6E7-B978-580A-2B7893C61786}" done="0">
+  <threadedComment ref="C5" personId="{6F937CC8-61BE-D0EE-F4A9-6B5B9699B9D3}" id="{CE67BEAA-F6E7-B978-580A-2B7893C61786}" done="0">
     <text xml:space="preserve">Консультирует о реализуемости интерфейсных решений, предлагает прототипы для уточнения
 </text>
   </threadedComment>
-  <threadedComment ref="D5" personId="{55C010E3-CD73-0CAD-46BE-B156B742904C}" id="{F968B835-7612-6291-F8F8-FC6D823E7EF7}" done="0">
+  <threadedComment ref="D5" personId="{6F937CC8-61BE-D0EE-F4A9-6B5B9699B9D3}" id="{F968B835-7612-6291-F8F8-FC6D823E7EF7}" done="0">
     <text xml:space="preserve">Оценивает техническую реализуемость API и логики с точки зрения архитектуры
 </text>
   </threadedComment>
-  <threadedComment ref="E5" personId="{55C010E3-CD73-0CAD-46BE-B156B742904C}" id="{417785EC-4884-ACCE-72AA-0B7219B998D7}" done="0">
+  <threadedComment ref="E5" personId="{6F937CC8-61BE-D0EE-F4A9-6B5B9699B9D3}" id="{417785EC-4884-ACCE-72AA-0B7219B998D7}" done="0">
     <text xml:space="preserve">Отвечает за полноту, непротиворечивость и формализацию требований, финализирует спецификацию
 </text>
   </threadedComment>
-  <threadedComment ref="F5" personId="{55C010E3-CD73-0CAD-46BE-B156B742904C}" id="{6C417BF5-DE07-0698-AAF2-F8C13C1BFC5C}" done="0">
+  <threadedComment ref="F5" personId="{6F937CC8-61BE-D0EE-F4A9-6B5B9699B9D3}" id="{6C417BF5-DE07-0698-AAF2-F8C13C1BFC5C}" done="0">
     <text xml:space="preserve">(Документирует требования и пользовательские сценарии на понятном для команды языке
 </text>
   </threadedComment>
-  <threadedComment ref="G5" personId="{55C010E3-CD73-0CAD-46BE-B156B742904C}" id="{7A2408D7-D9B4-4ABD-3B83-06D41BA8E58A}" done="0">
+  <threadedComment ref="G5" personId="{6F937CC8-61BE-D0EE-F4A9-6B5B9699B9D3}" id="{7A2408D7-D9B4-4ABD-3B83-06D41BA8E58A}" done="0">
     <text xml:space="preserve">Консультирует по инфраструктурным требованиям и ограничениям, влияющим на развертывание
 </text>
   </threadedComment>
-  <threadedComment ref="H5" personId="{55C010E3-CD73-0CAD-46BE-B156B742904C}" id="{F1DED64E-D08E-B5AE-C6CD-A85C8671A463}" done="0">
+  <threadedComment ref="H5" personId="{6F937CC8-61BE-D0EE-F4A9-6B5B9699B9D3}" id="{F1DED64E-D08E-B5AE-C6CD-A85C8671A463}" done="0">
     <text xml:space="preserve">Помогает сформулировать критерии приемки, чтобы требования были тестируемыми
 </text>
   </threadedComment>
-  <threadedComment ref="I5" personId="{55C010E3-CD73-0CAD-46BE-B156B742904C}" id="{7CB5543B-36F0-4F6C-C70C-074B6F2AA6B2}" done="0">
+  <threadedComment ref="I5" personId="{6F937CC8-61BE-D0EE-F4A9-6B5B9699B9D3}" id="{7CB5543B-36F0-4F6C-C70C-074B6F2AA6B2}" done="0">
     <text xml:space="preserve">Создает интерактивные прототипы и визуализации
-</text>
-  </threadedComment>
-  <threadedComment ref="J5" personId="{55C010E3-CD73-0CAD-46BE-B156B742904C}" id="{83B2669F-6FAD-1EEF-D66E-0F968B3E4855}" done="0">
-    <text xml:space="preserve">Информируется о завершении этапа сбора требований
 </text>
   </threadedComment>
 </ThreadedComments>
@@ -4260,3653 +4309,749 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col customWidth="1" min="1" max="1" width="4.4531200000000002"/>
-    <col customWidth="1" min="2" max="2" width="37.179699999999997"/>
-    <col customWidth="1" min="3" max="3" width="23.542999999999999"/>
-    <col customWidth="1" min="4" max="4" width="14.726599999999999"/>
-    <col customWidth="1" min="5" max="5" width="12.8164"/>
-    <col customWidth="1" min="6" max="6" width="9.5429700000000004"/>
-    <col customWidth="1" min="7" max="7" width="10"/>
-    <col customWidth="1" min="8" max="8" width="54.453099999999999"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="30">
-      <c r="A1" s="131" t="s">
-        <v>91</v>
-      </c>
-      <c r="B1" s="131" t="s">
-        <v>183</v>
-      </c>
-      <c r="C1" s="131" t="s">
-        <v>184</v>
-      </c>
-      <c r="D1" s="131" t="s">
-        <v>185</v>
-      </c>
-      <c r="E1" s="131" t="s">
-        <v>186</v>
-      </c>
-      <c r="F1" s="131" t="s">
-        <v>187</v>
-      </c>
-      <c r="G1" s="131" t="s">
-        <v>188</v>
-      </c>
-      <c r="H1" s="131" t="s">
-        <v>189</v>
-      </c>
-    </row>
-    <row r="2" ht="60">
-      <c r="A2" s="132">
-        <v>1</v>
-      </c>
-      <c r="B2" s="132" t="s">
-        <v>190</v>
-      </c>
-      <c r="C2" s="132" t="s">
-        <v>191</v>
-      </c>
-      <c r="D2" s="132" t="s">
-        <v>192</v>
-      </c>
-      <c r="E2" s="132">
-        <v>0.80000000000000004</v>
-      </c>
-      <c r="F2" s="132">
-        <v>0.90000000000000002</v>
-      </c>
-      <c r="G2" s="132">
-        <v>0.71999999999999997</v>
-      </c>
-      <c r="H2" s="132" t="s">
-        <v>193</v>
-      </c>
-    </row>
-    <row r="3" ht="60">
-      <c r="A3" s="132">
-        <v>2</v>
-      </c>
-      <c r="B3" s="132" t="s">
-        <v>194</v>
-      </c>
-      <c r="C3" s="132" t="s">
-        <v>195</v>
-      </c>
-      <c r="D3" s="132" t="s">
-        <v>196</v>
-      </c>
-      <c r="E3" s="132">
-        <v>0.80000000000000004</v>
-      </c>
-      <c r="F3" s="132">
-        <v>0.90000000000000002</v>
-      </c>
-      <c r="G3" s="132">
-        <v>0.71999999999999997</v>
-      </c>
-      <c r="H3" s="132" t="s">
-        <v>197</v>
-      </c>
-    </row>
-    <row r="4" ht="60">
-      <c r="A4" s="132">
-        <v>3</v>
-      </c>
-      <c r="B4" s="132" t="s">
-        <v>198</v>
-      </c>
-      <c r="C4" s="132" t="s">
-        <v>199</v>
-      </c>
-      <c r="D4" s="132" t="s">
-        <v>200</v>
-      </c>
-      <c r="E4" s="132">
-        <v>0.80000000000000004</v>
-      </c>
-      <c r="F4" s="132">
-        <v>0.90000000000000002</v>
-      </c>
-      <c r="G4" s="132">
-        <v>0.71999999999999997</v>
-      </c>
-      <c r="H4" s="132" t="s">
-        <v>201</v>
-      </c>
-    </row>
-    <row r="5" ht="60">
-      <c r="A5" s="132">
-        <v>4</v>
-      </c>
-      <c r="B5" s="132" t="s">
-        <v>202</v>
-      </c>
-      <c r="C5" s="132" t="s">
-        <v>203</v>
-      </c>
-      <c r="D5" s="132" t="s">
-        <v>200</v>
-      </c>
-      <c r="E5" s="132">
-        <v>0.80000000000000004</v>
-      </c>
-      <c r="F5" s="132">
-        <v>0.69999999999999996</v>
-      </c>
-      <c r="G5" s="132">
-        <v>0.56000000000000005</v>
-      </c>
-      <c r="H5" s="132" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="6" ht="45">
-      <c r="A6" s="132">
-        <v>5</v>
-      </c>
-      <c r="B6" s="132" t="s">
-        <v>205</v>
-      </c>
-      <c r="C6" s="132" t="s">
-        <v>206</v>
-      </c>
-      <c r="D6" s="132" t="s">
-        <v>207</v>
-      </c>
-      <c r="E6" s="132">
-        <v>0.80000000000000004</v>
-      </c>
-      <c r="F6" s="132">
-        <v>0.69999999999999996</v>
-      </c>
-      <c r="G6" s="132">
-        <v>0.56000000000000005</v>
-      </c>
-      <c r="H6" s="132" t="s">
-        <v>208</v>
-      </c>
-    </row>
-    <row r="7" ht="60">
-      <c r="A7" s="132">
-        <v>6</v>
-      </c>
-      <c r="B7" s="132" t="s">
-        <v>209</v>
-      </c>
-      <c r="C7" s="132" t="s">
-        <v>210</v>
-      </c>
-      <c r="D7" s="132" t="s">
-        <v>207</v>
-      </c>
-      <c r="E7" s="132">
-        <v>0.80000000000000004</v>
-      </c>
-      <c r="F7" s="132">
-        <v>0.69999999999999996</v>
-      </c>
-      <c r="G7" s="132">
-        <v>0.56000000000000005</v>
-      </c>
-      <c r="H7" s="132" t="s">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="8" ht="60">
-      <c r="A8" s="132">
-        <v>7</v>
-      </c>
-      <c r="B8" s="132" t="s">
-        <v>212</v>
-      </c>
-      <c r="C8" s="132" t="s">
-        <v>213</v>
-      </c>
-      <c r="D8" s="132" t="s">
-        <v>200</v>
-      </c>
-      <c r="E8" s="132">
-        <v>0.80000000000000004</v>
-      </c>
-      <c r="F8" s="132">
-        <v>0.69999999999999996</v>
-      </c>
-      <c r="G8" s="132">
-        <v>0.56000000000000005</v>
-      </c>
-      <c r="H8" s="132" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="9" ht="60">
-      <c r="A9" s="132">
-        <v>8</v>
-      </c>
-      <c r="B9" s="132" t="s">
-        <v>215</v>
-      </c>
-      <c r="C9" s="132" t="s">
-        <v>216</v>
-      </c>
-      <c r="D9" s="132" t="s">
-        <v>200</v>
-      </c>
-      <c r="E9" s="132">
-        <v>0.80000000000000004</v>
-      </c>
-      <c r="F9" s="132">
-        <v>0.69999999999999996</v>
-      </c>
-      <c r="G9" s="132">
-        <v>0.56000000000000005</v>
-      </c>
-      <c r="H9" s="132" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="10" ht="60">
-      <c r="A10" s="132">
-        <v>9</v>
-      </c>
-      <c r="B10" s="132" t="s">
-        <v>218</v>
-      </c>
-      <c r="C10" s="132" t="s">
-        <v>219</v>
-      </c>
-      <c r="D10" s="132" t="s">
-        <v>200</v>
-      </c>
-      <c r="E10" s="132">
-        <v>0.80000000000000004</v>
-      </c>
-      <c r="F10" s="132">
-        <v>0.69999999999999996</v>
-      </c>
-      <c r="G10" s="132">
-        <v>0.56000000000000005</v>
-      </c>
-      <c r="H10" s="132" t="s">
-        <v>220</v>
-      </c>
-    </row>
-    <row r="11" ht="45">
-      <c r="A11" s="132">
-        <v>10</v>
-      </c>
-      <c r="B11" s="132" t="s">
-        <v>221</v>
-      </c>
-      <c r="C11" s="132" t="s">
-        <v>222</v>
-      </c>
-      <c r="D11" s="132" t="s">
-        <v>207</v>
-      </c>
-      <c r="E11" s="132">
-        <v>0.40000000000000002</v>
-      </c>
-      <c r="F11" s="132">
-        <v>0.90000000000000002</v>
-      </c>
-      <c r="G11" s="132">
-        <v>0.35999999999999999</v>
-      </c>
-      <c r="H11" s="132" t="s">
-        <v>223</v>
-      </c>
-    </row>
-    <row r="12" ht="45">
-      <c r="A12" s="132">
-        <v>11</v>
-      </c>
-      <c r="B12" s="132" t="s">
-        <v>224</v>
-      </c>
-      <c r="C12" s="132" t="s">
-        <v>225</v>
-      </c>
-      <c r="D12" s="132" t="s">
-        <v>196</v>
-      </c>
-      <c r="E12" s="132">
-        <v>0.40000000000000002</v>
-      </c>
-      <c r="F12" s="132">
-        <v>0.90000000000000002</v>
-      </c>
-      <c r="G12" s="132">
-        <v>0.35999999999999999</v>
-      </c>
-      <c r="H12" s="132" t="s">
-        <v>226</v>
-      </c>
-    </row>
-    <row r="13" ht="30">
-      <c r="A13" s="132">
-        <v>12</v>
-      </c>
-      <c r="B13" s="132" t="s">
-        <v>227</v>
-      </c>
-      <c r="C13" s="132" t="s">
-        <v>228</v>
-      </c>
-      <c r="D13" s="132" t="s">
-        <v>200</v>
-      </c>
-      <c r="E13" s="132">
-        <v>0.40000000000000002</v>
-      </c>
-      <c r="F13" s="132">
-        <v>0.90000000000000002</v>
-      </c>
-      <c r="G13" s="132">
-        <v>0.35999999999999999</v>
-      </c>
-      <c r="H13" s="132" t="s">
-        <v>229</v>
-      </c>
-    </row>
-    <row r="14" ht="45">
-      <c r="A14" s="132">
-        <v>13</v>
-      </c>
-      <c r="B14" s="132" t="s">
-        <v>230</v>
-      </c>
-      <c r="C14" s="132" t="s">
-        <v>231</v>
-      </c>
-      <c r="D14" s="132" t="s">
-        <v>192</v>
-      </c>
-      <c r="E14" s="132">
-        <v>0.40000000000000002</v>
-      </c>
-      <c r="F14" s="132">
-        <v>0.90000000000000002</v>
-      </c>
-      <c r="G14" s="132">
-        <v>0.35999999999999999</v>
-      </c>
-      <c r="H14" s="132" t="s">
-        <v>232</v>
-      </c>
-    </row>
-    <row r="15" ht="45">
-      <c r="A15" s="132">
-        <v>14</v>
-      </c>
-      <c r="B15" s="132" t="s">
-        <v>233</v>
-      </c>
-      <c r="C15" s="132" t="s">
-        <v>234</v>
-      </c>
-      <c r="D15" s="132" t="s">
-        <v>200</v>
-      </c>
-      <c r="E15" s="132">
-        <v>0.80000000000000004</v>
-      </c>
-      <c r="F15" s="132">
-        <v>0.5</v>
-      </c>
-      <c r="G15" s="132">
-        <v>0.40000000000000002</v>
-      </c>
-      <c r="H15" s="132" t="s">
-        <v>235</v>
-      </c>
-    </row>
-    <row r="16" ht="45">
-      <c r="A16" s="132">
-        <v>15</v>
-      </c>
-      <c r="B16" s="132" t="s">
-        <v>236</v>
-      </c>
-      <c r="C16" s="132" t="s">
-        <v>237</v>
-      </c>
-      <c r="D16" s="132" t="s">
-        <v>192</v>
-      </c>
-      <c r="E16" s="132">
-        <v>0.80000000000000004</v>
-      </c>
-      <c r="F16" s="132">
-        <v>0.5</v>
-      </c>
-      <c r="G16" s="132">
-        <v>0.40000000000000002</v>
-      </c>
-      <c r="H16" s="132" t="s">
-        <v>238</v>
-      </c>
-    </row>
-    <row r="17" ht="30">
-      <c r="A17" s="132">
-        <v>16</v>
-      </c>
-      <c r="B17" s="132" t="s">
-        <v>239</v>
-      </c>
-      <c r="C17" s="132" t="s">
-        <v>240</v>
-      </c>
-      <c r="D17" s="132" t="s">
-        <v>200</v>
-      </c>
-      <c r="E17" s="132">
-        <v>0.80000000000000004</v>
-      </c>
-      <c r="F17" s="132">
-        <v>0.5</v>
-      </c>
-      <c r="G17" s="132">
-        <v>0.40000000000000002</v>
-      </c>
-      <c r="H17" s="132" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="18" ht="45">
-      <c r="A18" s="132">
-        <v>17</v>
-      </c>
-      <c r="B18" s="132" t="s">
-        <v>242</v>
-      </c>
-      <c r="C18" s="132" t="s">
-        <v>243</v>
-      </c>
-      <c r="D18" s="132" t="s">
-        <v>200</v>
-      </c>
-      <c r="E18" s="132">
-        <v>0.80000000000000004</v>
-      </c>
-      <c r="F18" s="132">
-        <v>0.5</v>
-      </c>
-      <c r="G18" s="132">
-        <v>0.40000000000000002</v>
-      </c>
-      <c r="H18" s="132" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="19" ht="60">
-      <c r="A19" s="132">
-        <v>18</v>
-      </c>
-      <c r="B19" s="132" t="s">
-        <v>245</v>
-      </c>
-      <c r="C19" s="132" t="s">
-        <v>246</v>
-      </c>
-      <c r="D19" s="132" t="s">
-        <v>207</v>
-      </c>
-      <c r="E19" s="132">
-        <v>0.40000000000000002</v>
-      </c>
-      <c r="F19" s="132">
-        <v>0.69999999999999996</v>
-      </c>
-      <c r="G19" s="132">
-        <v>0.28000000000000003</v>
-      </c>
-      <c r="H19" s="132" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="20" ht="45">
-      <c r="A20" s="132">
-        <v>19</v>
-      </c>
-      <c r="B20" s="132" t="s">
-        <v>248</v>
-      </c>
-      <c r="C20" s="132" t="s">
-        <v>249</v>
-      </c>
-      <c r="D20" s="132" t="s">
-        <v>200</v>
-      </c>
-      <c r="E20" s="132">
-        <v>0.40000000000000002</v>
-      </c>
-      <c r="F20" s="132">
-        <v>0.69999999999999996</v>
-      </c>
-      <c r="G20" s="132">
-        <v>0.28000000000000003</v>
-      </c>
-      <c r="H20" s="132" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="21" ht="45">
-      <c r="A21" s="132">
-        <v>20</v>
-      </c>
-      <c r="B21" s="132" t="s">
-        <v>251</v>
-      </c>
-      <c r="C21" s="132" t="s">
-        <v>252</v>
-      </c>
-      <c r="D21" s="132" t="s">
-        <v>196</v>
-      </c>
-      <c r="E21" s="132">
-        <v>0.40000000000000002</v>
-      </c>
-      <c r="F21" s="132">
-        <v>0.69999999999999996</v>
-      </c>
-      <c r="G21" s="132">
-        <v>0.28000000000000003</v>
-      </c>
-      <c r="H21" s="132" t="s">
-        <v>253</v>
-      </c>
-    </row>
-    <row r="22" ht="45">
-      <c r="A22" s="132">
-        <v>21</v>
-      </c>
-      <c r="B22" s="132" t="s">
-        <v>254</v>
-      </c>
-      <c r="C22" s="132" t="s">
-        <v>255</v>
-      </c>
-      <c r="D22" s="132" t="s">
-        <v>200</v>
-      </c>
-      <c r="E22" s="132">
-        <v>0.40000000000000002</v>
-      </c>
-      <c r="F22" s="132">
-        <v>0.69999999999999996</v>
-      </c>
-      <c r="G22" s="132">
-        <v>0.28000000000000003</v>
-      </c>
-      <c r="H22" s="132" t="s">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="23" ht="60">
-      <c r="A23" s="132">
-        <v>22</v>
-      </c>
-      <c r="B23" s="132" t="s">
-        <v>257</v>
-      </c>
-      <c r="C23" s="132" t="s">
-        <v>258</v>
-      </c>
-      <c r="D23" s="132" t="s">
-        <v>200</v>
-      </c>
-      <c r="E23" s="132">
-        <v>0.40000000000000002</v>
-      </c>
-      <c r="F23" s="132">
-        <v>0.69999999999999996</v>
-      </c>
-      <c r="G23" s="132">
-        <v>0.28000000000000003</v>
-      </c>
-      <c r="H23" s="132" t="s">
-        <v>259</v>
-      </c>
-    </row>
-    <row r="24" ht="45">
-      <c r="A24" s="132">
-        <v>23</v>
-      </c>
-      <c r="B24" s="132" t="s">
-        <v>260</v>
-      </c>
-      <c r="C24" s="132" t="s">
-        <v>261</v>
-      </c>
-      <c r="D24" s="132" t="s">
-        <v>196</v>
-      </c>
-      <c r="E24" s="132">
-        <v>0.40000000000000002</v>
-      </c>
-      <c r="F24" s="132">
-        <v>0.69999999999999996</v>
-      </c>
-      <c r="G24" s="132">
-        <v>0.28000000000000003</v>
-      </c>
-      <c r="H24" s="132" t="s">
-        <v>262</v>
-      </c>
-    </row>
-    <row r="25" ht="30">
-      <c r="A25" s="132">
-        <v>24</v>
-      </c>
-      <c r="B25" s="132" t="s">
-        <v>263</v>
-      </c>
-      <c r="C25" s="132" t="s">
-        <v>264</v>
-      </c>
-      <c r="D25" s="132" t="s">
-        <v>196</v>
-      </c>
-      <c r="E25" s="132">
-        <v>0.40000000000000002</v>
-      </c>
-      <c r="F25" s="132">
-        <v>0.69999999999999996</v>
-      </c>
-      <c r="G25" s="132">
-        <v>0.28000000000000003</v>
-      </c>
-      <c r="H25" s="132" t="s">
-        <v>265</v>
-      </c>
-    </row>
-    <row r="26" ht="45">
-      <c r="A26" s="132">
-        <v>25</v>
-      </c>
-      <c r="B26" s="132" t="s">
-        <v>266</v>
-      </c>
-      <c r="C26" s="132" t="s">
-        <v>267</v>
-      </c>
-      <c r="D26" s="132" t="s">
-        <v>200</v>
-      </c>
-      <c r="E26" s="132">
-        <v>0.80000000000000004</v>
-      </c>
-      <c r="F26" s="132">
-        <v>0.29999999999999999</v>
-      </c>
-      <c r="G26" s="132">
-        <v>0.23999999999999999</v>
-      </c>
-      <c r="H26" s="132" t="s">
-        <v>268</v>
-      </c>
-    </row>
-    <row r="27" ht="45">
-      <c r="A27" s="132">
-        <v>26</v>
-      </c>
-      <c r="B27" s="132" t="s">
-        <v>269</v>
-      </c>
-      <c r="C27" s="132" t="s">
-        <v>270</v>
-      </c>
-      <c r="D27" s="132" t="s">
-        <v>200</v>
-      </c>
-      <c r="E27" s="132">
-        <v>0.80000000000000004</v>
-      </c>
-      <c r="F27" s="132">
-        <v>0.29999999999999999</v>
-      </c>
-      <c r="G27" s="132">
-        <v>0.23999999999999999</v>
-      </c>
-      <c r="H27" s="132" t="s">
-        <v>271</v>
-      </c>
-    </row>
-    <row r="28" ht="45">
-      <c r="A28" s="132">
-        <v>27</v>
-      </c>
-      <c r="B28" s="132" t="s">
-        <v>272</v>
-      </c>
-      <c r="C28" s="132" t="s">
-        <v>273</v>
-      </c>
-      <c r="D28" s="132" t="s">
-        <v>207</v>
-      </c>
-      <c r="E28" s="132">
-        <v>0.80000000000000004</v>
-      </c>
-      <c r="F28" s="132">
-        <v>0.29999999999999999</v>
-      </c>
-      <c r="G28" s="132">
-        <v>0.23999999999999999</v>
-      </c>
-      <c r="H28" s="132" t="s">
-        <v>274</v>
-      </c>
-    </row>
-    <row r="29" ht="45">
-      <c r="A29" s="133">
-        <v>28</v>
-      </c>
-      <c r="B29" s="132" t="s">
-        <v>275</v>
-      </c>
-      <c r="C29" s="132" t="s">
-        <v>276</v>
-      </c>
-      <c r="D29" s="133" t="s">
-        <v>200</v>
-      </c>
-      <c r="E29" s="133">
-        <v>0.80000000000000004</v>
-      </c>
-      <c r="F29" s="133">
-        <v>0.29999999999999999</v>
-      </c>
-      <c r="G29" s="133">
-        <v>0.23999999999999999</v>
-      </c>
-      <c r="H29" s="133" t="s">
-        <v>277</v>
-      </c>
-    </row>
-    <row r="30" ht="45">
-      <c r="A30" s="133">
-        <v>29</v>
-      </c>
-      <c r="B30" s="132" t="s">
-        <v>278</v>
-      </c>
-      <c r="C30" s="132" t="s">
-        <v>279</v>
-      </c>
-      <c r="D30" s="133" t="s">
-        <v>207</v>
-      </c>
-      <c r="E30" s="133">
-        <v>0.80000000000000004</v>
-      </c>
-      <c r="F30" s="133">
-        <v>0.29999999999999999</v>
-      </c>
-      <c r="G30" s="133">
-        <v>0.23999999999999999</v>
-      </c>
-      <c r="H30" s="133" t="s">
-        <v>280</v>
-      </c>
-    </row>
-    <row r="31" ht="45">
-      <c r="A31" s="133">
-        <v>30</v>
-      </c>
-      <c r="B31" s="132" t="s">
-        <v>281</v>
-      </c>
-      <c r="C31" s="132" t="s">
-        <v>282</v>
-      </c>
-      <c r="D31" s="133" t="s">
-        <v>192</v>
-      </c>
-      <c r="E31" s="133">
-        <v>0.20000000000000001</v>
-      </c>
-      <c r="F31" s="133">
-        <v>0.90000000000000002</v>
-      </c>
-      <c r="G31" s="133">
-        <v>0.17999999999999999</v>
-      </c>
-      <c r="H31" s="133" t="s">
-        <v>283</v>
-      </c>
-    </row>
-    <row r="32" ht="45">
-      <c r="A32" s="133">
-        <v>31</v>
-      </c>
-      <c r="B32" s="132" t="s">
-        <v>284</v>
-      </c>
-      <c r="C32" s="132" t="s">
-        <v>285</v>
-      </c>
-      <c r="D32" s="133" t="s">
-        <v>200</v>
-      </c>
-      <c r="E32" s="133">
-        <v>0.20000000000000001</v>
-      </c>
-      <c r="F32" s="133">
-        <v>0.90000000000000002</v>
-      </c>
-      <c r="G32" s="133">
-        <v>0.17999999999999999</v>
-      </c>
-      <c r="H32" s="133" t="s">
-        <v>286</v>
-      </c>
-    </row>
-    <row r="33" ht="45">
-      <c r="A33" s="133">
-        <v>32</v>
-      </c>
-      <c r="B33" s="132" t="s">
-        <v>287</v>
-      </c>
-      <c r="C33" s="132" t="s">
-        <v>288</v>
-      </c>
-      <c r="D33" s="133" t="s">
-        <v>200</v>
-      </c>
-      <c r="E33" s="133">
-        <v>0.20000000000000001</v>
-      </c>
-      <c r="F33" s="133">
-        <v>0.90000000000000002</v>
-      </c>
-      <c r="G33" s="133">
-        <v>0.17999999999999999</v>
-      </c>
-      <c r="H33" s="133" t="s">
-        <v>289</v>
-      </c>
-    </row>
-    <row r="34" ht="45">
-      <c r="A34" s="133">
-        <v>33</v>
-      </c>
-      <c r="B34" s="132" t="s">
-        <v>290</v>
-      </c>
-      <c r="C34" s="132" t="s">
-        <v>291</v>
-      </c>
-      <c r="D34" s="133" t="s">
-        <v>192</v>
-      </c>
-      <c r="E34" s="133">
-        <v>0.20000000000000001</v>
-      </c>
-      <c r="F34" s="133">
-        <v>0.69999999999999996</v>
-      </c>
-      <c r="G34" s="133">
-        <v>0.14000000000000001</v>
-      </c>
-      <c r="H34" s="133" t="s">
-        <v>292</v>
-      </c>
-    </row>
-    <row r="35" ht="30">
-      <c r="A35" s="133">
-        <v>34</v>
-      </c>
-      <c r="B35" s="132" t="s">
-        <v>293</v>
-      </c>
-      <c r="C35" s="132" t="s">
-        <v>294</v>
-      </c>
-      <c r="D35" s="133" t="s">
-        <v>196</v>
-      </c>
-      <c r="E35" s="133">
-        <v>0.20000000000000001</v>
-      </c>
-      <c r="F35" s="133">
-        <v>0.69999999999999996</v>
-      </c>
-      <c r="G35" s="133">
-        <v>0.14000000000000001</v>
-      </c>
-      <c r="H35" s="133" t="s">
-        <v>295</v>
-      </c>
-    </row>
-    <row r="36" ht="30">
-      <c r="A36" s="133">
-        <v>35</v>
-      </c>
-      <c r="B36" s="132" t="s">
-        <v>296</v>
-      </c>
-      <c r="C36" s="132" t="s">
-        <v>297</v>
-      </c>
-      <c r="D36" s="133" t="s">
-        <v>200</v>
-      </c>
-      <c r="E36" s="133">
-        <v>0.20000000000000001</v>
-      </c>
-      <c r="F36" s="133">
-        <v>0.69999999999999996</v>
-      </c>
-      <c r="G36" s="133">
-        <v>0.14000000000000001</v>
-      </c>
-      <c r="H36" s="133" t="s">
-        <v>298</v>
-      </c>
-    </row>
-    <row r="37" ht="45">
-      <c r="A37" s="133">
-        <v>36</v>
-      </c>
-      <c r="B37" s="132" t="s">
-        <v>299</v>
-      </c>
-      <c r="C37" s="132" t="s">
-        <v>300</v>
-      </c>
-      <c r="D37" s="133" t="s">
-        <v>207</v>
-      </c>
-      <c r="E37" s="133">
-        <v>0.20000000000000001</v>
-      </c>
-      <c r="F37" s="133">
-        <v>0.69999999999999996</v>
-      </c>
-      <c r="G37" s="133">
-        <v>0.14000000000000001</v>
-      </c>
-      <c r="H37" s="133" t="s">
-        <v>301</v>
-      </c>
-    </row>
-    <row r="38" ht="30">
-      <c r="A38" s="132">
-        <v>37</v>
-      </c>
-      <c r="B38" s="132" t="s">
-        <v>302</v>
-      </c>
-      <c r="C38" s="132" t="s">
-        <v>303</v>
-      </c>
-      <c r="D38" s="132" t="s">
-        <v>192</v>
-      </c>
-      <c r="E38" s="132">
-        <v>0.40000000000000002</v>
-      </c>
-      <c r="F38" s="132">
-        <v>0.29999999999999999</v>
-      </c>
-      <c r="G38" s="132">
-        <v>0.12</v>
-      </c>
-      <c r="H38" s="132" t="s">
-        <v>304</v>
-      </c>
-    </row>
-    <row r="39" ht="45">
-      <c r="A39" s="132">
-        <v>38</v>
-      </c>
-      <c r="B39" s="132" t="s">
-        <v>305</v>
-      </c>
-      <c r="C39" s="132" t="s">
-        <v>306</v>
-      </c>
-      <c r="D39" s="132" t="s">
-        <v>196</v>
-      </c>
-      <c r="E39" s="132">
-        <v>0.40000000000000002</v>
-      </c>
-      <c r="F39" s="132">
-        <v>0.29999999999999999</v>
-      </c>
-      <c r="G39" s="132">
-        <v>0.12</v>
-      </c>
-      <c r="H39" s="132" t="s">
-        <v>307</v>
-      </c>
-    </row>
-    <row r="40" ht="45">
-      <c r="A40" s="132">
-        <v>39</v>
-      </c>
-      <c r="B40" s="132" t="s">
-        <v>308</v>
-      </c>
-      <c r="C40" s="132" t="s">
-        <v>309</v>
-      </c>
-      <c r="D40" s="132" t="s">
-        <v>196</v>
-      </c>
-      <c r="E40" s="132">
-        <v>0.40000000000000002</v>
-      </c>
-      <c r="F40" s="132">
-        <v>0.29999999999999999</v>
-      </c>
-      <c r="G40" s="132">
-        <v>0.12</v>
-      </c>
-      <c r="H40" s="132" t="s">
-        <v>310</v>
-      </c>
-    </row>
-    <row r="41" ht="45">
-      <c r="A41" s="132">
-        <v>40</v>
-      </c>
-      <c r="B41" s="132" t="s">
-        <v>311</v>
-      </c>
-      <c r="C41" s="132" t="s">
-        <v>312</v>
-      </c>
-      <c r="D41" s="132" t="s">
-        <v>200</v>
-      </c>
-      <c r="E41" s="132">
-        <v>0.40000000000000002</v>
-      </c>
-      <c r="F41" s="132">
-        <v>0.29999999999999999</v>
-      </c>
-      <c r="G41" s="132">
-        <v>0.12</v>
-      </c>
-      <c r="H41" s="132" t="s">
-        <v>313</v>
-      </c>
-    </row>
-    <row r="42" ht="30">
-      <c r="A42" s="132">
-        <v>41</v>
-      </c>
-      <c r="B42" s="132" t="s">
-        <v>314</v>
-      </c>
-      <c r="C42" s="132" t="s">
-        <v>315</v>
-      </c>
-      <c r="D42" s="132" t="s">
-        <v>207</v>
-      </c>
-      <c r="E42" s="132">
-        <v>0.20000000000000001</v>
-      </c>
-      <c r="F42" s="132">
-        <v>0.5</v>
-      </c>
-      <c r="G42" s="132">
-        <v>0.10000000000000001</v>
-      </c>
-      <c r="H42" s="132" t="s">
-        <v>316</v>
-      </c>
-    </row>
-    <row r="43" ht="30">
-      <c r="A43" s="132">
-        <v>42</v>
-      </c>
-      <c r="B43" s="132" t="s">
-        <v>317</v>
-      </c>
-      <c r="C43" s="132" t="s">
-        <v>318</v>
-      </c>
-      <c r="D43" s="132" t="s">
-        <v>192</v>
-      </c>
-      <c r="E43" s="132">
-        <v>0.20000000000000001</v>
-      </c>
-      <c r="F43" s="132">
-        <v>0.5</v>
-      </c>
-      <c r="G43" s="132">
-        <v>0.10000000000000001</v>
-      </c>
-      <c r="H43" s="132" t="s">
-        <v>319</v>
-      </c>
-    </row>
-    <row r="44" ht="30">
-      <c r="A44" s="132">
-        <v>43</v>
-      </c>
-      <c r="B44" s="132" t="s">
-        <v>320</v>
-      </c>
-      <c r="C44" s="132" t="s">
-        <v>321</v>
-      </c>
-      <c r="D44" s="132" t="s">
-        <v>192</v>
-      </c>
-      <c r="E44" s="132">
-        <v>0.10000000000000001</v>
-      </c>
-      <c r="F44" s="132">
-        <v>0.69999999999999996</v>
-      </c>
-      <c r="G44" s="132">
-        <v>0.070000000000000007</v>
-      </c>
-      <c r="H44" s="132" t="s">
-        <v>322</v>
-      </c>
-    </row>
-    <row r="45" ht="30">
-      <c r="A45" s="132">
-        <v>44</v>
-      </c>
-      <c r="B45" s="132" t="s">
-        <v>323</v>
-      </c>
-      <c r="C45" s="132" t="s">
-        <v>324</v>
-      </c>
-      <c r="D45" s="132" t="s">
-        <v>192</v>
-      </c>
-      <c r="E45" s="132">
-        <v>0.10000000000000001</v>
-      </c>
-      <c r="F45" s="132">
-        <v>0.69999999999999996</v>
-      </c>
-      <c r="G45" s="132">
-        <v>0.070000000000000007</v>
-      </c>
-      <c r="H45" s="132" t="s">
-        <v>325</v>
-      </c>
-    </row>
-    <row r="46" ht="45">
-      <c r="A46" s="132">
-        <v>45</v>
-      </c>
-      <c r="B46" s="132" t="s">
-        <v>326</v>
-      </c>
-      <c r="C46" s="132" t="s">
-        <v>327</v>
-      </c>
-      <c r="D46" s="132" t="s">
-        <v>328</v>
-      </c>
-      <c r="E46" s="132">
-        <v>0.40000000000000002</v>
-      </c>
-      <c r="F46" s="132">
-        <v>0.29999999999999999</v>
-      </c>
-      <c r="G46" s="132">
-        <v>0.12</v>
-      </c>
-      <c r="H46" s="132" t="s">
-        <v>329</v>
-      </c>
-    </row>
-    <row r="47" ht="15">
-      <c r="A47" t="s">
-        <v>330</v>
-      </c>
-      <c r="G47" s="134">
-        <f>SUM(G1:G46)</f>
-        <v>13.759999999999998</v>
-      </c>
-    </row>
-    <row r="49" ht="15">
-      <c r="A49" t="s">
-        <v>331</v>
-      </c>
-    </row>
-    <row r="51" ht="15">
-      <c r="B51" s="135" t="s">
-        <v>332</v>
-      </c>
-      <c r="C51" s="135" t="s">
-        <v>333</v>
-      </c>
-    </row>
-    <row r="52" ht="15">
-      <c r="B52" s="136">
-        <v>78</v>
-      </c>
-      <c r="C52" s="136">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="54" ht="15">
-      <c r="B54" s="135" t="s">
-        <v>334</v>
-      </c>
-      <c r="C54" s="135" t="s">
-        <v>333</v>
-      </c>
-    </row>
-    <row r="55" ht="15">
-      <c r="B55" s="137">
-        <v>2451262.8399999999</v>
-      </c>
-      <c r="C55" s="137">
-        <v>2696389.1200000001</v>
-      </c>
-    </row>
-    <row r="59" ht="15">
-      <c r="B59" s="138" t="s">
-        <v>335</v>
-      </c>
-      <c r="C59" s="138" t="s">
-        <v>336</v>
-      </c>
-    </row>
-    <row r="60" ht="15">
-      <c r="B60" s="139" t="s">
-        <v>337</v>
-      </c>
-      <c r="C60" s="139">
-        <v>0.050000000000000003</v>
-      </c>
-    </row>
-    <row r="61" ht="15">
-      <c r="B61" s="139" t="s">
-        <v>338</v>
-      </c>
-      <c r="C61" s="139">
-        <v>0.10000000000000001</v>
-      </c>
-    </row>
-    <row r="62" ht="15">
-      <c r="B62" s="139" t="s">
-        <v>339</v>
-      </c>
-      <c r="C62" s="139">
-        <v>0.20000000000000001</v>
-      </c>
-    </row>
-    <row r="63" ht="15">
-      <c r="B63" s="139" t="s">
-        <v>340</v>
-      </c>
-      <c r="C63" s="139">
-        <v>0.40000000000000002</v>
-      </c>
-    </row>
-    <row r="64" ht="15">
-      <c r="B64" s="139" t="s">
-        <v>341</v>
-      </c>
-      <c r="C64" s="139">
-        <v>0.80000000000000004</v>
-      </c>
-    </row>
-    <row r="65" ht="15">
-      <c r="B65" s="140"/>
-      <c r="C65" s="140"/>
-    </row>
-    <row r="66" ht="15">
-      <c r="B66" s="138" t="s">
-        <v>342</v>
-      </c>
-      <c r="C66" s="138" t="s">
-        <v>336</v>
-      </c>
-    </row>
-    <row r="67" ht="15">
-      <c r="B67" s="139" t="s">
-        <v>343</v>
-      </c>
-      <c r="C67" s="139">
-        <v>0.10000000000000001</v>
-      </c>
-    </row>
-    <row r="68" ht="15">
-      <c r="B68" s="139" t="s">
-        <v>344</v>
-      </c>
-      <c r="C68" s="139">
-        <v>0.29999999999999999</v>
-      </c>
-    </row>
-    <row r="69" ht="15">
-      <c r="B69" s="139" t="s">
-        <v>345</v>
-      </c>
-      <c r="C69" s="139">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="70" ht="15">
-      <c r="B70" s="139" t="s">
-        <v>346</v>
-      </c>
-      <c r="C70" s="139">
-        <v>0.69999999999999996</v>
-      </c>
-    </row>
-    <row r="71" ht="15">
-      <c r="B71" s="139" t="s">
-        <v>347</v>
-      </c>
-      <c r="C71" s="139">
-        <v>0.90000000000000002</v>
-      </c>
-    </row>
-  </sheetData>
-  <printOptions headings="0" gridLines="0"/>
-  <pageMargins left="0.70078740157480324" right="0.70078740157480324" top="0.75196850393700787" bottom="0.75196850393700787" header="0.29999999999999999" footer="0.29999999999999999"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" cellComments="none" useFirstPageNumber="0" errors="displayed" horizontalDpi="600" verticalDpi="600" copies="1"/>
-  <headerFooter/>
-  <legacyDrawing r:id="rId3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col customWidth="1" min="1" max="1" width="19.1797"/>
-    <col customWidth="1" min="2" max="2" width="9.4531200000000002"/>
-    <col customWidth="1" min="3" max="3" width="11.9062"/>
-    <col customWidth="1" min="4" max="4" width="11.363300000000001"/>
-    <col customWidth="1" min="5" max="5" width="10.363300000000001"/>
-    <col customWidth="1" min="6" max="6" width="10.6328"/>
-    <col customWidth="1" min="7" max="11" width="8.88671875"/>
-    <col customWidth="1" min="12" max="12" width="12.269500000000001"/>
-    <col customWidth="1" min="13" max="13" width="6.3632799999999996"/>
-    <col customWidth="1" min="14" max="14" width="29.6328"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="150">
-      <c r="A1" s="141" t="s">
-        <v>348</v>
-      </c>
-      <c r="B1" s="141" t="s">
-        <v>131</v>
-      </c>
-      <c r="C1" s="141" t="s">
-        <v>132</v>
-      </c>
-      <c r="D1" s="141" t="s">
-        <v>133</v>
-      </c>
-      <c r="E1" s="141" t="s">
-        <v>134</v>
-      </c>
-      <c r="F1" s="141" t="s">
-        <v>135</v>
-      </c>
-      <c r="G1" s="141" t="s">
-        <v>136</v>
-      </c>
-      <c r="H1" s="141" t="s">
-        <v>137</v>
-      </c>
-      <c r="I1" s="141" t="s">
-        <v>349</v>
-      </c>
-      <c r="J1" s="141" t="s">
-        <v>350</v>
-      </c>
-      <c r="K1" s="142"/>
-      <c r="L1" s="142"/>
-      <c r="M1" s="40"/>
-      <c r="N1" s="143" t="s">
-        <v>351</v>
-      </c>
-    </row>
-    <row r="2" ht="45">
-      <c r="A2" s="144" t="s">
-        <v>190</v>
-      </c>
-      <c r="B2" s="141" t="s">
-        <v>352</v>
-      </c>
-      <c r="C2" s="141" t="s">
-        <v>353</v>
-      </c>
-      <c r="D2" s="141" t="s">
-        <v>354</v>
-      </c>
-      <c r="E2" s="141" t="s">
-        <v>354</v>
-      </c>
-      <c r="F2" s="141" t="s">
-        <v>354</v>
-      </c>
-      <c r="G2" s="141" t="s">
-        <v>355</v>
-      </c>
-      <c r="H2" s="141" t="s">
-        <v>354</v>
-      </c>
-      <c r="I2" s="141" t="s">
-        <v>353</v>
-      </c>
-      <c r="J2" s="141" t="s">
-        <v>355</v>
-      </c>
-      <c r="K2" s="142"/>
-      <c r="L2" s="142"/>
-      <c r="M2" s="40"/>
-      <c r="N2" s="145"/>
-    </row>
-    <row r="3" ht="30">
-      <c r="A3" s="144" t="s">
-        <v>194</v>
-      </c>
-      <c r="B3" s="141" t="s">
-        <v>352</v>
-      </c>
-      <c r="C3" s="141" t="s">
-        <v>353</v>
-      </c>
-      <c r="D3" s="141" t="s">
-        <v>355</v>
-      </c>
-      <c r="E3" s="141" t="s">
-        <v>355</v>
-      </c>
-      <c r="F3" s="141" t="s">
-        <v>355</v>
-      </c>
-      <c r="G3" s="141" t="s">
-        <v>355</v>
-      </c>
-      <c r="H3" s="141" t="s">
-        <v>354</v>
-      </c>
-      <c r="I3" s="141" t="s">
-        <v>353</v>
-      </c>
-      <c r="J3" s="141" t="s">
-        <v>354</v>
-      </c>
-      <c r="K3" s="142"/>
-      <c r="L3" s="142"/>
-      <c r="M3" s="40"/>
-      <c r="N3" s="145"/>
-    </row>
-    <row r="4" ht="30">
-      <c r="A4" s="144" t="s">
-        <v>198</v>
-      </c>
-      <c r="B4" s="141" t="s">
-        <v>354</v>
-      </c>
-      <c r="C4" s="141" t="s">
-        <v>355</v>
-      </c>
-      <c r="D4" s="141" t="s">
-        <v>354</v>
-      </c>
-      <c r="E4" s="141" t="s">
-        <v>354</v>
-      </c>
-      <c r="F4" s="141" t="s">
-        <v>356</v>
-      </c>
-      <c r="G4" s="141" t="s">
-        <v>354</v>
-      </c>
-      <c r="H4" s="141" t="s">
-        <v>355</v>
-      </c>
-      <c r="I4" s="141" t="s">
-        <v>355</v>
-      </c>
-      <c r="J4" s="141" t="s">
-        <v>354</v>
-      </c>
-      <c r="K4" s="142"/>
-      <c r="L4" s="142"/>
-      <c r="M4" s="40"/>
-      <c r="N4" s="145"/>
-    </row>
-    <row r="5" ht="60">
-      <c r="A5" s="144" t="s">
-        <v>202</v>
-      </c>
-      <c r="B5" s="141" t="s">
-        <v>354</v>
-      </c>
-      <c r="C5" s="141" t="s">
-        <v>355</v>
-      </c>
-      <c r="D5" s="141" t="s">
-        <v>354</v>
-      </c>
-      <c r="E5" s="141" t="s">
-        <v>355</v>
-      </c>
-      <c r="F5" s="141" t="s">
-        <v>356</v>
-      </c>
-      <c r="G5" s="141" t="s">
-        <v>355</v>
-      </c>
-      <c r="H5" s="141" t="s">
-        <v>355</v>
-      </c>
-      <c r="I5" s="141" t="s">
-        <v>353</v>
-      </c>
-      <c r="J5" s="141" t="s">
-        <v>354</v>
-      </c>
-      <c r="K5" s="146"/>
-      <c r="L5" s="146"/>
-      <c r="M5" s="40"/>
-      <c r="N5" s="145"/>
-    </row>
-    <row r="6" ht="45">
-      <c r="A6" s="144" t="s">
-        <v>205</v>
-      </c>
-      <c r="B6" s="141" t="s">
-        <v>356</v>
-      </c>
-      <c r="C6" s="141" t="s">
-        <v>354</v>
-      </c>
-      <c r="D6" s="141" t="s">
-        <v>355</v>
-      </c>
-      <c r="E6" s="141" t="s">
-        <v>355</v>
-      </c>
-      <c r="F6" s="141" t="s">
-        <v>355</v>
-      </c>
-      <c r="G6" s="141" t="s">
-        <v>354</v>
-      </c>
-      <c r="H6" s="141" t="s">
-        <v>354</v>
-      </c>
-      <c r="I6" s="141" t="s">
-        <v>354</v>
-      </c>
-      <c r="J6" s="141" t="s">
-        <v>354</v>
-      </c>
-      <c r="K6" s="142"/>
-      <c r="L6" s="142"/>
-      <c r="M6" s="34"/>
-      <c r="N6" s="147"/>
-    </row>
-    <row r="7" ht="30">
-      <c r="A7" s="144" t="s">
-        <v>209</v>
-      </c>
-      <c r="B7" s="141" t="s">
-        <v>352</v>
-      </c>
-      <c r="C7" s="141" t="s">
-        <v>354</v>
-      </c>
-      <c r="D7" s="141" t="s">
-        <v>354</v>
-      </c>
-      <c r="E7" s="141" t="s">
-        <v>354</v>
-      </c>
-      <c r="F7" s="141" t="s">
-        <v>353</v>
-      </c>
-      <c r="G7" s="141" t="s">
-        <v>354</v>
-      </c>
-      <c r="H7" s="141" t="s">
-        <v>354</v>
-      </c>
-      <c r="I7" s="141" t="s">
-        <v>354</v>
-      </c>
-      <c r="J7" s="141" t="s">
-        <v>355</v>
-      </c>
-      <c r="K7" s="34"/>
-      <c r="L7" s="34"/>
-      <c r="M7" s="34"/>
-      <c r="N7" s="147"/>
-    </row>
-    <row r="8" ht="30">
-      <c r="A8" s="144" t="s">
-        <v>212</v>
-      </c>
-      <c r="B8" s="141" t="s">
-        <v>352</v>
-      </c>
-      <c r="C8" s="141" t="s">
-        <v>354</v>
-      </c>
-      <c r="D8" s="141" t="s">
-        <v>353</v>
-      </c>
-      <c r="E8" s="141" t="s">
-        <v>354</v>
-      </c>
-      <c r="F8" s="141" t="s">
-        <v>353</v>
-      </c>
-      <c r="G8" s="141" t="s">
-        <v>354</v>
-      </c>
-      <c r="H8" s="141" t="s">
-        <v>355</v>
-      </c>
-      <c r="I8" s="141" t="s">
-        <v>354</v>
-      </c>
-      <c r="J8" s="141" t="s">
-        <v>354</v>
-      </c>
-      <c r="K8" s="34"/>
-      <c r="L8" s="34"/>
-      <c r="M8" s="34"/>
-      <c r="N8" s="147"/>
-    </row>
-    <row r="9" ht="45">
-      <c r="A9" s="144" t="s">
-        <v>215</v>
-      </c>
-      <c r="B9" s="141" t="s">
-        <v>352</v>
-      </c>
-      <c r="C9" s="141" t="s">
-        <v>354</v>
-      </c>
-      <c r="D9" s="141" t="s">
-        <v>353</v>
-      </c>
-      <c r="E9" s="141" t="s">
-        <v>354</v>
-      </c>
-      <c r="F9" s="141" t="s">
-        <v>353</v>
-      </c>
-      <c r="G9" s="141" t="s">
-        <v>354</v>
-      </c>
-      <c r="H9" s="141" t="s">
-        <v>355</v>
-      </c>
-      <c r="I9" s="141" t="s">
-        <v>354</v>
-      </c>
-      <c r="J9" s="141" t="s">
-        <v>354</v>
-      </c>
-      <c r="K9" s="34"/>
-      <c r="L9" s="34"/>
-      <c r="M9" s="34"/>
-      <c r="N9" s="147"/>
-    </row>
-    <row r="10" ht="45">
-      <c r="A10" s="148" t="s">
-        <v>218</v>
-      </c>
-      <c r="B10" s="149" t="s">
-        <v>352</v>
-      </c>
-      <c r="C10" s="149" t="s">
-        <v>354</v>
-      </c>
-      <c r="D10" s="149" t="s">
-        <v>355</v>
-      </c>
-      <c r="E10" s="149" t="s">
-        <v>354</v>
-      </c>
-      <c r="F10" s="149" t="s">
-        <v>353</v>
-      </c>
-      <c r="G10" s="149" t="s">
-        <v>354</v>
-      </c>
-      <c r="H10" s="149" t="s">
-        <v>355</v>
-      </c>
-      <c r="I10" s="149" t="s">
-        <v>354</v>
-      </c>
-      <c r="J10" s="149" t="s">
-        <v>355</v>
-      </c>
-      <c r="K10" s="150"/>
-      <c r="L10" s="150"/>
-      <c r="M10" s="150"/>
-      <c r="N10" s="147"/>
-    </row>
-    <row r="11" ht="30">
-      <c r="A11" s="148" t="s">
-        <v>221</v>
-      </c>
-      <c r="B11" s="149" t="s">
-        <v>356</v>
-      </c>
-      <c r="C11" s="149" t="s">
-        <v>354</v>
-      </c>
-      <c r="D11" s="149" t="s">
-        <v>354</v>
-      </c>
-      <c r="E11" s="149" t="s">
-        <v>354</v>
-      </c>
-      <c r="F11" s="149" t="s">
-        <v>354</v>
-      </c>
-      <c r="G11" s="149" t="s">
-        <v>354</v>
-      </c>
-      <c r="H11" s="149" t="s">
-        <v>354</v>
-      </c>
-      <c r="I11" s="149" t="s">
-        <v>354</v>
-      </c>
-      <c r="J11" s="149" t="s">
-        <v>355</v>
-      </c>
-      <c r="K11" s="150"/>
-      <c r="L11" s="150"/>
-      <c r="M11" s="150"/>
-      <c r="N11" s="147"/>
-    </row>
-    <row r="12" ht="15">
-      <c r="A12" s="150"/>
-      <c r="B12" s="150"/>
-      <c r="C12" s="150"/>
-      <c r="D12" s="150"/>
-      <c r="E12" s="150"/>
-      <c r="F12" s="150"/>
-      <c r="G12" s="150"/>
-      <c r="H12" s="150"/>
-      <c r="I12" s="150"/>
-      <c r="J12" s="150"/>
-      <c r="K12" s="150"/>
-      <c r="L12" s="150"/>
-      <c r="M12" s="150"/>
-      <c r="N12" s="147"/>
-    </row>
-    <row r="13" ht="15">
-      <c r="A13" s="150"/>
-      <c r="B13" s="150"/>
-      <c r="C13" s="150"/>
-      <c r="D13" s="150"/>
-      <c r="E13" s="150"/>
-      <c r="F13" s="150"/>
-      <c r="G13" s="150"/>
-      <c r="H13" s="150"/>
-      <c r="I13" s="150"/>
-      <c r="J13" s="150"/>
-      <c r="K13" s="150"/>
-      <c r="L13" s="150"/>
-      <c r="M13" s="150"/>
-      <c r="N13" s="147"/>
-    </row>
-    <row r="14" ht="15">
-      <c r="A14" s="150"/>
-      <c r="B14" s="150"/>
-      <c r="C14" s="150"/>
-      <c r="D14" s="150"/>
-      <c r="E14" s="150"/>
-      <c r="F14" s="150"/>
-      <c r="G14" s="150"/>
-      <c r="H14" s="150"/>
-      <c r="I14" s="150"/>
-      <c r="J14" s="150"/>
-      <c r="K14" s="150"/>
-      <c r="L14" s="150"/>
-      <c r="M14" s="150"/>
-      <c r="N14" s="147"/>
-    </row>
-  </sheetData>
-  <printOptions headings="0" gridLines="0"/>
-  <pageMargins left="0.70078740157480324" right="0.70078740157480324" top="0.75196850393700787" bottom="0.75196850393700787" header="0.29999999999999999" footer="0.29999999999999999"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" cellComments="none" useFirstPageNumber="0" errors="displayed" horizontalDpi="600" verticalDpi="600" copies="1"/>
-  <headerFooter/>
-  <legacyDrawing r:id="rId3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
-  <sheetPr>
-    <outlinePr applyStyles="0" summaryBelow="1" summaryRight="1" showOutlineSymbols="1"/>
-    <pageSetUpPr autoPageBreaks="1" fitToPage="0"/>
-  </sheetPr>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15.050000000000001" customHeight="1"/>
-  <sheetData>
-    <row r="1" ht="15.050000000000001">
-      <c r="A1" s="25" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="3" ht="15.050000000000001" customHeight="1">
-      <c r="A3" s="26"/>
-    </row>
-  </sheetData>
-  <printOptions headings="0" gridLines="0"/>
-  <pageMargins left="0.69999999999999996" right="0.69999999999999996" top="0.75" bottom="0.75" header="0.29999999999999999" footer="0.29999999999999999"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" cellComments="none" useFirstPageNumber="0" errors="displayed" horizontalDpi="600" verticalDpi="600" copies="1"/>
-  <headerFooter/>
-  <drawing r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
-  <sheetPr>
-    <outlinePr applyStyles="0" summaryBelow="1" summaryRight="1" showOutlineSymbols="1"/>
-    <pageSetUpPr autoPageBreaks="1" fitToPage="0"/>
-  </sheetPr>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15.050000000000001" customHeight="1"/>
-  <cols>
-    <col customWidth="1" min="1" max="1" width="44.816400000000002"/>
-    <col customWidth="1" min="2" max="2" width="20.99609375"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="15.050000000000001">
-      <c r="A1" s="27" t="s">
-        <v>65</v>
-      </c>
-      <c r="B1" s="27" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="2" ht="15.050000000000001">
-      <c r="A2" s="11" t="s">
-        <v>67</v>
-      </c>
-      <c r="B2" s="11" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="3" ht="30">
-      <c r="A3" s="11" t="s">
-        <v>69</v>
-      </c>
-      <c r="B3" s="11" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="4" ht="30">
-      <c r="A4" s="11" t="s">
-        <v>71</v>
-      </c>
-      <c r="B4" s="11" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="5" ht="45">
-      <c r="A5" s="11" t="s">
-        <v>73</v>
-      </c>
-      <c r="B5" s="11" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="6" ht="30">
-      <c r="A6" s="11" t="s">
-        <v>75</v>
-      </c>
-      <c r="B6" s="11" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="7" ht="30">
-      <c r="A7" s="11" t="s">
-        <v>77</v>
-      </c>
-      <c r="B7" s="11" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="8" ht="30">
-      <c r="A8" s="11" t="s">
-        <v>79</v>
-      </c>
-      <c r="B8" s="11" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="9" ht="30">
-      <c r="A9" s="11" t="s">
-        <v>81</v>
-      </c>
-      <c r="B9" s="11" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="10" ht="30">
-      <c r="A10" s="11" t="s">
-        <v>83</v>
-      </c>
-      <c r="B10" s="11" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="11" ht="30">
-      <c r="A11" s="11" t="s">
-        <v>85</v>
-      </c>
-      <c r="B11" s="11" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="12" ht="30">
-      <c r="A12" s="11" t="s">
-        <v>87</v>
-      </c>
-      <c r="B12" s="11" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="13" ht="30">
-      <c r="A13" s="11" t="s">
-        <v>89</v>
-      </c>
-      <c r="B13" s="11" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="14" ht="15.050000000000001">
-      <c r="A14" s="27"/>
-      <c r="B14" s="27"/>
-    </row>
-    <row r="15" ht="15.050000000000001">
-      <c r="A15" s="27"/>
-      <c r="B15" s="27"/>
-    </row>
-    <row r="16" ht="15.050000000000001">
-      <c r="A16" s="27"/>
-      <c r="B16" s="27"/>
-    </row>
-    <row r="17" ht="15.050000000000001">
-      <c r="A17" s="27"/>
-      <c r="B17" s="27"/>
-    </row>
-    <row r="18" ht="15.050000000000001">
-      <c r="A18" s="27"/>
-      <c r="B18" s="27"/>
-    </row>
-    <row r="19" ht="15.050000000000001">
-      <c r="A19" s="27"/>
-      <c r="B19" s="27"/>
-    </row>
-  </sheetData>
-  <printOptions headings="0" gridLines="0"/>
-  <pageMargins left="0.69999999999999996" right="0.69999999999999996" top="0.75" bottom="0.75" header="0.29999999999999999" footer="0.29999999999999999"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" cellComments="none" useFirstPageNumber="0" errors="displayed" horizontalDpi="600" verticalDpi="600" copies="1"/>
-  <headerFooter/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
-  <sheetPr>
-    <outlinePr applyStyles="0" summaryBelow="1" summaryRight="1" showOutlineSymbols="1"/>
-    <pageSetUpPr autoPageBreaks="1" fitToPage="0"/>
-  </sheetPr>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15.050000000000001" customHeight="1"/>
-  <cols>
-    <col customWidth="1" min="1" max="1" width="4.0898399999999997"/>
-    <col bestFit="1" customWidth="1" min="2" max="2" width="20.265625"/>
-    <col bestFit="1" min="3" max="3" width="10.1640625"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="15.050000000000001">
-      <c r="A1" s="27" t="s">
-        <v>91</v>
-      </c>
-      <c r="B1" s="27" t="s">
-        <v>92</v>
-      </c>
-      <c r="C1" s="27" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="2" ht="60">
-      <c r="A2" s="11">
-        <v>1</v>
-      </c>
-      <c r="B2" s="11" t="s">
-        <v>94</v>
-      </c>
-      <c r="C2" s="11" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="3" ht="75">
-      <c r="A3" s="11">
-        <v>2</v>
-      </c>
-      <c r="B3" s="11" t="s">
-        <v>96</v>
-      </c>
-      <c r="C3" s="11" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="4" ht="105">
-      <c r="A4" s="11">
-        <v>3</v>
-      </c>
-      <c r="B4" s="11" t="s">
-        <v>98</v>
-      </c>
-      <c r="C4" s="11" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="5" ht="75">
-      <c r="A5" s="11">
-        <v>4</v>
-      </c>
-      <c r="B5" s="11" t="s">
-        <v>100</v>
-      </c>
-      <c r="C5" s="11" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="6" ht="75">
-      <c r="A6" s="11">
-        <v>5</v>
-      </c>
-      <c r="B6" s="11" t="s">
-        <v>102</v>
-      </c>
-      <c r="C6" s="11" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="7" ht="75">
-      <c r="A7" s="11">
-        <v>6</v>
-      </c>
-      <c r="B7" s="11" t="s">
-        <v>104</v>
-      </c>
-      <c r="C7" s="11" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="8" ht="62.25" customHeight="1">
-      <c r="A8" s="11">
-        <v>7</v>
-      </c>
-      <c r="B8" s="11" t="s">
-        <v>106</v>
-      </c>
-      <c r="C8" s="28">
-        <v>46203</v>
-      </c>
-    </row>
-  </sheetData>
-  <printOptions headings="0" gridLines="0"/>
-  <pageMargins left="0.69999999999999996" right="0.69999999999999996" top="0.75" bottom="0.75" header="0.29999999999999999" footer="0.29999999999999999"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" cellComments="none" useFirstPageNumber="0" errors="displayed" horizontalDpi="600" verticalDpi="600" copies="1"/>
-  <headerFooter/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
-  <sheetPr>
-    <outlinePr applyStyles="0" summaryBelow="1" summaryRight="1" showOutlineSymbols="1"/>
-    <pageSetUpPr autoPageBreaks="1" fitToPage="0"/>
-  </sheetPr>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15.050000000000001" customHeight="1"/>
-  <cols>
-    <col customWidth="1" min="1" max="1" width="4.3632799999999996"/>
-    <col customWidth="1" min="2" max="2" width="32.363300000000002"/>
-    <col customWidth="1" min="3" max="3" width="18.906199999999998"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="15.050000000000001">
-      <c r="A1" s="27" t="s">
-        <v>91</v>
-      </c>
-      <c r="B1" s="27" t="s">
-        <v>92</v>
-      </c>
-      <c r="C1" s="27" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="2" ht="45">
-      <c r="A2" s="11">
-        <v>1</v>
-      </c>
-      <c r="B2" s="11" t="s">
-        <v>107</v>
-      </c>
-      <c r="C2" s="11" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="3" ht="45">
-      <c r="A3" s="11">
-        <v>2</v>
-      </c>
-      <c r="B3" s="11" t="s">
-        <v>108</v>
-      </c>
-      <c r="C3" s="11" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="4" ht="60">
-      <c r="A4" s="11">
-        <v>3</v>
-      </c>
-      <c r="B4" s="11" t="s">
-        <v>109</v>
-      </c>
-      <c r="C4" s="11" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="5" ht="45">
-      <c r="A5" s="11">
-        <v>4</v>
-      </c>
-      <c r="B5" s="11" t="s">
-        <v>110</v>
-      </c>
-      <c r="C5" s="11" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="6" ht="60">
-      <c r="A6" s="11">
-        <v>5</v>
-      </c>
-      <c r="B6" s="11" t="s">
-        <v>111</v>
-      </c>
-      <c r="C6" s="11" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="7" ht="45">
-      <c r="A7" s="11">
-        <v>6</v>
-      </c>
-      <c r="B7" s="11" t="s">
-        <v>112</v>
-      </c>
-      <c r="C7" s="28">
-        <v>46203</v>
-      </c>
-    </row>
-    <row r="8" ht="78.75" customHeight="1">
-      <c r="A8" s="11">
-        <v>7</v>
-      </c>
-      <c r="B8" s="11" t="s">
-        <v>113</v>
-      </c>
-      <c r="C8" s="28">
-        <v>46203</v>
-      </c>
-    </row>
-  </sheetData>
-  <printOptions headings="0" gridLines="0"/>
-  <pageMargins left="0.69999999999999996" right="0.69999999999999996" top="0.75" bottom="0.75" header="0.29999999999999999" footer="0.29999999999999999"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" cellComments="none" useFirstPageNumber="0" errors="displayed" horizontalDpi="600" verticalDpi="600" copies="1"/>
-  <headerFooter/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
-  <sheetPr>
-    <outlinePr applyStyles="0" summaryBelow="1" summaryRight="1" showOutlineSymbols="1"/>
-    <pageSetUpPr autoPageBreaks="1" fitToPage="0"/>
-  </sheetPr>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15.050000000000001" customHeight="1"/>
-  <cols>
-    <col customWidth="1" min="1" max="1" width="11.9062"/>
-    <col customWidth="1" min="2" max="2" width="40.906199999999998"/>
-    <col customWidth="1" min="3" max="3" width="29.0898"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="15.65">
-      <c r="A1" s="29" t="s">
-        <v>114</v>
-      </c>
-      <c r="B1" s="29" t="s">
-        <v>115</v>
-      </c>
-      <c r="C1" s="29" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="2" ht="47">
-      <c r="A2" s="30">
-        <v>1</v>
-      </c>
-      <c r="B2" s="30" t="s">
-        <v>117</v>
-      </c>
-      <c r="C2" s="30" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="3" ht="15.65">
-      <c r="A3" s="31">
-        <v>2</v>
-      </c>
-      <c r="B3" s="31" t="s">
-        <v>119</v>
-      </c>
-      <c r="C3" s="31" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="4" ht="15.65">
-      <c r="A4" s="31">
-        <v>3</v>
-      </c>
-      <c r="B4" s="31" t="s">
-        <v>121</v>
-      </c>
-      <c r="C4" s="31" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="5" ht="15.65">
-      <c r="A5" s="31">
-        <v>4</v>
-      </c>
-      <c r="B5" s="31" t="s">
-        <v>123</v>
-      </c>
-      <c r="C5" s="31" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="6" ht="15.65">
-      <c r="A6" s="32">
-        <v>5</v>
-      </c>
-      <c r="B6" s="32" t="s">
-        <v>125</v>
-      </c>
-      <c r="C6" s="32" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="7" ht="15.65">
-      <c r="A7" s="33"/>
-      <c r="B7" s="33"/>
-      <c r="C7" s="33"/>
-    </row>
-    <row r="8" ht="15.65">
-      <c r="A8" s="33"/>
-      <c r="B8" s="33"/>
-      <c r="C8" s="33"/>
-    </row>
-    <row r="9" ht="15.65">
-      <c r="A9" s="33"/>
-      <c r="B9" s="33"/>
-      <c r="C9" s="33"/>
-    </row>
-    <row r="10" ht="15.65">
-      <c r="A10" s="33"/>
-      <c r="B10" s="33"/>
-      <c r="C10" s="33"/>
-    </row>
-    <row r="11" ht="15.050000000000001">
-      <c r="A11" s="3"/>
-      <c r="B11" s="3"/>
-      <c r="C11" s="3"/>
-    </row>
-    <row r="12" ht="15.050000000000001">
-      <c r="A12" s="3"/>
-      <c r="B12" s="3"/>
-      <c r="C12" s="3"/>
-    </row>
-    <row r="13" ht="15.050000000000001">
-      <c r="A13" s="3"/>
-      <c r="B13" s="3"/>
-      <c r="C13" s="3"/>
-    </row>
-    <row r="14" ht="15.050000000000001">
-      <c r="A14" s="3"/>
-      <c r="B14" s="3"/>
-      <c r="C14" s="3"/>
-    </row>
-    <row r="15" ht="15.050000000000001">
-      <c r="A15" s="3"/>
-      <c r="B15" s="3"/>
-      <c r="C15" s="3"/>
-    </row>
-    <row r="16" ht="15.050000000000001">
-      <c r="A16" s="3"/>
-      <c r="B16" s="3"/>
-      <c r="C16" s="3"/>
-    </row>
-    <row r="17" ht="15.050000000000001">
-      <c r="A17" s="3"/>
-      <c r="B17" s="3"/>
-      <c r="C17" s="3"/>
-    </row>
-    <row r="18" ht="15.050000000000001">
-      <c r="A18" s="3"/>
-      <c r="B18" s="3"/>
-      <c r="C18" s="3"/>
-    </row>
-    <row r="19" ht="15.050000000000001">
-      <c r="A19" s="3"/>
-      <c r="B19" s="3"/>
-      <c r="C19" s="3"/>
-    </row>
-    <row r="20" ht="15.050000000000001">
-      <c r="A20" s="3"/>
-      <c r="B20" s="3"/>
-      <c r="C20" s="3"/>
-    </row>
-  </sheetData>
-  <printOptions headings="0" gridLines="0"/>
-  <pageMargins left="0.69999999999999996" right="0.69999999999999996" top="0.75" bottom="0.75" header="0.29999999999999999" footer="0.29999999999999999"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" cellComments="none" useFirstPageNumber="0" errors="displayed" horizontalDpi="600" verticalDpi="600" copies="1"/>
-  <headerFooter/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
-  <sheetPr>
-    <outlinePr applyStyles="0" summaryBelow="1" summaryRight="1" showOutlineSymbols="1"/>
-    <pageSetUpPr autoPageBreaks="1" fitToPage="0"/>
-  </sheetPr>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15.050000000000001" customHeight="1"/>
-  <cols>
-    <col customWidth="1" min="1" max="1" style="34" width="3.8164099999999999"/>
-    <col customWidth="1" min="2" max="2" style="34" width="19.726600000000001"/>
-    <col customWidth="1" min="3" max="3" style="34" width="12.363300000000001"/>
-    <col customWidth="1" min="4" max="4" style="34" width="18"/>
-    <col customWidth="1" min="5" max="5" style="34" width="17"/>
-    <col customWidth="1" min="6" max="6" style="34" width="8.7265599999999992"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="30">
-      <c r="A1" s="35" t="s">
-        <v>91</v>
-      </c>
-      <c r="B1" s="35" t="s">
-        <v>127</v>
-      </c>
-      <c r="C1" s="35" t="s">
-        <v>128</v>
-      </c>
-      <c r="D1" s="35" t="s">
-        <v>129</v>
-      </c>
-      <c r="E1" s="35" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="2" ht="45">
-      <c r="A2" s="36" t="s">
-        <v>91</v>
-      </c>
-      <c r="B2" s="36" t="s">
-        <v>127</v>
-      </c>
-      <c r="C2" s="36" t="s">
-        <v>128</v>
-      </c>
-      <c r="D2" s="36" t="s">
-        <v>129</v>
-      </c>
-      <c r="E2" s="36" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="3" ht="15.65">
-      <c r="A3" s="30">
-        <v>1</v>
-      </c>
-      <c r="B3" s="30" t="s">
-        <v>131</v>
-      </c>
-      <c r="C3" s="30">
-        <v>1</v>
-      </c>
-      <c r="D3" s="30">
-        <v>100</v>
-      </c>
-      <c r="E3" s="37">
-        <v>2.5</v>
-      </c>
-    </row>
-    <row r="4" ht="15.65">
-      <c r="A4" s="31">
-        <v>2</v>
-      </c>
-      <c r="B4" s="31" t="s">
-        <v>132</v>
-      </c>
-      <c r="C4" s="31">
-        <v>1</v>
-      </c>
-      <c r="D4" s="31">
-        <v>90</v>
-      </c>
-      <c r="E4" s="38">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" ht="15.65">
-      <c r="A5" s="31">
-        <v>3</v>
-      </c>
-      <c r="B5" s="31" t="s">
-        <v>133</v>
-      </c>
-      <c r="C5" s="31">
-        <v>1</v>
-      </c>
-      <c r="D5" s="31">
-        <v>140</v>
-      </c>
-      <c r="E5" s="38">
-        <v>1.5</v>
-      </c>
-    </row>
-    <row r="6" ht="15.65">
-      <c r="A6" s="31">
-        <v>4</v>
-      </c>
-      <c r="B6" s="31" t="s">
-        <v>134</v>
-      </c>
-      <c r="C6" s="31">
-        <v>1</v>
-      </c>
-      <c r="D6" s="31">
-        <v>130</v>
-      </c>
-      <c r="E6" s="38">
-        <v>1.5</v>
-      </c>
-    </row>
-    <row r="7" ht="15.65">
-      <c r="A7" s="31">
-        <v>5</v>
-      </c>
-      <c r="B7" s="31" t="s">
-        <v>135</v>
-      </c>
-      <c r="C7" s="31">
-        <v>1</v>
-      </c>
-      <c r="D7" s="31">
-        <v>160</v>
-      </c>
-      <c r="E7" s="38">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="8" ht="15.65">
-      <c r="A8" s="31">
-        <v>6</v>
-      </c>
-      <c r="B8" s="31" t="s">
-        <v>136</v>
-      </c>
-      <c r="C8" s="31">
-        <v>1</v>
-      </c>
-      <c r="D8" s="31">
-        <v>100</v>
-      </c>
-      <c r="E8" s="38">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="9" ht="15.65">
-      <c r="A9" s="32">
-        <v>7</v>
-      </c>
-      <c r="B9" s="32" t="s">
-        <v>137</v>
-      </c>
-      <c r="C9" s="32">
-        <v>1</v>
-      </c>
-      <c r="D9" s="32">
-        <v>90</v>
-      </c>
-      <c r="E9" s="39">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="10" ht="15.65">
-      <c r="A10" s="33"/>
-      <c r="B10" s="33"/>
-      <c r="C10" s="33"/>
-      <c r="D10" s="33"/>
-      <c r="E10" s="33"/>
-    </row>
-    <row r="11" ht="15.65">
-      <c r="A11" s="40"/>
-      <c r="B11" s="40"/>
-      <c r="C11" s="40"/>
-      <c r="D11" s="40"/>
-      <c r="E11" s="40"/>
-    </row>
-    <row r="12" ht="15.65">
-      <c r="A12" s="40"/>
-      <c r="B12" s="40"/>
-      <c r="C12" s="40"/>
-      <c r="D12" s="40"/>
-      <c r="E12" s="40"/>
-    </row>
-    <row r="13" ht="15.65">
-      <c r="A13" s="40"/>
-      <c r="B13" s="40"/>
-      <c r="C13" s="40"/>
-      <c r="D13" s="40"/>
-      <c r="E13" s="40"/>
-    </row>
-    <row r="14" ht="15.65">
-      <c r="A14" s="40"/>
-      <c r="B14" s="40"/>
-      <c r="C14" s="40"/>
-      <c r="D14" s="40"/>
-      <c r="E14" s="40"/>
-    </row>
-    <row r="15" ht="15.65">
-      <c r="A15" s="40"/>
-      <c r="B15" s="40"/>
-      <c r="C15" s="40"/>
-      <c r="D15" s="40"/>
-      <c r="E15" s="40"/>
-    </row>
-    <row r="16" ht="15.65">
-      <c r="A16" s="40"/>
-      <c r="B16" s="40"/>
-      <c r="C16" s="40"/>
-      <c r="D16" s="40"/>
-      <c r="E16" s="40"/>
-    </row>
-    <row r="17" ht="15.65">
-      <c r="A17" s="40"/>
-      <c r="B17" s="40"/>
-      <c r="C17" s="40"/>
-      <c r="D17" s="40"/>
-      <c r="E17" s="40"/>
-    </row>
-    <row r="18" ht="15.65">
-      <c r="A18" s="40"/>
-      <c r="B18" s="40"/>
-      <c r="C18" s="40"/>
-      <c r="D18" s="40"/>
-      <c r="E18" s="40"/>
-    </row>
-    <row r="19" ht="15.65">
-      <c r="A19" s="40"/>
-      <c r="B19" s="40"/>
-      <c r="C19" s="40"/>
-      <c r="D19" s="40"/>
-      <c r="E19" s="40"/>
-    </row>
-    <row r="20" ht="15.65">
-      <c r="A20" s="40"/>
-      <c r="B20" s="40"/>
-      <c r="C20" s="40"/>
-      <c r="D20" s="40"/>
-      <c r="E20" s="40"/>
-    </row>
-    <row r="21" ht="15.65">
-      <c r="A21" s="40"/>
-      <c r="B21" s="40"/>
-      <c r="C21" s="40"/>
-      <c r="D21" s="40"/>
-      <c r="E21" s="40"/>
-    </row>
-    <row r="22" ht="15.65">
-      <c r="A22" s="40"/>
-      <c r="B22" s="40"/>
-      <c r="C22" s="40"/>
-      <c r="D22" s="40"/>
-      <c r="E22" s="40"/>
-    </row>
-    <row r="23" ht="15.65">
-      <c r="A23" s="40"/>
-      <c r="B23" s="40"/>
-      <c r="C23" s="40"/>
-      <c r="D23" s="40"/>
-      <c r="E23" s="40"/>
-    </row>
-  </sheetData>
-  <printOptions headings="0" gridLines="0"/>
-  <pageMargins left="0.69999999999999996" right="0.69999999999999996" top="0.75" bottom="0.75" header="0.29999999999999999" footer="0.29999999999999999"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" cellComments="none" useFirstPageNumber="0" errors="displayed" horizontalDpi="600" verticalDpi="600" copies="1"/>
-  <headerFooter/>
-  <legacyDrawing r:id="rId3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
-  <sheetPr>
-    <outlinePr applyStyles="0" summaryBelow="1" summaryRight="1" showOutlineSymbols="1"/>
-    <pageSetUpPr autoPageBreaks="1" fitToPage="0"/>
-  </sheetPr>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15.050000000000001" customHeight="1"/>
-  <cols>
-    <col customWidth="1" min="1" max="1" width="5.5429700000000004"/>
-    <col customWidth="1" min="2" max="2" width="27.453099999999999"/>
-    <col customWidth="1" min="3" max="4" width="18.542999999999999"/>
-    <col customWidth="1" min="5" max="5" width="22.1797"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="52" customHeight="1">
-      <c r="A1" s="41" t="s">
-        <v>138</v>
-      </c>
-      <c r="B1" s="41"/>
-      <c r="C1" s="41"/>
-      <c r="D1" s="41"/>
-      <c r="E1" s="41"/>
-    </row>
-    <row r="2" ht="52.600000000000001" customHeight="1">
-      <c r="A2" s="36" t="s">
-        <v>91</v>
-      </c>
-      <c r="B2" s="36" t="s">
-        <v>139</v>
-      </c>
-      <c r="C2" s="36" t="s">
-        <v>140</v>
-      </c>
-      <c r="D2" s="36" t="s">
-        <v>141</v>
-      </c>
-      <c r="E2" s="42" t="s">
-        <v>142</v>
-      </c>
-      <c r="F2" s="34"/>
-    </row>
-    <row r="3" ht="30">
-      <c r="A3" s="43">
-        <v>1</v>
-      </c>
-      <c r="B3" s="43" t="s">
-        <v>143</v>
-      </c>
-      <c r="C3" s="43">
-        <v>1</v>
-      </c>
-      <c r="D3" s="43">
-        <v>120000</v>
-      </c>
-      <c r="E3" s="31">
-        <v>144000</v>
-      </c>
-      <c r="F3" s="34"/>
-    </row>
-    <row r="4" ht="15.65">
-      <c r="A4" s="31">
-        <v>2</v>
-      </c>
-      <c r="B4" s="31" t="s">
-        <v>144</v>
-      </c>
-      <c r="C4" s="31">
-        <v>2</v>
-      </c>
-      <c r="D4" s="31">
-        <v>80000</v>
-      </c>
-      <c r="E4" s="31">
-        <v>192000</v>
-      </c>
-      <c r="F4" s="34"/>
-    </row>
-    <row r="5" ht="15.65">
-      <c r="A5" s="31">
-        <v>3</v>
-      </c>
-      <c r="B5" s="31" t="s">
-        <v>145</v>
-      </c>
-      <c r="C5" s="31" t="s">
-        <v>146</v>
-      </c>
-      <c r="D5" s="31">
-        <v>25000</v>
-      </c>
-      <c r="E5" s="31">
-        <v>60000</v>
-      </c>
-      <c r="F5" s="34"/>
-    </row>
-    <row r="6" ht="15.65">
-      <c r="A6" s="31">
-        <v>4</v>
-      </c>
-      <c r="B6" s="31" t="s">
-        <v>147</v>
-      </c>
-      <c r="C6" s="31" t="s">
-        <v>148</v>
-      </c>
-      <c r="D6" s="31">
-        <v>5000</v>
-      </c>
-      <c r="E6" s="31">
-        <v>18000</v>
-      </c>
-      <c r="F6" s="34"/>
-    </row>
-    <row r="7" ht="15.65">
-      <c r="A7" s="31">
-        <v>5</v>
-      </c>
-      <c r="B7" s="31" t="s">
-        <v>149</v>
-      </c>
-      <c r="C7" s="31" t="s">
-        <v>148</v>
-      </c>
-      <c r="D7" s="31">
-        <v>3000</v>
-      </c>
-      <c r="E7" s="31">
-        <v>10800</v>
-      </c>
-      <c r="F7" s="34"/>
-    </row>
-    <row r="8" ht="15.65">
-      <c r="A8" s="31">
-        <v>6</v>
-      </c>
-      <c r="B8" s="31" t="s">
-        <v>150</v>
-      </c>
-      <c r="C8" s="31">
-        <v>1</v>
-      </c>
-      <c r="D8" s="31">
-        <v>3000</v>
-      </c>
-      <c r="E8" s="31">
-        <v>3600</v>
-      </c>
-      <c r="F8" s="34"/>
-    </row>
-    <row r="9" ht="15.65">
-      <c r="A9" s="31">
-        <v>7</v>
-      </c>
-      <c r="B9" s="31" t="s">
-        <v>151</v>
-      </c>
-      <c r="C9" s="31">
-        <v>1</v>
-      </c>
-      <c r="D9" s="31">
-        <v>5000</v>
-      </c>
-      <c r="E9" s="31">
-        <v>6000</v>
-      </c>
-      <c r="F9" s="34"/>
-    </row>
-    <row r="10" ht="15.65">
-      <c r="A10" s="32">
-        <v>8</v>
-      </c>
-      <c r="B10" s="32" t="s">
-        <v>152</v>
-      </c>
-      <c r="C10" s="32">
-        <v>1</v>
-      </c>
-      <c r="D10" s="32">
-        <v>10000</v>
-      </c>
-      <c r="E10" s="32">
-        <v>12000</v>
-      </c>
-      <c r="F10" s="34"/>
-    </row>
-    <row r="11" ht="15.65">
-      <c r="A11" s="44" t="s">
-        <v>153</v>
-      </c>
-      <c r="B11" s="45"/>
-      <c r="C11" s="45"/>
-      <c r="D11" s="46"/>
-      <c r="E11" s="33">
-        <f>SUM(E3:E10)</f>
-        <v>446400</v>
-      </c>
-      <c r="F11" s="34"/>
-    </row>
-    <row r="12" ht="15.65">
-      <c r="A12" s="47"/>
-      <c r="B12" s="48"/>
-      <c r="C12" s="48"/>
-      <c r="D12" s="49"/>
-      <c r="E12" s="50"/>
-      <c r="F12" s="34"/>
-    </row>
-    <row r="13" ht="15.050000000000001">
-      <c r="A13" s="34"/>
-      <c r="B13" s="34"/>
-      <c r="C13" s="34"/>
-      <c r="D13" s="34"/>
-      <c r="E13" s="34"/>
-      <c r="F13" s="34"/>
-    </row>
-    <row r="14" ht="15.050000000000001">
-      <c r="A14" s="34"/>
-      <c r="B14" s="34"/>
-      <c r="C14" s="34"/>
-      <c r="D14" s="34"/>
-      <c r="E14" s="34"/>
-      <c r="F14" s="34"/>
-    </row>
-    <row r="15" ht="15.050000000000001">
-      <c r="A15" s="34"/>
-      <c r="B15" s="34"/>
-      <c r="C15" s="34"/>
-      <c r="D15" s="34"/>
-      <c r="E15" s="34"/>
-      <c r="F15" s="34"/>
-    </row>
-  </sheetData>
-  <mergeCells count="3">
-    <mergeCell ref="A1:E1"/>
-    <mergeCell ref="A11:D11"/>
-    <mergeCell ref="A12:D12"/>
-  </mergeCells>
-  <printOptions headings="0" gridLines="0"/>
-  <pageMargins left="0.69999999999999996" right="0.69999999999999996" top="0.75" bottom="0.75" header="0.29999999999999999" footer="0.29999999999999999"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" cellComments="none" useFirstPageNumber="0" errors="displayed" horizontalDpi="600" verticalDpi="600" copies="1"/>
-  <headerFooter/>
-  <legacyDrawing r:id="rId3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
   <sheetPr>
     <outlinePr applyStyles="0" summaryBelow="1" summaryRight="1" showOutlineSymbols="1"/>
     <pageSetUpPr autoPageBreaks="1" fitToPage="1"/>
   </sheetPr>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.90625" defaultRowHeight="15.65" customHeight="1"/>
   <cols>
-    <col customWidth="1" min="1" max="1" style="51" width="8.90625"/>
-    <col customWidth="1" min="2" max="2" style="51" width="26.906199999999998"/>
-    <col customWidth="1" min="3" max="3" style="51" width="27.453099999999999"/>
-    <col customWidth="1" min="4" max="4" style="51" width="16.453099999999999"/>
-    <col customWidth="1" min="5" max="5" style="51" width="19.542999999999999"/>
-    <col customWidth="1" min="6" max="6" style="51" width="16.453099999999999"/>
-    <col customWidth="1" min="7" max="7" style="51" width="27.6328"/>
-    <col customWidth="1" min="8" max="8" style="51" width="23.6328"/>
-    <col bestFit="1" customWidth="1" min="9" max="9" style="51" width="19.453099999999999"/>
-    <col customWidth="1" min="10" max="10" style="51" width="13.363300000000001"/>
-    <col customWidth="1" min="11" max="11" style="51" width="2.8164099999999999"/>
-    <col customWidth="1" min="12" max="257" style="51" width="8.90625"/>
+    <col customWidth="1" min="1" max="1" style="71" width="8.90625"/>
+    <col customWidth="1" min="2" max="2" style="71" width="26.906199999999998"/>
+    <col customWidth="1" min="3" max="3" style="71" width="27.453099999999999"/>
+    <col customWidth="1" min="4" max="4" style="71" width="16.453099999999999"/>
+    <col customWidth="1" min="5" max="5" style="71" width="19.542999999999999"/>
+    <col customWidth="1" min="6" max="6" style="71" width="16.453099999999999"/>
+    <col customWidth="1" min="7" max="7" style="71" width="27.6328"/>
+    <col customWidth="1" min="8" max="8" style="71" width="23.6328"/>
+    <col bestFit="1" customWidth="1" min="9" max="9" style="71" width="19.453099999999999"/>
+    <col customWidth="1" min="10" max="10" style="71" width="13.363300000000001"/>
+    <col customWidth="1" min="11" max="11" style="71" width="2.8164099999999999"/>
+    <col customWidth="1" min="12" max="257" style="71" width="8.90625"/>
   </cols>
   <sheetData>
     <row r="1" ht="15.65">
-      <c r="A1" s="52"/>
-      <c r="B1" s="52"/>
-      <c r="C1" s="52"/>
-      <c r="D1" s="52"/>
-      <c r="E1" s="52"/>
-      <c r="F1" s="52"/>
-      <c r="G1" s="52"/>
-      <c r="H1" s="52"/>
-      <c r="I1" s="53" t="s">
-        <v>154</v>
+      <c r="A1" s="72"/>
+      <c r="B1" s="72"/>
+      <c r="C1" s="72"/>
+      <c r="D1" s="72"/>
+      <c r="E1" s="72"/>
+      <c r="F1" s="72"/>
+      <c r="G1" s="72"/>
+      <c r="H1" s="72"/>
+      <c r="I1" s="73" t="s">
+        <v>178</v>
       </c>
     </row>
     <row r="2" ht="15.65" customHeight="1">
-      <c r="A2" s="52"/>
-      <c r="B2" s="52"/>
-      <c r="C2" s="52"/>
-      <c r="D2" s="52"/>
-      <c r="E2" s="52"/>
-      <c r="F2" s="52"/>
-      <c r="G2" s="52"/>
-      <c r="H2" s="52"/>
-      <c r="I2" s="52"/>
+      <c r="A2" s="72"/>
+      <c r="B2" s="72"/>
+      <c r="C2" s="72"/>
+      <c r="D2" s="72"/>
+      <c r="E2" s="72"/>
+      <c r="F2" s="72"/>
+      <c r="G2" s="72"/>
+      <c r="H2" s="72"/>
+      <c r="I2" s="72"/>
     </row>
     <row r="3" ht="15.65">
-      <c r="A3" s="54" t="s">
-        <v>155</v>
-      </c>
-      <c r="B3" s="54"/>
-      <c r="C3" s="54"/>
-      <c r="D3" s="54"/>
-      <c r="E3" s="54"/>
-      <c r="F3" s="54"/>
-      <c r="G3" s="54"/>
-      <c r="H3" s="54"/>
-      <c r="I3" s="54"/>
-      <c r="J3" s="55"/>
+      <c r="A3" s="74" t="s">
+        <v>179</v>
+      </c>
+      <c r="B3" s="74"/>
+      <c r="C3" s="74"/>
+      <c r="D3" s="74"/>
+      <c r="E3" s="74"/>
+      <c r="F3" s="74"/>
+      <c r="G3" s="74"/>
+      <c r="H3" s="74"/>
+      <c r="I3" s="74"/>
+      <c r="J3" s="75"/>
     </row>
     <row r="4" ht="31.5" customHeight="1">
-      <c r="A4" s="56" t="s">
-        <v>156</v>
-      </c>
-      <c r="B4" s="56"/>
-      <c r="C4" s="56"/>
-      <c r="D4" s="56"/>
-      <c r="E4" s="56"/>
-      <c r="F4" s="56"/>
-      <c r="G4" s="56"/>
-      <c r="H4" s="56"/>
-      <c r="I4" s="56"/>
-      <c r="J4" s="55"/>
+      <c r="A4" s="76" t="s">
+        <v>180</v>
+      </c>
+      <c r="B4" s="76"/>
+      <c r="C4" s="76"/>
+      <c r="D4" s="76"/>
+      <c r="E4" s="76"/>
+      <c r="F4" s="76"/>
+      <c r="G4" s="76"/>
+      <c r="H4" s="76"/>
+      <c r="I4" s="76"/>
+      <c r="J4" s="75"/>
     </row>
     <row r="5" ht="15.65">
-      <c r="A5" s="57" t="s">
-        <v>157</v>
-      </c>
-      <c r="B5" s="57"/>
-      <c r="C5" s="57"/>
-      <c r="D5" s="57"/>
-      <c r="E5" s="57"/>
-      <c r="F5" s="57"/>
-      <c r="G5" s="57"/>
-      <c r="H5" s="57"/>
-      <c r="I5" s="57"/>
-      <c r="J5" s="55"/>
+      <c r="A5" s="77" t="s">
+        <v>181</v>
+      </c>
+      <c r="B5" s="77"/>
+      <c r="C5" s="77"/>
+      <c r="D5" s="77"/>
+      <c r="E5" s="77"/>
+      <c r="F5" s="77"/>
+      <c r="G5" s="77"/>
+      <c r="H5" s="77"/>
+      <c r="I5" s="77"/>
+      <c r="J5" s="75"/>
     </row>
     <row r="6" ht="16.300000000000001">
-      <c r="A6" s="58"/>
-      <c r="B6" s="58"/>
-      <c r="C6" s="58"/>
-      <c r="D6" s="58"/>
-      <c r="E6" s="58"/>
-      <c r="F6" s="58"/>
-      <c r="G6" s="58"/>
-      <c r="H6" s="58"/>
-      <c r="I6" s="58"/>
-    </row>
-    <row r="7" s="59" customFormat="1" ht="43.549999999999997" customHeight="1">
-      <c r="A7" s="60" t="s">
-        <v>158</v>
-      </c>
-      <c r="B7" s="60" t="s">
-        <v>159</v>
-      </c>
-      <c r="C7" s="61" t="s">
-        <v>160</v>
-      </c>
-      <c r="D7" s="62"/>
-      <c r="E7" s="61" t="s">
-        <v>161</v>
-      </c>
-      <c r="F7" s="62"/>
-      <c r="G7" s="60" t="s">
-        <v>162</v>
-      </c>
-      <c r="H7" s="60" t="s">
-        <v>163</v>
-      </c>
-      <c r="I7" s="60" t="s">
-        <v>164</v>
-      </c>
-      <c r="J7" s="63"/>
-    </row>
-    <row r="8" s="59" customFormat="1" ht="43.549999999999997" customHeight="1">
-      <c r="A8" s="64"/>
-      <c r="B8" s="64"/>
-      <c r="C8" s="64" t="s">
+      <c r="A6" s="78"/>
+      <c r="B6" s="78"/>
+      <c r="C6" s="78"/>
+      <c r="D6" s="78"/>
+      <c r="E6" s="78"/>
+      <c r="F6" s="78"/>
+      <c r="G6" s="78"/>
+      <c r="H6" s="78"/>
+      <c r="I6" s="78"/>
+    </row>
+    <row r="7" s="79" customFormat="1" ht="43.549999999999997" customHeight="1">
+      <c r="A7" s="80" t="s">
+        <v>182</v>
+      </c>
+      <c r="B7" s="80" t="s">
+        <v>183</v>
+      </c>
+      <c r="C7" s="81" t="s">
+        <v>184</v>
+      </c>
+      <c r="D7" s="82"/>
+      <c r="E7" s="81" t="s">
+        <v>185</v>
+      </c>
+      <c r="F7" s="82"/>
+      <c r="G7" s="80" t="s">
+        <v>186</v>
+      </c>
+      <c r="H7" s="80" t="s">
+        <v>187</v>
+      </c>
+      <c r="I7" s="80" t="s">
+        <v>188</v>
+      </c>
+      <c r="J7" s="83"/>
+    </row>
+    <row r="8" s="79" customFormat="1" ht="43.549999999999997" customHeight="1">
+      <c r="A8" s="84"/>
+      <c r="B8" s="84"/>
+      <c r="C8" s="84" t="s">
         <v>127</v>
       </c>
-      <c r="D8" s="64" t="s">
-        <v>165</v>
-      </c>
-      <c r="E8" s="64" t="s">
-        <v>166</v>
-      </c>
-      <c r="F8" s="64" t="s">
-        <v>167</v>
-      </c>
-      <c r="G8" s="64"/>
-      <c r="H8" s="64"/>
-      <c r="I8" s="64"/>
-      <c r="J8" s="63"/>
+      <c r="D8" s="84" t="s">
+        <v>189</v>
+      </c>
+      <c r="E8" s="84" t="s">
+        <v>190</v>
+      </c>
+      <c r="F8" s="84" t="s">
+        <v>191</v>
+      </c>
+      <c r="G8" s="84"/>
+      <c r="H8" s="84"/>
+      <c r="I8" s="84"/>
+      <c r="J8" s="83"/>
     </row>
     <row r="9" ht="16.300000000000001">
-      <c r="A9" s="65">
+      <c r="A9" s="85">
         <v>1</v>
       </c>
-      <c r="B9" s="66"/>
-      <c r="C9" s="66">
+      <c r="B9" s="86"/>
+      <c r="C9" s="86">
         <v>2</v>
       </c>
-      <c r="D9" s="66">
+      <c r="D9" s="86">
         <v>3</v>
       </c>
-      <c r="E9" s="66">
+      <c r="E9" s="86">
         <v>4</v>
       </c>
-      <c r="F9" s="66">
+      <c r="F9" s="86">
         <v>5</v>
       </c>
-      <c r="G9" s="66">
+      <c r="G9" s="86">
         <v>6</v>
       </c>
-      <c r="H9" s="66">
+      <c r="H9" s="86">
         <v>7</v>
       </c>
-      <c r="I9" s="67" t="s">
-        <v>168</v>
-      </c>
-      <c r="J9" s="68"/>
+      <c r="I9" s="87" t="s">
+        <v>192</v>
+      </c>
+      <c r="J9" s="88"/>
     </row>
     <row r="10" ht="47.450000000000003" customHeight="1">
-      <c r="A10" s="69">
+      <c r="A10" s="89">
         <v>1</v>
       </c>
-      <c r="B10" s="70" t="s">
-        <v>169</v>
-      </c>
-      <c r="C10" s="69" t="s">
-        <v>131</v>
-      </c>
-      <c r="D10" s="69">
+      <c r="B10" s="90" t="s">
+        <v>193</v>
+      </c>
+      <c r="C10" s="89" t="s">
+        <v>134</v>
+      </c>
+      <c r="D10" s="89">
         <v>1</v>
       </c>
-      <c r="E10" s="71">
+      <c r="E10" s="91">
         <v>46063</v>
       </c>
-      <c r="F10" s="72">
+      <c r="F10" s="92">
         <v>46139</v>
       </c>
-      <c r="G10" s="69">
+      <c r="G10" s="89">
         <v>440</v>
       </c>
-      <c r="H10" s="69">
+      <c r="H10" s="89">
         <v>568</v>
       </c>
-      <c r="I10" s="73">
+      <c r="I10" s="93">
         <f t="shared" ref="I10:I16" si="0">G10*H10</f>
         <v>249920</v>
       </c>
-      <c r="J10" s="68"/>
-      <c r="O10" s="51"/>
-      <c r="P10" s="51"/>
-      <c r="Q10" s="51"/>
+      <c r="J10" s="88"/>
+      <c r="O10" s="71"/>
+      <c r="P10" s="71"/>
+      <c r="Q10" s="71"/>
     </row>
     <row r="11" ht="30">
-      <c r="A11" s="69">
+      <c r="A11" s="89">
         <v>2</v>
       </c>
-      <c r="B11" s="74"/>
-      <c r="C11" s="69" t="s">
-        <v>132</v>
-      </c>
-      <c r="D11" s="69">
+      <c r="B11" s="94"/>
+      <c r="C11" s="89" t="s">
+        <v>138</v>
+      </c>
+      <c r="D11" s="89">
         <v>1</v>
       </c>
-      <c r="E11" s="71">
+      <c r="E11" s="91">
         <v>46063</v>
       </c>
-      <c r="F11" s="72">
+      <c r="F11" s="92">
         <v>46090</v>
       </c>
-      <c r="G11" s="69">
+      <c r="G11" s="89">
         <v>176</v>
       </c>
-      <c r="H11" s="69">
+      <c r="H11" s="89">
         <v>511</v>
       </c>
-      <c r="I11" s="73">
+      <c r="I11" s="93">
         <f t="shared" si="0"/>
         <v>89936</v>
       </c>
-      <c r="J11" s="75"/>
-      <c r="O11" s="51"/>
-      <c r="P11" s="51"/>
-      <c r="Q11" s="51"/>
+      <c r="J11" s="95"/>
+      <c r="O11" s="71"/>
+      <c r="P11" s="71"/>
+      <c r="Q11" s="71"/>
     </row>
     <row r="12" ht="16.300000000000001">
-      <c r="A12" s="69">
+      <c r="A12" s="89">
         <v>3</v>
       </c>
-      <c r="B12" s="74"/>
-      <c r="C12" s="69" t="s">
-        <v>133</v>
-      </c>
-      <c r="D12" s="69">
+      <c r="B12" s="94"/>
+      <c r="C12" s="89" t="s">
+        <v>140</v>
+      </c>
+      <c r="D12" s="89">
         <v>1</v>
       </c>
-      <c r="E12" s="71">
+      <c r="E12" s="91">
         <v>46091</v>
       </c>
-      <c r="F12" s="72">
+      <c r="F12" s="92">
         <v>46135</v>
       </c>
-      <c r="G12" s="69">
+      <c r="G12" s="89">
         <v>264</v>
       </c>
-      <c r="H12" s="69">
+      <c r="H12" s="89">
         <v>795</v>
       </c>
-      <c r="I12" s="73">
+      <c r="I12" s="93">
         <f t="shared" si="0"/>
         <v>209880</v>
       </c>
-      <c r="J12" s="75"/>
-      <c r="O12" s="51"/>
-      <c r="P12" s="51"/>
-      <c r="Q12" s="51"/>
+      <c r="J12" s="95"/>
+      <c r="O12" s="71"/>
+      <c r="P12" s="71"/>
+      <c r="Q12" s="71"/>
     </row>
     <row r="13" ht="16.300000000000001">
-      <c r="A13" s="69">
+      <c r="A13" s="89">
         <v>4</v>
       </c>
-      <c r="B13" s="74"/>
-      <c r="C13" s="69" t="s">
-        <v>134</v>
-      </c>
-      <c r="D13" s="69">
+      <c r="B13" s="94"/>
+      <c r="C13" s="89" t="s">
+        <v>142</v>
+      </c>
+      <c r="D13" s="89">
         <v>1</v>
       </c>
-      <c r="E13" s="71">
+      <c r="E13" s="91">
         <v>46091</v>
       </c>
-      <c r="F13" s="72">
+      <c r="F13" s="92">
         <v>46135</v>
       </c>
-      <c r="G13" s="76">
+      <c r="G13" s="96">
         <v>264</v>
       </c>
-      <c r="H13" s="69">
+      <c r="H13" s="89">
         <v>739</v>
       </c>
-      <c r="I13" s="73">
+      <c r="I13" s="93">
         <f t="shared" si="0"/>
         <v>195096</v>
       </c>
-      <c r="J13" s="75"/>
-      <c r="O13" s="51"/>
-      <c r="P13" s="51"/>
-      <c r="Q13" s="51"/>
+      <c r="J13" s="95"/>
+      <c r="O13" s="71"/>
+      <c r="P13" s="71"/>
+      <c r="Q13" s="71"/>
     </row>
     <row r="14" ht="16.300000000000001">
-      <c r="A14" s="69">
+      <c r="A14" s="89">
         <v>5</v>
       </c>
-      <c r="B14" s="74"/>
-      <c r="C14" s="69" t="s">
-        <v>135</v>
-      </c>
-      <c r="D14" s="69">
+      <c r="B14" s="94"/>
+      <c r="C14" s="89" t="s">
+        <v>144</v>
+      </c>
+      <c r="D14" s="89">
         <v>1</v>
       </c>
-      <c r="E14" s="71">
+      <c r="E14" s="91">
         <v>46077</v>
       </c>
-      <c r="F14" s="72">
+      <c r="F14" s="92">
         <v>46139</v>
       </c>
-      <c r="G14" s="76">
+      <c r="G14" s="96">
         <v>352</v>
       </c>
-      <c r="H14" s="69">
+      <c r="H14" s="89">
         <v>909</v>
       </c>
-      <c r="I14" s="73">
+      <c r="I14" s="93">
         <f t="shared" si="0"/>
         <v>319968</v>
       </c>
-      <c r="J14" s="75"/>
-      <c r="K14" s="51"/>
-      <c r="O14" s="51"/>
-      <c r="P14" s="51"/>
-      <c r="Q14" s="51"/>
+      <c r="J14" s="95"/>
+      <c r="K14" s="71"/>
+      <c r="O14" s="71"/>
+      <c r="P14" s="71"/>
+      <c r="Q14" s="71"/>
     </row>
     <row r="15" ht="16.300000000000001">
-      <c r="A15" s="69">
+      <c r="A15" s="89">
         <v>6</v>
       </c>
-      <c r="B15" s="74"/>
-      <c r="C15" s="69" t="s">
-        <v>136</v>
-      </c>
-      <c r="D15" s="69">
+      <c r="B15" s="94"/>
+      <c r="C15" s="89" t="s">
+        <v>146</v>
+      </c>
+      <c r="D15" s="89">
         <v>1</v>
       </c>
-      <c r="E15" s="71">
+      <c r="E15" s="91">
         <v>46077</v>
       </c>
-      <c r="F15" s="72">
+      <c r="F15" s="92">
         <v>46104</v>
       </c>
-      <c r="G15" s="76">
+      <c r="G15" s="96">
         <v>176</v>
       </c>
-      <c r="H15" s="69">
+      <c r="H15" s="89">
         <v>568</v>
       </c>
-      <c r="I15" s="73">
+      <c r="I15" s="93">
         <f t="shared" si="0"/>
         <v>99968</v>
       </c>
-      <c r="J15" s="75"/>
-      <c r="K15" s="51"/>
-      <c r="O15" s="51"/>
-      <c r="P15" s="51"/>
-      <c r="Q15" s="51"/>
+      <c r="J15" s="95"/>
+      <c r="K15" s="71"/>
+      <c r="O15" s="71"/>
+      <c r="P15" s="71"/>
+      <c r="Q15" s="71"/>
     </row>
     <row r="16" ht="16.300000000000001">
-      <c r="A16" s="69">
+      <c r="A16" s="89">
         <v>7</v>
       </c>
-      <c r="B16" s="77"/>
-      <c r="C16" s="69" t="s">
-        <v>137</v>
-      </c>
-      <c r="D16" s="69">
+      <c r="B16" s="97"/>
+      <c r="C16" s="89" t="s">
+        <v>148</v>
+      </c>
+      <c r="D16" s="89">
         <v>1</v>
       </c>
-      <c r="E16" s="71">
+      <c r="E16" s="91">
         <v>46112</v>
       </c>
-      <c r="F16" s="72">
+      <c r="F16" s="92">
         <v>46139</v>
       </c>
-      <c r="G16" s="76">
+      <c r="G16" s="96">
         <v>176</v>
       </c>
-      <c r="H16" s="69">
+      <c r="H16" s="89">
         <v>511</v>
       </c>
-      <c r="I16" s="73">
+      <c r="I16" s="93">
         <f t="shared" si="0"/>
         <v>89936</v>
       </c>
-      <c r="J16" s="75"/>
-      <c r="K16" s="78"/>
-      <c r="O16" s="51"/>
-      <c r="P16" s="51"/>
-      <c r="Q16" s="51"/>
+      <c r="J16" s="95"/>
+      <c r="K16" s="98"/>
+      <c r="O16" s="71"/>
+      <c r="P16" s="71"/>
+      <c r="Q16" s="71"/>
     </row>
     <row r="17" ht="16.300000000000001">
-      <c r="A17" s="79"/>
-      <c r="B17" s="80"/>
-      <c r="C17" s="74"/>
-      <c r="D17" s="74"/>
-      <c r="E17" s="81"/>
-      <c r="F17" s="82"/>
-      <c r="G17" s="83"/>
-      <c r="H17" s="74"/>
-      <c r="I17" s="84">
+      <c r="A17" s="99"/>
+      <c r="B17" s="100"/>
+      <c r="C17" s="94"/>
+      <c r="D17" s="94"/>
+      <c r="E17" s="101"/>
+      <c r="F17" s="102"/>
+      <c r="G17" s="103"/>
+      <c r="H17" s="94"/>
+      <c r="I17" s="104">
         <f t="shared" ref="I17:I21" si="1">D17*G17*H17</f>
         <v>0</v>
       </c>
-      <c r="J17" s="75"/>
-      <c r="K17" s="78"/>
-      <c r="O17" s="51"/>
-      <c r="P17" s="51"/>
-      <c r="Q17" s="51"/>
+      <c r="J17" s="95"/>
+      <c r="K17" s="98"/>
+      <c r="O17" s="71"/>
+      <c r="P17" s="71"/>
+      <c r="Q17" s="71"/>
     </row>
     <row r="18" ht="16.300000000000001">
-      <c r="A18" s="79"/>
-      <c r="B18" s="80"/>
-      <c r="C18" s="74"/>
-      <c r="D18" s="74"/>
-      <c r="E18" s="85"/>
-      <c r="F18" s="82"/>
-      <c r="G18" s="83"/>
-      <c r="H18" s="74"/>
-      <c r="I18" s="84">
+      <c r="A18" s="99"/>
+      <c r="B18" s="100"/>
+      <c r="C18" s="94"/>
+      <c r="D18" s="94"/>
+      <c r="E18" s="105"/>
+      <c r="F18" s="102"/>
+      <c r="G18" s="103"/>
+      <c r="H18" s="94"/>
+      <c r="I18" s="104">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="J18" s="75"/>
-      <c r="K18" s="78"/>
-      <c r="O18" s="51"/>
-      <c r="P18" s="51"/>
-      <c r="Q18" s="51"/>
+      <c r="J18" s="95"/>
+      <c r="K18" s="98"/>
+      <c r="O18" s="71"/>
+      <c r="P18" s="71"/>
+      <c r="Q18" s="71"/>
     </row>
     <row r="19" ht="16.300000000000001">
-      <c r="A19" s="79"/>
-      <c r="B19" s="80"/>
-      <c r="C19" s="74"/>
-      <c r="D19" s="74"/>
-      <c r="E19" s="85"/>
-      <c r="F19" s="82"/>
-      <c r="G19" s="83"/>
-      <c r="H19" s="74"/>
-      <c r="I19" s="84">
+      <c r="A19" s="99"/>
+      <c r="B19" s="100"/>
+      <c r="C19" s="94"/>
+      <c r="D19" s="94"/>
+      <c r="E19" s="105"/>
+      <c r="F19" s="102"/>
+      <c r="G19" s="103"/>
+      <c r="H19" s="94"/>
+      <c r="I19" s="104">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="J19" s="75"/>
-      <c r="K19" s="78"/>
-      <c r="O19" s="51"/>
-      <c r="P19" s="51"/>
-      <c r="Q19" s="51"/>
+      <c r="J19" s="95"/>
+      <c r="K19" s="98"/>
+      <c r="O19" s="71"/>
+      <c r="P19" s="71"/>
+      <c r="Q19" s="71"/>
     </row>
     <row r="20" ht="16.300000000000001">
-      <c r="A20" s="79"/>
-      <c r="B20" s="80"/>
-      <c r="C20" s="74"/>
-      <c r="D20" s="74"/>
-      <c r="E20" s="85"/>
-      <c r="F20" s="82"/>
-      <c r="G20" s="74"/>
-      <c r="H20" s="74"/>
-      <c r="I20" s="84">
+      <c r="A20" s="99"/>
+      <c r="B20" s="100"/>
+      <c r="C20" s="94"/>
+      <c r="D20" s="94"/>
+      <c r="E20" s="105"/>
+      <c r="F20" s="102"/>
+      <c r="G20" s="94"/>
+      <c r="H20" s="94"/>
+      <c r="I20" s="104">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="J20" s="75"/>
-      <c r="K20" s="78"/>
-      <c r="O20" s="51"/>
-      <c r="P20" s="51"/>
-      <c r="Q20" s="51"/>
+      <c r="J20" s="95"/>
+      <c r="K20" s="98"/>
+      <c r="O20" s="71"/>
+      <c r="P20" s="71"/>
+      <c r="Q20" s="71"/>
     </row>
     <row r="21" ht="15.65">
-      <c r="A21" s="79"/>
-      <c r="B21" s="80"/>
-      <c r="C21" s="74"/>
-      <c r="D21" s="74"/>
-      <c r="E21" s="86"/>
-      <c r="F21" s="82"/>
-      <c r="G21" s="74"/>
-      <c r="H21" s="74"/>
-      <c r="I21" s="84">
+      <c r="A21" s="99"/>
+      <c r="B21" s="100"/>
+      <c r="C21" s="94"/>
+      <c r="D21" s="94"/>
+      <c r="E21" s="106"/>
+      <c r="F21" s="102"/>
+      <c r="G21" s="94"/>
+      <c r="H21" s="94"/>
+      <c r="I21" s="104">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="J21" s="75"/>
-      <c r="K21" s="78"/>
-      <c r="O21" s="51"/>
-      <c r="P21" s="51"/>
-      <c r="Q21" s="51"/>
+      <c r="J21" s="95"/>
+      <c r="K21" s="98"/>
+      <c r="O21" s="71"/>
+      <c r="P21" s="71"/>
+      <c r="Q21" s="71"/>
     </row>
     <row r="22" ht="30.699999999999999" customHeight="1">
-      <c r="A22" s="87"/>
-      <c r="B22" s="88"/>
-      <c r="C22" s="89"/>
-      <c r="D22" s="90"/>
-      <c r="E22" s="91"/>
-      <c r="F22" s="92"/>
-      <c r="G22" s="90"/>
-      <c r="H22" s="93"/>
-      <c r="I22" s="94"/>
-      <c r="J22" s="75"/>
-      <c r="K22" s="51"/>
-      <c r="O22" s="51"/>
-      <c r="P22" s="51"/>
-      <c r="Q22" s="51"/>
+      <c r="A22" s="107"/>
+      <c r="B22" s="108"/>
+      <c r="C22" s="109"/>
+      <c r="D22" s="110"/>
+      <c r="E22" s="111"/>
+      <c r="F22" s="112"/>
+      <c r="G22" s="110"/>
+      <c r="H22" s="113"/>
+      <c r="I22" s="114"/>
+      <c r="J22" s="95"/>
+      <c r="K22" s="71"/>
+      <c r="O22" s="71"/>
+      <c r="P22" s="71"/>
+      <c r="Q22" s="71"/>
     </row>
     <row r="23" ht="19.899999999999999" customHeight="1">
-      <c r="A23" s="95" t="s">
-        <v>170</v>
-      </c>
-      <c r="B23" s="96"/>
-      <c r="C23" s="96"/>
-      <c r="D23" s="96"/>
-      <c r="E23" s="96"/>
-      <c r="F23" s="96"/>
-      <c r="G23" s="96"/>
-      <c r="H23" s="97"/>
-      <c r="I23" s="98">
+      <c r="A23" s="115" t="s">
+        <v>194</v>
+      </c>
+      <c r="B23" s="116"/>
+      <c r="C23" s="116"/>
+      <c r="D23" s="116"/>
+      <c r="E23" s="116"/>
+      <c r="F23" s="116"/>
+      <c r="G23" s="116"/>
+      <c r="H23" s="117"/>
+      <c r="I23" s="118">
         <f>SUM(I10:I22)</f>
         <v>1254704</v>
       </c>
-      <c r="K23" s="51"/>
+      <c r="K23" s="71"/>
     </row>
     <row r="24" ht="19.899999999999999" customHeight="1">
-      <c r="A24" s="99" t="s">
-        <v>171</v>
-      </c>
-      <c r="B24" s="100"/>
-      <c r="C24" s="100"/>
-      <c r="D24" s="100"/>
-      <c r="E24" s="100"/>
-      <c r="F24" s="100"/>
-      <c r="G24" s="100"/>
-      <c r="H24" s="101"/>
-      <c r="I24" s="102"/>
-      <c r="J24" s="68"/>
-      <c r="K24" s="51"/>
+      <c r="A24" s="119" t="s">
+        <v>195</v>
+      </c>
+      <c r="B24" s="120"/>
+      <c r="C24" s="120"/>
+      <c r="D24" s="120"/>
+      <c r="E24" s="120"/>
+      <c r="F24" s="120"/>
+      <c r="G24" s="120"/>
+      <c r="H24" s="121"/>
+      <c r="I24" s="122"/>
+      <c r="J24" s="88"/>
+      <c r="K24" s="71"/>
     </row>
     <row r="25" ht="19.899999999999999" customHeight="1">
-      <c r="A25" s="103" t="s">
-        <v>172</v>
-      </c>
-      <c r="B25" s="104"/>
-      <c r="C25" s="104"/>
-      <c r="D25" s="104"/>
-      <c r="E25" s="104"/>
-      <c r="F25" s="104"/>
-      <c r="G25" s="104"/>
-      <c r="H25" s="105"/>
-      <c r="I25" s="106">
+      <c r="A25" s="123" t="s">
+        <v>196</v>
+      </c>
+      <c r="B25" s="124"/>
+      <c r="C25" s="124"/>
+      <c r="D25" s="124"/>
+      <c r="E25" s="124"/>
+      <c r="F25" s="124"/>
+      <c r="G25" s="124"/>
+      <c r="H25" s="125"/>
+      <c r="I25" s="126">
         <f>I23</f>
         <v>1254704</v>
       </c>
-      <c r="J25" s="68"/>
-      <c r="K25" s="107"/>
+      <c r="J25" s="88"/>
+      <c r="K25" s="127"/>
     </row>
     <row r="26" ht="19.449999999999999" customHeight="1">
-      <c r="A26" s="103" t="s">
-        <v>173</v>
-      </c>
-      <c r="B26" s="104"/>
-      <c r="C26" s="104"/>
-      <c r="D26" s="104"/>
-      <c r="E26" s="104"/>
-      <c r="F26" s="104"/>
-      <c r="G26" s="104"/>
-      <c r="H26" s="105"/>
-      <c r="I26" s="108">
+      <c r="A26" s="123" t="s">
+        <v>197</v>
+      </c>
+      <c r="B26" s="124"/>
+      <c r="C26" s="124"/>
+      <c r="D26" s="124"/>
+      <c r="E26" s="124"/>
+      <c r="F26" s="124"/>
+      <c r="G26" s="124"/>
+      <c r="H26" s="125"/>
+      <c r="I26" s="128">
         <f>I25*0.1</f>
         <v>125470.40000000001</v>
       </c>
-      <c r="J26" s="109"/>
-      <c r="K26" s="110"/>
+      <c r="J26" s="129"/>
+      <c r="K26" s="130"/>
     </row>
     <row r="27" ht="19.449999999999999" customHeight="1">
-      <c r="A27" s="111" t="s">
-        <v>174</v>
-      </c>
-      <c r="B27" s="112"/>
-      <c r="C27" s="112"/>
-      <c r="D27" s="112"/>
-      <c r="E27" s="112"/>
-      <c r="F27" s="112"/>
-      <c r="G27" s="112"/>
-      <c r="H27" s="113"/>
-      <c r="I27" s="114">
+      <c r="A27" s="131" t="s">
+        <v>198</v>
+      </c>
+      <c r="B27" s="132"/>
+      <c r="C27" s="132"/>
+      <c r="D27" s="132"/>
+      <c r="E27" s="132"/>
+      <c r="F27" s="132"/>
+      <c r="G27" s="132"/>
+      <c r="H27" s="133"/>
+      <c r="I27" s="134">
         <f>'Технические ограничения'!E11</f>
         <v>446400</v>
       </c>
-      <c r="J27" s="68"/>
-      <c r="K27" s="110"/>
+      <c r="J27" s="88"/>
+      <c r="K27" s="130"/>
     </row>
     <row r="28" ht="19.899999999999999" customHeight="1">
-      <c r="A28" s="111" t="s">
-        <v>175</v>
-      </c>
-      <c r="B28" s="112"/>
-      <c r="C28" s="112"/>
-      <c r="D28" s="112"/>
-      <c r="E28" s="112"/>
-      <c r="F28" s="112"/>
-      <c r="G28" s="112"/>
-      <c r="H28" s="113"/>
-      <c r="I28" s="114">
+      <c r="A28" s="131" t="s">
+        <v>199</v>
+      </c>
+      <c r="B28" s="132"/>
+      <c r="C28" s="132"/>
+      <c r="D28" s="132"/>
+      <c r="E28" s="132"/>
+      <c r="F28" s="132"/>
+      <c r="G28" s="132"/>
+      <c r="H28" s="133"/>
+      <c r="I28" s="134">
         <v>0</v>
       </c>
-      <c r="J28" s="68"/>
-      <c r="K28" s="110"/>
+      <c r="J28" s="88"/>
+      <c r="K28" s="130"/>
     </row>
     <row r="29" ht="19.899999999999999" customHeight="1">
-      <c r="A29" s="115" t="s">
-        <v>176</v>
-      </c>
-      <c r="B29" s="116"/>
-      <c r="C29" s="116"/>
-      <c r="D29" s="116"/>
-      <c r="E29" s="116"/>
-      <c r="F29" s="116"/>
-      <c r="G29" s="116"/>
-      <c r="H29" s="117"/>
-      <c r="I29" s="106">
+      <c r="A29" s="135" t="s">
+        <v>200</v>
+      </c>
+      <c r="B29" s="136"/>
+      <c r="C29" s="136"/>
+      <c r="D29" s="136"/>
+      <c r="E29" s="136"/>
+      <c r="F29" s="136"/>
+      <c r="G29" s="136"/>
+      <c r="H29" s="137"/>
+      <c r="I29" s="126">
         <f>I25+I26+I27+I28</f>
         <v>1826574.3999999999</v>
       </c>
-      <c r="J29" s="68"/>
-      <c r="K29" s="107"/>
+      <c r="J29" s="88"/>
+      <c r="K29" s="127"/>
     </row>
     <row r="30" ht="19.899999999999999" customHeight="1">
-      <c r="A30" s="111" t="s">
-        <v>177</v>
-      </c>
-      <c r="B30" s="112"/>
-      <c r="C30" s="112"/>
-      <c r="D30" s="112"/>
-      <c r="E30" s="112"/>
-      <c r="F30" s="112"/>
-      <c r="G30" s="112"/>
-      <c r="H30" s="113"/>
-      <c r="I30" s="114">
+      <c r="A30" s="131" t="s">
+        <v>201</v>
+      </c>
+      <c r="B30" s="132"/>
+      <c r="C30" s="132"/>
+      <c r="D30" s="132"/>
+      <c r="E30" s="132"/>
+      <c r="F30" s="132"/>
+      <c r="G30" s="132"/>
+      <c r="H30" s="133"/>
+      <c r="I30" s="134">
         <v>0</v>
       </c>
-      <c r="J30" s="68"/>
-      <c r="K30" s="110"/>
+      <c r="J30" s="88"/>
+      <c r="K30" s="130"/>
     </row>
     <row r="31" ht="19.899999999999999" customHeight="1">
-      <c r="A31" s="118" t="s">
-        <v>178</v>
-      </c>
-      <c r="B31" s="119"/>
-      <c r="C31" s="119"/>
-      <c r="D31" s="119"/>
-      <c r="E31" s="119"/>
-      <c r="F31" s="119"/>
-      <c r="G31" s="119"/>
-      <c r="H31" s="120"/>
-      <c r="I31" s="114">
+      <c r="A31" s="138" t="s">
+        <v>202</v>
+      </c>
+      <c r="B31" s="139"/>
+      <c r="C31" s="139"/>
+      <c r="D31" s="139"/>
+      <c r="E31" s="139"/>
+      <c r="F31" s="139"/>
+      <c r="G31" s="139"/>
+      <c r="H31" s="140"/>
+      <c r="I31" s="134">
         <f>I29+I30</f>
         <v>1826574.3999999999</v>
       </c>
-      <c r="J31" s="68"/>
-      <c r="K31" s="110"/>
+      <c r="J31" s="88"/>
+      <c r="K31" s="130"/>
     </row>
     <row r="32" ht="19.899999999999999" customHeight="1">
-      <c r="A32" s="103" t="s">
-        <v>179</v>
-      </c>
-      <c r="B32" s="104"/>
-      <c r="C32" s="104"/>
-      <c r="D32" s="104"/>
-      <c r="E32" s="104"/>
-      <c r="F32" s="104"/>
-      <c r="G32" s="104"/>
-      <c r="H32" s="105"/>
-      <c r="I32" s="114">
+      <c r="A32" s="123" t="s">
+        <v>203</v>
+      </c>
+      <c r="B32" s="124"/>
+      <c r="C32" s="124"/>
+      <c r="D32" s="124"/>
+      <c r="E32" s="124"/>
+      <c r="F32" s="124"/>
+      <c r="G32" s="124"/>
+      <c r="H32" s="125"/>
+      <c r="I32" s="134">
         <f>I31*0.1</f>
         <v>182657.44</v>
       </c>
-      <c r="J32" s="109"/>
-      <c r="K32" s="110"/>
-      <c r="Q32" s="121"/>
+      <c r="J32" s="129"/>
+      <c r="K32" s="130"/>
+      <c r="Q32" s="141"/>
     </row>
     <row r="33" ht="19.899999999999999" customHeight="1">
-      <c r="A33" s="122" t="s">
-        <v>180</v>
-      </c>
-      <c r="B33" s="123"/>
-      <c r="C33" s="123"/>
-      <c r="D33" s="123"/>
-      <c r="E33" s="123"/>
-      <c r="F33" s="123"/>
-      <c r="G33" s="123"/>
-      <c r="H33" s="124"/>
-      <c r="I33" s="125">
+      <c r="A33" s="142" t="s">
+        <v>204</v>
+      </c>
+      <c r="B33" s="143"/>
+      <c r="C33" s="143"/>
+      <c r="D33" s="143"/>
+      <c r="E33" s="143"/>
+      <c r="F33" s="143"/>
+      <c r="G33" s="143"/>
+      <c r="H33" s="144"/>
+      <c r="I33" s="145">
         <f>I32+I31</f>
         <v>2009231.8399999999</v>
       </c>
-      <c r="J33" s="121"/>
-      <c r="K33" s="107"/>
-    </row>
-    <row r="34" s="51" customFormat="1" ht="19.449999999999999" customHeight="1">
-      <c r="A34" s="126" t="s">
-        <v>181</v>
-      </c>
-      <c r="B34" s="104"/>
-      <c r="C34" s="104"/>
-      <c r="D34" s="104"/>
-      <c r="E34" s="104"/>
-      <c r="F34" s="104"/>
-      <c r="G34" s="104"/>
-      <c r="H34" s="105"/>
-      <c r="I34" s="114">
+      <c r="J33" s="141"/>
+      <c r="K33" s="127"/>
+    </row>
+    <row r="34" s="71" customFormat="1" ht="19.449999999999999" customHeight="1">
+      <c r="A34" s="146" t="s">
+        <v>205</v>
+      </c>
+      <c r="B34" s="124"/>
+      <c r="C34" s="124"/>
+      <c r="D34" s="124"/>
+      <c r="E34" s="124"/>
+      <c r="F34" s="124"/>
+      <c r="G34" s="124"/>
+      <c r="H34" s="125"/>
+      <c r="I34" s="134">
         <f>I33*0.22</f>
         <v>442031.0048</v>
       </c>
-      <c r="J34" s="121"/>
-      <c r="K34" s="107"/>
-    </row>
-    <row r="35" s="51" customFormat="1" ht="16.300000000000001" customHeight="1">
-      <c r="A35" s="127" t="s">
-        <v>182</v>
-      </c>
-      <c r="B35" s="128"/>
-      <c r="C35" s="128"/>
-      <c r="D35" s="128"/>
-      <c r="E35" s="128"/>
-      <c r="F35" s="128"/>
-      <c r="G35" s="128"/>
-      <c r="H35" s="129"/>
-      <c r="I35" s="130">
+      <c r="J34" s="141"/>
+      <c r="K34" s="127"/>
+    </row>
+    <row r="35" s="71" customFormat="1" ht="16.300000000000001" customHeight="1">
+      <c r="A35" s="147" t="s">
+        <v>206</v>
+      </c>
+      <c r="B35" s="148"/>
+      <c r="C35" s="148"/>
+      <c r="D35" s="148"/>
+      <c r="E35" s="148"/>
+      <c r="F35" s="148"/>
+      <c r="G35" s="148"/>
+      <c r="H35" s="149"/>
+      <c r="I35" s="150">
         <f>I33+0.22*I33</f>
         <v>2451262.8448000001</v>
       </c>
     </row>
     <row r="36" ht="15.65">
-      <c r="K36" s="51"/>
+      <c r="K36" s="71"/>
     </row>
     <row r="37" ht="15.65">
-      <c r="K37" s="51"/>
+      <c r="K37" s="71"/>
     </row>
     <row r="40" ht="34.450000000000003" customHeight="1"/>
   </sheetData>
@@ -7943,4 +5088,3175 @@
   <headerFooter/>
   <legacyDrawing r:id="rId3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col customWidth="1" min="1" max="1" width="4.4531200000000002"/>
+    <col customWidth="1" min="2" max="2" width="37.179699999999997"/>
+    <col customWidth="1" min="3" max="3" width="23.542999999999999"/>
+    <col customWidth="1" min="4" max="4" width="14.726599999999999"/>
+    <col customWidth="1" min="5" max="5" width="12.8164"/>
+    <col customWidth="1" min="6" max="6" width="9.5429700000000004"/>
+    <col customWidth="1" min="7" max="7" width="10"/>
+    <col customWidth="1" min="8" max="8" width="54.453099999999999"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="30">
+      <c r="A1" s="151" t="s">
+        <v>91</v>
+      </c>
+      <c r="B1" s="151" t="s">
+        <v>207</v>
+      </c>
+      <c r="C1" s="151" t="s">
+        <v>208</v>
+      </c>
+      <c r="D1" s="151" t="s">
+        <v>209</v>
+      </c>
+      <c r="E1" s="151" t="s">
+        <v>210</v>
+      </c>
+      <c r="F1" s="151" t="s">
+        <v>211</v>
+      </c>
+      <c r="G1" s="151" t="s">
+        <v>212</v>
+      </c>
+      <c r="H1" s="151" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="2" ht="60">
+      <c r="A2" s="11">
+        <v>1</v>
+      </c>
+      <c r="B2" s="11" t="s">
+        <v>214</v>
+      </c>
+      <c r="C2" s="11" t="s">
+        <v>215</v>
+      </c>
+      <c r="D2" s="11" t="s">
+        <v>216</v>
+      </c>
+      <c r="E2" s="11">
+        <v>0.80000000000000004</v>
+      </c>
+      <c r="F2" s="11">
+        <v>0.90000000000000002</v>
+      </c>
+      <c r="G2" s="11">
+        <v>0.71999999999999997</v>
+      </c>
+      <c r="H2" s="11" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="3" ht="60">
+      <c r="A3" s="11">
+        <v>2</v>
+      </c>
+      <c r="B3" s="11" t="s">
+        <v>218</v>
+      </c>
+      <c r="C3" s="11" t="s">
+        <v>219</v>
+      </c>
+      <c r="D3" s="11" t="s">
+        <v>220</v>
+      </c>
+      <c r="E3" s="11">
+        <v>0.80000000000000004</v>
+      </c>
+      <c r="F3" s="11">
+        <v>0.90000000000000002</v>
+      </c>
+      <c r="G3" s="11">
+        <v>0.71999999999999997</v>
+      </c>
+      <c r="H3" s="11" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="4" ht="60">
+      <c r="A4" s="11">
+        <v>3</v>
+      </c>
+      <c r="B4" s="11" t="s">
+        <v>222</v>
+      </c>
+      <c r="C4" s="11" t="s">
+        <v>223</v>
+      </c>
+      <c r="D4" s="11" t="s">
+        <v>224</v>
+      </c>
+      <c r="E4" s="11">
+        <v>0.80000000000000004</v>
+      </c>
+      <c r="F4" s="11">
+        <v>0.90000000000000002</v>
+      </c>
+      <c r="G4" s="11">
+        <v>0.71999999999999997</v>
+      </c>
+      <c r="H4" s="11" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="5" ht="60">
+      <c r="A5" s="11">
+        <v>4</v>
+      </c>
+      <c r="B5" s="11" t="s">
+        <v>226</v>
+      </c>
+      <c r="C5" s="11" t="s">
+        <v>227</v>
+      </c>
+      <c r="D5" s="11" t="s">
+        <v>224</v>
+      </c>
+      <c r="E5" s="11">
+        <v>0.80000000000000004</v>
+      </c>
+      <c r="F5" s="11">
+        <v>0.69999999999999996</v>
+      </c>
+      <c r="G5" s="11">
+        <v>0.56000000000000005</v>
+      </c>
+      <c r="H5" s="11" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="6" ht="45">
+      <c r="A6" s="11">
+        <v>5</v>
+      </c>
+      <c r="B6" s="11" t="s">
+        <v>229</v>
+      </c>
+      <c r="C6" s="11" t="s">
+        <v>230</v>
+      </c>
+      <c r="D6" s="11" t="s">
+        <v>231</v>
+      </c>
+      <c r="E6" s="11">
+        <v>0.80000000000000004</v>
+      </c>
+      <c r="F6" s="11">
+        <v>0.69999999999999996</v>
+      </c>
+      <c r="G6" s="11">
+        <v>0.56000000000000005</v>
+      </c>
+      <c r="H6" s="11" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="7" ht="60">
+      <c r="A7" s="11">
+        <v>6</v>
+      </c>
+      <c r="B7" s="11" t="s">
+        <v>233</v>
+      </c>
+      <c r="C7" s="11" t="s">
+        <v>234</v>
+      </c>
+      <c r="D7" s="11" t="s">
+        <v>231</v>
+      </c>
+      <c r="E7" s="11">
+        <v>0.80000000000000004</v>
+      </c>
+      <c r="F7" s="11">
+        <v>0.69999999999999996</v>
+      </c>
+      <c r="G7" s="11">
+        <v>0.56000000000000005</v>
+      </c>
+      <c r="H7" s="11" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="8" ht="60">
+      <c r="A8" s="11">
+        <v>7</v>
+      </c>
+      <c r="B8" s="11" t="s">
+        <v>236</v>
+      </c>
+      <c r="C8" s="11" t="s">
+        <v>237</v>
+      </c>
+      <c r="D8" s="11" t="s">
+        <v>224</v>
+      </c>
+      <c r="E8" s="11">
+        <v>0.80000000000000004</v>
+      </c>
+      <c r="F8" s="11">
+        <v>0.69999999999999996</v>
+      </c>
+      <c r="G8" s="11">
+        <v>0.56000000000000005</v>
+      </c>
+      <c r="H8" s="11" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="9" ht="60">
+      <c r="A9" s="11">
+        <v>8</v>
+      </c>
+      <c r="B9" s="11" t="s">
+        <v>239</v>
+      </c>
+      <c r="C9" s="11" t="s">
+        <v>240</v>
+      </c>
+      <c r="D9" s="11" t="s">
+        <v>224</v>
+      </c>
+      <c r="E9" s="11">
+        <v>0.80000000000000004</v>
+      </c>
+      <c r="F9" s="11">
+        <v>0.69999999999999996</v>
+      </c>
+      <c r="G9" s="11">
+        <v>0.56000000000000005</v>
+      </c>
+      <c r="H9" s="11" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="10" ht="60">
+      <c r="A10" s="11">
+        <v>9</v>
+      </c>
+      <c r="B10" s="11" t="s">
+        <v>242</v>
+      </c>
+      <c r="C10" s="11" t="s">
+        <v>243</v>
+      </c>
+      <c r="D10" s="11" t="s">
+        <v>224</v>
+      </c>
+      <c r="E10" s="11">
+        <v>0.80000000000000004</v>
+      </c>
+      <c r="F10" s="11">
+        <v>0.69999999999999996</v>
+      </c>
+      <c r="G10" s="11">
+        <v>0.56000000000000005</v>
+      </c>
+      <c r="H10" s="11" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="11" ht="45">
+      <c r="A11" s="11">
+        <v>10</v>
+      </c>
+      <c r="B11" s="11" t="s">
+        <v>245</v>
+      </c>
+      <c r="C11" s="11" t="s">
+        <v>246</v>
+      </c>
+      <c r="D11" s="11" t="s">
+        <v>231</v>
+      </c>
+      <c r="E11" s="11">
+        <v>0.40000000000000002</v>
+      </c>
+      <c r="F11" s="11">
+        <v>0.90000000000000002</v>
+      </c>
+      <c r="G11" s="11">
+        <v>0.35999999999999999</v>
+      </c>
+      <c r="H11" s="11" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="12" ht="45">
+      <c r="A12" s="11">
+        <v>11</v>
+      </c>
+      <c r="B12" s="11" t="s">
+        <v>248</v>
+      </c>
+      <c r="C12" s="11" t="s">
+        <v>249</v>
+      </c>
+      <c r="D12" s="11" t="s">
+        <v>220</v>
+      </c>
+      <c r="E12" s="11">
+        <v>0.40000000000000002</v>
+      </c>
+      <c r="F12" s="11">
+        <v>0.90000000000000002</v>
+      </c>
+      <c r="G12" s="11">
+        <v>0.35999999999999999</v>
+      </c>
+      <c r="H12" s="11" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="13" ht="30">
+      <c r="A13" s="11">
+        <v>12</v>
+      </c>
+      <c r="B13" s="11" t="s">
+        <v>251</v>
+      </c>
+      <c r="C13" s="11" t="s">
+        <v>252</v>
+      </c>
+      <c r="D13" s="11" t="s">
+        <v>224</v>
+      </c>
+      <c r="E13" s="11">
+        <v>0.40000000000000002</v>
+      </c>
+      <c r="F13" s="11">
+        <v>0.90000000000000002</v>
+      </c>
+      <c r="G13" s="11">
+        <v>0.35999999999999999</v>
+      </c>
+      <c r="H13" s="11" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="14" ht="45">
+      <c r="A14" s="11">
+        <v>13</v>
+      </c>
+      <c r="B14" s="11" t="s">
+        <v>254</v>
+      </c>
+      <c r="C14" s="11" t="s">
+        <v>255</v>
+      </c>
+      <c r="D14" s="11" t="s">
+        <v>216</v>
+      </c>
+      <c r="E14" s="11">
+        <v>0.40000000000000002</v>
+      </c>
+      <c r="F14" s="11">
+        <v>0.90000000000000002</v>
+      </c>
+      <c r="G14" s="11">
+        <v>0.35999999999999999</v>
+      </c>
+      <c r="H14" s="11" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="15" ht="45">
+      <c r="A15" s="11">
+        <v>14</v>
+      </c>
+      <c r="B15" s="11" t="s">
+        <v>257</v>
+      </c>
+      <c r="C15" s="11" t="s">
+        <v>258</v>
+      </c>
+      <c r="D15" s="11" t="s">
+        <v>224</v>
+      </c>
+      <c r="E15" s="11">
+        <v>0.80000000000000004</v>
+      </c>
+      <c r="F15" s="11">
+        <v>0.5</v>
+      </c>
+      <c r="G15" s="11">
+        <v>0.40000000000000002</v>
+      </c>
+      <c r="H15" s="11" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="16" ht="45">
+      <c r="A16" s="11">
+        <v>15</v>
+      </c>
+      <c r="B16" s="11" t="s">
+        <v>260</v>
+      </c>
+      <c r="C16" s="11" t="s">
+        <v>261</v>
+      </c>
+      <c r="D16" s="11" t="s">
+        <v>216</v>
+      </c>
+      <c r="E16" s="11">
+        <v>0.80000000000000004</v>
+      </c>
+      <c r="F16" s="11">
+        <v>0.5</v>
+      </c>
+      <c r="G16" s="11">
+        <v>0.40000000000000002</v>
+      </c>
+      <c r="H16" s="11" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="17" ht="30">
+      <c r="A17" s="11">
+        <v>16</v>
+      </c>
+      <c r="B17" s="11" t="s">
+        <v>263</v>
+      </c>
+      <c r="C17" s="11" t="s">
+        <v>264</v>
+      </c>
+      <c r="D17" s="11" t="s">
+        <v>224</v>
+      </c>
+      <c r="E17" s="11">
+        <v>0.80000000000000004</v>
+      </c>
+      <c r="F17" s="11">
+        <v>0.5</v>
+      </c>
+      <c r="G17" s="11">
+        <v>0.40000000000000002</v>
+      </c>
+      <c r="H17" s="11" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="18" ht="45">
+      <c r="A18" s="11">
+        <v>17</v>
+      </c>
+      <c r="B18" s="11" t="s">
+        <v>266</v>
+      </c>
+      <c r="C18" s="11" t="s">
+        <v>267</v>
+      </c>
+      <c r="D18" s="11" t="s">
+        <v>224</v>
+      </c>
+      <c r="E18" s="11">
+        <v>0.80000000000000004</v>
+      </c>
+      <c r="F18" s="11">
+        <v>0.5</v>
+      </c>
+      <c r="G18" s="11">
+        <v>0.40000000000000002</v>
+      </c>
+      <c r="H18" s="11" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="19" ht="60">
+      <c r="A19" s="11">
+        <v>18</v>
+      </c>
+      <c r="B19" s="11" t="s">
+        <v>269</v>
+      </c>
+      <c r="C19" s="11" t="s">
+        <v>270</v>
+      </c>
+      <c r="D19" s="11" t="s">
+        <v>231</v>
+      </c>
+      <c r="E19" s="11">
+        <v>0.40000000000000002</v>
+      </c>
+      <c r="F19" s="11">
+        <v>0.69999999999999996</v>
+      </c>
+      <c r="G19" s="11">
+        <v>0.28000000000000003</v>
+      </c>
+      <c r="H19" s="11" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="20" ht="45">
+      <c r="A20" s="11">
+        <v>19</v>
+      </c>
+      <c r="B20" s="11" t="s">
+        <v>272</v>
+      </c>
+      <c r="C20" s="11" t="s">
+        <v>273</v>
+      </c>
+      <c r="D20" s="11" t="s">
+        <v>224</v>
+      </c>
+      <c r="E20" s="11">
+        <v>0.40000000000000002</v>
+      </c>
+      <c r="F20" s="11">
+        <v>0.69999999999999996</v>
+      </c>
+      <c r="G20" s="11">
+        <v>0.28000000000000003</v>
+      </c>
+      <c r="H20" s="11" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="21" ht="45">
+      <c r="A21" s="11">
+        <v>20</v>
+      </c>
+      <c r="B21" s="11" t="s">
+        <v>275</v>
+      </c>
+      <c r="C21" s="11" t="s">
+        <v>276</v>
+      </c>
+      <c r="D21" s="11" t="s">
+        <v>220</v>
+      </c>
+      <c r="E21" s="11">
+        <v>0.40000000000000002</v>
+      </c>
+      <c r="F21" s="11">
+        <v>0.69999999999999996</v>
+      </c>
+      <c r="G21" s="11">
+        <v>0.28000000000000003</v>
+      </c>
+      <c r="H21" s="11" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="22" ht="45">
+      <c r="A22" s="11">
+        <v>21</v>
+      </c>
+      <c r="B22" s="11" t="s">
+        <v>278</v>
+      </c>
+      <c r="C22" s="11" t="s">
+        <v>279</v>
+      </c>
+      <c r="D22" s="11" t="s">
+        <v>224</v>
+      </c>
+      <c r="E22" s="11">
+        <v>0.40000000000000002</v>
+      </c>
+      <c r="F22" s="11">
+        <v>0.69999999999999996</v>
+      </c>
+      <c r="G22" s="11">
+        <v>0.28000000000000003</v>
+      </c>
+      <c r="H22" s="11" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="23" ht="60">
+      <c r="A23" s="11">
+        <v>22</v>
+      </c>
+      <c r="B23" s="11" t="s">
+        <v>281</v>
+      </c>
+      <c r="C23" s="11" t="s">
+        <v>282</v>
+      </c>
+      <c r="D23" s="11" t="s">
+        <v>224</v>
+      </c>
+      <c r="E23" s="11">
+        <v>0.40000000000000002</v>
+      </c>
+      <c r="F23" s="11">
+        <v>0.69999999999999996</v>
+      </c>
+      <c r="G23" s="11">
+        <v>0.28000000000000003</v>
+      </c>
+      <c r="H23" s="11" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="24" ht="45">
+      <c r="A24" s="11">
+        <v>23</v>
+      </c>
+      <c r="B24" s="11" t="s">
+        <v>284</v>
+      </c>
+      <c r="C24" s="11" t="s">
+        <v>285</v>
+      </c>
+      <c r="D24" s="11" t="s">
+        <v>220</v>
+      </c>
+      <c r="E24" s="11">
+        <v>0.40000000000000002</v>
+      </c>
+      <c r="F24" s="11">
+        <v>0.69999999999999996</v>
+      </c>
+      <c r="G24" s="11">
+        <v>0.28000000000000003</v>
+      </c>
+      <c r="H24" s="11" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="25" ht="30">
+      <c r="A25" s="11">
+        <v>24</v>
+      </c>
+      <c r="B25" s="11" t="s">
+        <v>287</v>
+      </c>
+      <c r="C25" s="11" t="s">
+        <v>288</v>
+      </c>
+      <c r="D25" s="11" t="s">
+        <v>220</v>
+      </c>
+      <c r="E25" s="11">
+        <v>0.40000000000000002</v>
+      </c>
+      <c r="F25" s="11">
+        <v>0.69999999999999996</v>
+      </c>
+      <c r="G25" s="11">
+        <v>0.28000000000000003</v>
+      </c>
+      <c r="H25" s="11" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="26" ht="45">
+      <c r="A26" s="11">
+        <v>25</v>
+      </c>
+      <c r="B26" s="11" t="s">
+        <v>290</v>
+      </c>
+      <c r="C26" s="11" t="s">
+        <v>291</v>
+      </c>
+      <c r="D26" s="11" t="s">
+        <v>224</v>
+      </c>
+      <c r="E26" s="11">
+        <v>0.80000000000000004</v>
+      </c>
+      <c r="F26" s="11">
+        <v>0.29999999999999999</v>
+      </c>
+      <c r="G26" s="11">
+        <v>0.23999999999999999</v>
+      </c>
+      <c r="H26" s="11" t="s">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="27" ht="45">
+      <c r="A27" s="11">
+        <v>26</v>
+      </c>
+      <c r="B27" s="11" t="s">
+        <v>293</v>
+      </c>
+      <c r="C27" s="11" t="s">
+        <v>294</v>
+      </c>
+      <c r="D27" s="11" t="s">
+        <v>224</v>
+      </c>
+      <c r="E27" s="11">
+        <v>0.80000000000000004</v>
+      </c>
+      <c r="F27" s="11">
+        <v>0.29999999999999999</v>
+      </c>
+      <c r="G27" s="11">
+        <v>0.23999999999999999</v>
+      </c>
+      <c r="H27" s="11" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="28" ht="45">
+      <c r="A28" s="11">
+        <v>27</v>
+      </c>
+      <c r="B28" s="11" t="s">
+        <v>296</v>
+      </c>
+      <c r="C28" s="11" t="s">
+        <v>297</v>
+      </c>
+      <c r="D28" s="11" t="s">
+        <v>231</v>
+      </c>
+      <c r="E28" s="11">
+        <v>0.80000000000000004</v>
+      </c>
+      <c r="F28" s="11">
+        <v>0.29999999999999999</v>
+      </c>
+      <c r="G28" s="11">
+        <v>0.23999999999999999</v>
+      </c>
+      <c r="H28" s="11" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="29" ht="45">
+      <c r="A29" s="152">
+        <v>28</v>
+      </c>
+      <c r="B29" s="11" t="s">
+        <v>299</v>
+      </c>
+      <c r="C29" s="11" t="s">
+        <v>300</v>
+      </c>
+      <c r="D29" s="152" t="s">
+        <v>224</v>
+      </c>
+      <c r="E29" s="152">
+        <v>0.80000000000000004</v>
+      </c>
+      <c r="F29" s="152">
+        <v>0.29999999999999999</v>
+      </c>
+      <c r="G29" s="152">
+        <v>0.23999999999999999</v>
+      </c>
+      <c r="H29" s="152" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="30" ht="45">
+      <c r="A30" s="152">
+        <v>29</v>
+      </c>
+      <c r="B30" s="11" t="s">
+        <v>302</v>
+      </c>
+      <c r="C30" s="11" t="s">
+        <v>303</v>
+      </c>
+      <c r="D30" s="152" t="s">
+        <v>231</v>
+      </c>
+      <c r="E30" s="152">
+        <v>0.80000000000000004</v>
+      </c>
+      <c r="F30" s="152">
+        <v>0.29999999999999999</v>
+      </c>
+      <c r="G30" s="152">
+        <v>0.23999999999999999</v>
+      </c>
+      <c r="H30" s="152" t="s">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="31" ht="45">
+      <c r="A31" s="152">
+        <v>30</v>
+      </c>
+      <c r="B31" s="11" t="s">
+        <v>305</v>
+      </c>
+      <c r="C31" s="11" t="s">
+        <v>306</v>
+      </c>
+      <c r="D31" s="152" t="s">
+        <v>216</v>
+      </c>
+      <c r="E31" s="152">
+        <v>0.20000000000000001</v>
+      </c>
+      <c r="F31" s="152">
+        <v>0.90000000000000002</v>
+      </c>
+      <c r="G31" s="152">
+        <v>0.17999999999999999</v>
+      </c>
+      <c r="H31" s="152" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="32" ht="45">
+      <c r="A32" s="152">
+        <v>31</v>
+      </c>
+      <c r="B32" s="11" t="s">
+        <v>308</v>
+      </c>
+      <c r="C32" s="11" t="s">
+        <v>309</v>
+      </c>
+      <c r="D32" s="152" t="s">
+        <v>224</v>
+      </c>
+      <c r="E32" s="152">
+        <v>0.20000000000000001</v>
+      </c>
+      <c r="F32" s="152">
+        <v>0.90000000000000002</v>
+      </c>
+      <c r="G32" s="152">
+        <v>0.17999999999999999</v>
+      </c>
+      <c r="H32" s="152" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="33" ht="45">
+      <c r="A33" s="152">
+        <v>32</v>
+      </c>
+      <c r="B33" s="11" t="s">
+        <v>311</v>
+      </c>
+      <c r="C33" s="11" t="s">
+        <v>312</v>
+      </c>
+      <c r="D33" s="152" t="s">
+        <v>224</v>
+      </c>
+      <c r="E33" s="152">
+        <v>0.20000000000000001</v>
+      </c>
+      <c r="F33" s="152">
+        <v>0.90000000000000002</v>
+      </c>
+      <c r="G33" s="152">
+        <v>0.17999999999999999</v>
+      </c>
+      <c r="H33" s="152" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="34" ht="45">
+      <c r="A34" s="152">
+        <v>33</v>
+      </c>
+      <c r="B34" s="11" t="s">
+        <v>314</v>
+      </c>
+      <c r="C34" s="11" t="s">
+        <v>315</v>
+      </c>
+      <c r="D34" s="152" t="s">
+        <v>216</v>
+      </c>
+      <c r="E34" s="152">
+        <v>0.20000000000000001</v>
+      </c>
+      <c r="F34" s="152">
+        <v>0.69999999999999996</v>
+      </c>
+      <c r="G34" s="152">
+        <v>0.14000000000000001</v>
+      </c>
+      <c r="H34" s="152" t="s">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="35" ht="30">
+      <c r="A35" s="152">
+        <v>34</v>
+      </c>
+      <c r="B35" s="11" t="s">
+        <v>317</v>
+      </c>
+      <c r="C35" s="11" t="s">
+        <v>318</v>
+      </c>
+      <c r="D35" s="152" t="s">
+        <v>220</v>
+      </c>
+      <c r="E35" s="152">
+        <v>0.20000000000000001</v>
+      </c>
+      <c r="F35" s="152">
+        <v>0.69999999999999996</v>
+      </c>
+      <c r="G35" s="152">
+        <v>0.14000000000000001</v>
+      </c>
+      <c r="H35" s="152" t="s">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="36" ht="30">
+      <c r="A36" s="152">
+        <v>35</v>
+      </c>
+      <c r="B36" s="11" t="s">
+        <v>320</v>
+      </c>
+      <c r="C36" s="11" t="s">
+        <v>321</v>
+      </c>
+      <c r="D36" s="152" t="s">
+        <v>224</v>
+      </c>
+      <c r="E36" s="152">
+        <v>0.20000000000000001</v>
+      </c>
+      <c r="F36" s="152">
+        <v>0.69999999999999996</v>
+      </c>
+      <c r="G36" s="152">
+        <v>0.14000000000000001</v>
+      </c>
+      <c r="H36" s="152" t="s">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="37" ht="45">
+      <c r="A37" s="152">
+        <v>36</v>
+      </c>
+      <c r="B37" s="11" t="s">
+        <v>323</v>
+      </c>
+      <c r="C37" s="11" t="s">
+        <v>324</v>
+      </c>
+      <c r="D37" s="152" t="s">
+        <v>231</v>
+      </c>
+      <c r="E37" s="152">
+        <v>0.20000000000000001</v>
+      </c>
+      <c r="F37" s="152">
+        <v>0.69999999999999996</v>
+      </c>
+      <c r="G37" s="152">
+        <v>0.14000000000000001</v>
+      </c>
+      <c r="H37" s="152" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="38" ht="30">
+      <c r="A38" s="11">
+        <v>37</v>
+      </c>
+      <c r="B38" s="11" t="s">
+        <v>326</v>
+      </c>
+      <c r="C38" s="11" t="s">
+        <v>327</v>
+      </c>
+      <c r="D38" s="11" t="s">
+        <v>216</v>
+      </c>
+      <c r="E38" s="11">
+        <v>0.40000000000000002</v>
+      </c>
+      <c r="F38" s="11">
+        <v>0.29999999999999999</v>
+      </c>
+      <c r="G38" s="11">
+        <v>0.12</v>
+      </c>
+      <c r="H38" s="11" t="s">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="39" ht="45">
+      <c r="A39" s="11">
+        <v>38</v>
+      </c>
+      <c r="B39" s="11" t="s">
+        <v>329</v>
+      </c>
+      <c r="C39" s="11" t="s">
+        <v>330</v>
+      </c>
+      <c r="D39" s="11" t="s">
+        <v>220</v>
+      </c>
+      <c r="E39" s="11">
+        <v>0.40000000000000002</v>
+      </c>
+      <c r="F39" s="11">
+        <v>0.29999999999999999</v>
+      </c>
+      <c r="G39" s="11">
+        <v>0.12</v>
+      </c>
+      <c r="H39" s="11" t="s">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="40" ht="45">
+      <c r="A40" s="11">
+        <v>39</v>
+      </c>
+      <c r="B40" s="11" t="s">
+        <v>332</v>
+      </c>
+      <c r="C40" s="11" t="s">
+        <v>333</v>
+      </c>
+      <c r="D40" s="11" t="s">
+        <v>220</v>
+      </c>
+      <c r="E40" s="11">
+        <v>0.40000000000000002</v>
+      </c>
+      <c r="F40" s="11">
+        <v>0.29999999999999999</v>
+      </c>
+      <c r="G40" s="11">
+        <v>0.12</v>
+      </c>
+      <c r="H40" s="11" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="41" ht="45">
+      <c r="A41" s="11">
+        <v>40</v>
+      </c>
+      <c r="B41" s="11" t="s">
+        <v>335</v>
+      </c>
+      <c r="C41" s="11" t="s">
+        <v>336</v>
+      </c>
+      <c r="D41" s="11" t="s">
+        <v>224</v>
+      </c>
+      <c r="E41" s="11">
+        <v>0.40000000000000002</v>
+      </c>
+      <c r="F41" s="11">
+        <v>0.29999999999999999</v>
+      </c>
+      <c r="G41" s="11">
+        <v>0.12</v>
+      </c>
+      <c r="H41" s="11" t="s">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="42" ht="30">
+      <c r="A42" s="11">
+        <v>41</v>
+      </c>
+      <c r="B42" s="11" t="s">
+        <v>338</v>
+      </c>
+      <c r="C42" s="11" t="s">
+        <v>339</v>
+      </c>
+      <c r="D42" s="11" t="s">
+        <v>231</v>
+      </c>
+      <c r="E42" s="11">
+        <v>0.20000000000000001</v>
+      </c>
+      <c r="F42" s="11">
+        <v>0.5</v>
+      </c>
+      <c r="G42" s="11">
+        <v>0.10000000000000001</v>
+      </c>
+      <c r="H42" s="11" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="43" ht="30">
+      <c r="A43" s="11">
+        <v>42</v>
+      </c>
+      <c r="B43" s="11" t="s">
+        <v>341</v>
+      </c>
+      <c r="C43" s="11" t="s">
+        <v>342</v>
+      </c>
+      <c r="D43" s="11" t="s">
+        <v>216</v>
+      </c>
+      <c r="E43" s="11">
+        <v>0.20000000000000001</v>
+      </c>
+      <c r="F43" s="11">
+        <v>0.5</v>
+      </c>
+      <c r="G43" s="11">
+        <v>0.10000000000000001</v>
+      </c>
+      <c r="H43" s="11" t="s">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="44" ht="30">
+      <c r="A44" s="11">
+        <v>43</v>
+      </c>
+      <c r="B44" s="11" t="s">
+        <v>344</v>
+      </c>
+      <c r="C44" s="11" t="s">
+        <v>345</v>
+      </c>
+      <c r="D44" s="11" t="s">
+        <v>216</v>
+      </c>
+      <c r="E44" s="11">
+        <v>0.10000000000000001</v>
+      </c>
+      <c r="F44" s="11">
+        <v>0.69999999999999996</v>
+      </c>
+      <c r="G44" s="11">
+        <v>0.070000000000000007</v>
+      </c>
+      <c r="H44" s="11" t="s">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="45" ht="30">
+      <c r="A45" s="11">
+        <v>44</v>
+      </c>
+      <c r="B45" s="11" t="s">
+        <v>347</v>
+      </c>
+      <c r="C45" s="11" t="s">
+        <v>348</v>
+      </c>
+      <c r="D45" s="11" t="s">
+        <v>216</v>
+      </c>
+      <c r="E45" s="11">
+        <v>0.10000000000000001</v>
+      </c>
+      <c r="F45" s="11">
+        <v>0.69999999999999996</v>
+      </c>
+      <c r="G45" s="11">
+        <v>0.070000000000000007</v>
+      </c>
+      <c r="H45" s="11" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="46" ht="45">
+      <c r="A46" s="11">
+        <v>45</v>
+      </c>
+      <c r="B46" s="11" t="s">
+        <v>350</v>
+      </c>
+      <c r="C46" s="11" t="s">
+        <v>351</v>
+      </c>
+      <c r="D46" s="11" t="s">
+        <v>352</v>
+      </c>
+      <c r="E46" s="11">
+        <v>0.40000000000000002</v>
+      </c>
+      <c r="F46" s="11">
+        <v>0.29999999999999999</v>
+      </c>
+      <c r="G46" s="11">
+        <v>0.12</v>
+      </c>
+      <c r="H46" s="11" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="47" ht="15">
+      <c r="A47" t="s">
+        <v>354</v>
+      </c>
+      <c r="G47" s="153">
+        <f>SUM(G1:G46)</f>
+        <v>13.759999999999998</v>
+      </c>
+    </row>
+    <row r="49" ht="15">
+      <c r="A49" t="s">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="51" ht="15">
+      <c r="B51" s="154" t="s">
+        <v>356</v>
+      </c>
+      <c r="C51" s="154" t="s">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="52" ht="15">
+      <c r="B52" s="155">
+        <v>78</v>
+      </c>
+      <c r="C52" s="155">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="54" ht="15">
+      <c r="B54" s="154" t="s">
+        <v>358</v>
+      </c>
+      <c r="C54" s="154" t="s">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="55" ht="15">
+      <c r="B55" s="156">
+        <v>2451262.8399999999</v>
+      </c>
+      <c r="C55" s="156">
+        <v>2696389.1200000001</v>
+      </c>
+    </row>
+    <row r="59" ht="15">
+      <c r="B59" s="157" t="s">
+        <v>359</v>
+      </c>
+      <c r="C59" s="157" t="s">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="60" ht="15">
+      <c r="B60" s="158" t="s">
+        <v>361</v>
+      </c>
+      <c r="C60" s="158">
+        <v>0.050000000000000003</v>
+      </c>
+    </row>
+    <row r="61" ht="15">
+      <c r="B61" s="158" t="s">
+        <v>362</v>
+      </c>
+      <c r="C61" s="158">
+        <v>0.10000000000000001</v>
+      </c>
+    </row>
+    <row r="62" ht="15">
+      <c r="B62" s="158" t="s">
+        <v>363</v>
+      </c>
+      <c r="C62" s="158">
+        <v>0.20000000000000001</v>
+      </c>
+    </row>
+    <row r="63" ht="15">
+      <c r="B63" s="158" t="s">
+        <v>364</v>
+      </c>
+      <c r="C63" s="158">
+        <v>0.40000000000000002</v>
+      </c>
+    </row>
+    <row r="64" ht="15">
+      <c r="B64" s="158" t="s">
+        <v>365</v>
+      </c>
+      <c r="C64" s="158">
+        <v>0.80000000000000004</v>
+      </c>
+    </row>
+    <row r="65" ht="15">
+      <c r="B65" s="159"/>
+      <c r="C65" s="159"/>
+    </row>
+    <row r="66" ht="15">
+      <c r="B66" s="157" t="s">
+        <v>366</v>
+      </c>
+      <c r="C66" s="157" t="s">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="67" ht="15">
+      <c r="B67" s="158" t="s">
+        <v>367</v>
+      </c>
+      <c r="C67" s="158">
+        <v>0.10000000000000001</v>
+      </c>
+    </row>
+    <row r="68" ht="15">
+      <c r="B68" s="158" t="s">
+        <v>368</v>
+      </c>
+      <c r="C68" s="158">
+        <v>0.29999999999999999</v>
+      </c>
+    </row>
+    <row r="69" ht="15">
+      <c r="B69" s="158" t="s">
+        <v>369</v>
+      </c>
+      <c r="C69" s="158">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="70" ht="15">
+      <c r="B70" s="158" t="s">
+        <v>370</v>
+      </c>
+      <c r="C70" s="158">
+        <v>0.69999999999999996</v>
+      </c>
+    </row>
+    <row r="71" ht="15">
+      <c r="B71" s="158" t="s">
+        <v>371</v>
+      </c>
+      <c r="C71" s="158">
+        <v>0.90000000000000002</v>
+      </c>
+    </row>
+  </sheetData>
+  <printOptions headings="0" gridLines="0"/>
+  <pageMargins left="0.70078740157480324" right="0.70078740157480324" top="0.75196850393700787" bottom="0.75196850393700787" header="0.29999999999999999" footer="0.29999999999999999"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" cellComments="none" useFirstPageNumber="0" errors="displayed" horizontalDpi="600" verticalDpi="600" copies="1"/>
+  <headerFooter/>
+  <legacyDrawing r:id="rId3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col customWidth="1" min="1" max="1" width="19.1797"/>
+    <col customWidth="1" min="2" max="2" width="9.4531200000000002"/>
+    <col customWidth="1" min="3" max="3" width="11.9062"/>
+    <col customWidth="1" min="4" max="4" width="11.363300000000001"/>
+    <col customWidth="1" min="5" max="5" width="10.363300000000001"/>
+    <col customWidth="1" min="6" max="6" width="10.6328"/>
+    <col customWidth="1" min="7" max="11" width="8.88671875"/>
+    <col customWidth="1" min="12" max="12" width="12.269500000000001"/>
+    <col customWidth="1" min="13" max="13" width="6.3632799999999996"/>
+    <col customWidth="1" min="14" max="14" width="29.6328"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="150">
+      <c r="A1" s="37" t="s">
+        <v>372</v>
+      </c>
+      <c r="B1" s="37" t="s">
+        <v>135</v>
+      </c>
+      <c r="C1" s="37" t="s">
+        <v>134</v>
+      </c>
+      <c r="D1" s="37" t="s">
+        <v>138</v>
+      </c>
+      <c r="E1" s="37" t="s">
+        <v>140</v>
+      </c>
+      <c r="F1" s="37" t="s">
+        <v>142</v>
+      </c>
+      <c r="G1" s="37" t="s">
+        <v>144</v>
+      </c>
+      <c r="H1" s="37" t="s">
+        <v>146</v>
+      </c>
+      <c r="I1" s="37" t="s">
+        <v>148</v>
+      </c>
+      <c r="J1" s="160"/>
+      <c r="K1" s="45"/>
+      <c r="L1" s="45"/>
+      <c r="M1" s="45"/>
+      <c r="N1" s="161" t="s">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="2" ht="45">
+      <c r="A2" s="40" t="s">
+        <v>374</v>
+      </c>
+      <c r="B2" s="37" t="s">
+        <v>375</v>
+      </c>
+      <c r="C2" s="37" t="s">
+        <v>376</v>
+      </c>
+      <c r="D2" s="37" t="s">
+        <v>377</v>
+      </c>
+      <c r="E2" s="37" t="s">
+        <v>375</v>
+      </c>
+      <c r="F2" s="37" t="s">
+        <v>377</v>
+      </c>
+      <c r="G2" s="37" t="s">
+        <v>375</v>
+      </c>
+      <c r="H2" s="37" t="s">
+        <v>378</v>
+      </c>
+      <c r="I2" s="37" t="s">
+        <v>375</v>
+      </c>
+      <c r="J2" s="160"/>
+      <c r="K2" s="45"/>
+      <c r="L2" s="45"/>
+      <c r="M2" s="45"/>
+      <c r="N2" s="162"/>
+    </row>
+    <row r="3" ht="30">
+      <c r="A3" s="40" t="s">
+        <v>379</v>
+      </c>
+      <c r="B3" s="37" t="s">
+        <v>375</v>
+      </c>
+      <c r="C3" s="37" t="s">
+        <v>376</v>
+      </c>
+      <c r="D3" s="37" t="s">
+        <v>377</v>
+      </c>
+      <c r="E3" s="37" t="s">
+        <v>377</v>
+      </c>
+      <c r="F3" s="37" t="s">
+        <v>378</v>
+      </c>
+      <c r="G3" s="37" t="s">
+        <v>375</v>
+      </c>
+      <c r="H3" s="37" t="s">
+        <v>377</v>
+      </c>
+      <c r="I3" s="37" t="s">
+        <v>375</v>
+      </c>
+      <c r="J3" s="160"/>
+      <c r="K3" s="45"/>
+      <c r="L3" s="45"/>
+      <c r="M3" s="45"/>
+      <c r="N3" s="162"/>
+    </row>
+    <row r="4" ht="30">
+      <c r="A4" s="40" t="s">
+        <v>380</v>
+      </c>
+      <c r="B4" s="37" t="s">
+        <v>375</v>
+      </c>
+      <c r="C4" s="37" t="s">
+        <v>376</v>
+      </c>
+      <c r="D4" s="37" t="s">
+        <v>377</v>
+      </c>
+      <c r="E4" s="37" t="s">
+        <v>378</v>
+      </c>
+      <c r="F4" s="37" t="s">
+        <v>377</v>
+      </c>
+      <c r="G4" s="37" t="s">
+        <v>375</v>
+      </c>
+      <c r="H4" s="37" t="s">
+        <v>375</v>
+      </c>
+      <c r="I4" s="37" t="s">
+        <v>375</v>
+      </c>
+      <c r="J4" s="160"/>
+      <c r="K4" s="45"/>
+      <c r="L4" s="45"/>
+      <c r="M4" s="45"/>
+      <c r="N4" s="162"/>
+    </row>
+    <row r="5" ht="45">
+      <c r="A5" s="40" t="s">
+        <v>381</v>
+      </c>
+      <c r="B5" s="37" t="s">
+        <v>375</v>
+      </c>
+      <c r="C5" s="37" t="s">
+        <v>376</v>
+      </c>
+      <c r="D5" s="37" t="s">
+        <v>377</v>
+      </c>
+      <c r="E5" s="37" t="s">
+        <v>378</v>
+      </c>
+      <c r="F5" s="37" t="s">
+        <v>375</v>
+      </c>
+      <c r="G5" s="37" t="s">
+        <v>377</v>
+      </c>
+      <c r="H5" s="37" t="s">
+        <v>375</v>
+      </c>
+      <c r="I5" s="37" t="s">
+        <v>377</v>
+      </c>
+      <c r="J5" s="160"/>
+      <c r="K5" s="163"/>
+      <c r="L5" s="163"/>
+      <c r="M5" s="45"/>
+      <c r="N5" s="162"/>
+    </row>
+    <row r="6" ht="45">
+      <c r="A6" s="40" t="s">
+        <v>382</v>
+      </c>
+      <c r="B6" s="37" t="s">
+        <v>375</v>
+      </c>
+      <c r="C6" s="37" t="s">
+        <v>376</v>
+      </c>
+      <c r="D6" s="37" t="s">
+        <v>377</v>
+      </c>
+      <c r="E6" s="37" t="s">
+        <v>378</v>
+      </c>
+      <c r="F6" s="37" t="s">
+        <v>377</v>
+      </c>
+      <c r="G6" s="37" t="s">
+        <v>377</v>
+      </c>
+      <c r="H6" s="37" t="s">
+        <v>375</v>
+      </c>
+      <c r="I6" s="37" t="s">
+        <v>375</v>
+      </c>
+      <c r="J6" s="160"/>
+      <c r="K6" s="45"/>
+      <c r="L6" s="45"/>
+      <c r="M6" s="34"/>
+      <c r="N6" s="164"/>
+    </row>
+    <row r="7" ht="30">
+      <c r="A7" s="40" t="s">
+        <v>383</v>
+      </c>
+      <c r="B7" s="37" t="s">
+        <v>375</v>
+      </c>
+      <c r="C7" s="37" t="s">
+        <v>377</v>
+      </c>
+      <c r="D7" s="37" t="s">
+        <v>375</v>
+      </c>
+      <c r="E7" s="37" t="s">
+        <v>377</v>
+      </c>
+      <c r="F7" s="37" t="s">
+        <v>375</v>
+      </c>
+      <c r="G7" s="37" t="s">
+        <v>384</v>
+      </c>
+      <c r="H7" s="37" t="s">
+        <v>375</v>
+      </c>
+      <c r="I7" s="37" t="s">
+        <v>377</v>
+      </c>
+      <c r="J7" s="160"/>
+      <c r="K7" s="34"/>
+      <c r="L7" s="34"/>
+      <c r="M7" s="34"/>
+      <c r="N7" s="164"/>
+    </row>
+    <row r="8" ht="30">
+      <c r="A8" s="40" t="s">
+        <v>385</v>
+      </c>
+      <c r="B8" s="37" t="s">
+        <v>375</v>
+      </c>
+      <c r="C8" s="37" t="s">
+        <v>376</v>
+      </c>
+      <c r="D8" s="37" t="s">
+        <v>375</v>
+      </c>
+      <c r="E8" s="37" t="s">
+        <v>377</v>
+      </c>
+      <c r="F8" s="37" t="s">
+        <v>378</v>
+      </c>
+      <c r="G8" s="37" t="s">
+        <v>377</v>
+      </c>
+      <c r="H8" s="37" t="s">
+        <v>377</v>
+      </c>
+      <c r="I8" s="37" t="s">
+        <v>375</v>
+      </c>
+      <c r="J8" s="160"/>
+      <c r="K8" s="34"/>
+      <c r="L8" s="34"/>
+      <c r="M8" s="34"/>
+      <c r="N8" s="164"/>
+    </row>
+    <row r="9" ht="45">
+      <c r="A9" s="40" t="s">
+        <v>386</v>
+      </c>
+      <c r="B9" s="37" t="s">
+        <v>375</v>
+      </c>
+      <c r="C9" s="37" t="s">
+        <v>376</v>
+      </c>
+      <c r="D9" s="37" t="s">
+        <v>375</v>
+      </c>
+      <c r="E9" s="37" t="s">
+        <v>377</v>
+      </c>
+      <c r="F9" s="37" t="s">
+        <v>378</v>
+      </c>
+      <c r="G9" s="37" t="s">
+        <v>375</v>
+      </c>
+      <c r="H9" s="37" t="s">
+        <v>375</v>
+      </c>
+      <c r="I9" s="37" t="s">
+        <v>377</v>
+      </c>
+      <c r="J9" s="160"/>
+      <c r="K9" s="34"/>
+      <c r="L9" s="34"/>
+      <c r="M9" s="34"/>
+      <c r="N9" s="164"/>
+    </row>
+    <row r="10" ht="45">
+      <c r="A10" s="165" t="s">
+        <v>387</v>
+      </c>
+      <c r="B10" s="166" t="s">
+        <v>375</v>
+      </c>
+      <c r="C10" s="166" t="s">
+        <v>376</v>
+      </c>
+      <c r="D10" s="166" t="s">
+        <v>377</v>
+      </c>
+      <c r="E10" s="166" t="s">
+        <v>378</v>
+      </c>
+      <c r="F10" s="166" t="s">
+        <v>375</v>
+      </c>
+      <c r="G10" s="166" t="s">
+        <v>375</v>
+      </c>
+      <c r="H10" s="166" t="s">
+        <v>375</v>
+      </c>
+      <c r="I10" s="166" t="s">
+        <v>377</v>
+      </c>
+      <c r="J10" s="167"/>
+      <c r="K10" s="168"/>
+      <c r="L10" s="168"/>
+      <c r="M10" s="168"/>
+      <c r="N10" s="164"/>
+    </row>
+    <row r="11" ht="30">
+      <c r="A11" s="165" t="s">
+        <v>388</v>
+      </c>
+      <c r="B11" s="166" t="s">
+        <v>375</v>
+      </c>
+      <c r="C11" s="166" t="s">
+        <v>376</v>
+      </c>
+      <c r="D11" s="166" t="s">
+        <v>377</v>
+      </c>
+      <c r="E11" s="166" t="s">
+        <v>377</v>
+      </c>
+      <c r="F11" s="166" t="s">
+        <v>377</v>
+      </c>
+      <c r="G11" s="166" t="s">
+        <v>377</v>
+      </c>
+      <c r="H11" s="166" t="s">
+        <v>375</v>
+      </c>
+      <c r="I11" s="166" t="s">
+        <v>378</v>
+      </c>
+      <c r="J11" s="167"/>
+      <c r="K11" s="168"/>
+      <c r="L11" s="168"/>
+      <c r="M11" s="168"/>
+      <c r="N11" s="164"/>
+    </row>
+    <row r="12" ht="15">
+      <c r="A12" s="168"/>
+      <c r="B12" s="168"/>
+      <c r="C12" s="168"/>
+      <c r="D12" s="168"/>
+      <c r="E12" s="168"/>
+      <c r="F12" s="168"/>
+      <c r="G12" s="168"/>
+      <c r="H12" s="168"/>
+      <c r="I12" s="168"/>
+      <c r="J12" s="168"/>
+      <c r="K12" s="168"/>
+      <c r="L12" s="168"/>
+      <c r="M12" s="168"/>
+      <c r="N12" s="164"/>
+    </row>
+    <row r="13" ht="15">
+      <c r="A13" s="168"/>
+      <c r="B13" s="168"/>
+      <c r="C13" s="168"/>
+      <c r="D13" s="168"/>
+      <c r="E13" s="168"/>
+      <c r="F13" s="168"/>
+      <c r="G13" s="168"/>
+      <c r="H13" s="168"/>
+      <c r="I13" s="168"/>
+      <c r="J13" s="168"/>
+      <c r="K13" s="168"/>
+      <c r="L13" s="168"/>
+      <c r="M13" s="168"/>
+      <c r="N13" s="164"/>
+    </row>
+    <row r="14" ht="15">
+      <c r="A14" s="168"/>
+      <c r="B14" s="168"/>
+      <c r="C14" s="168"/>
+      <c r="D14" s="168"/>
+      <c r="E14" s="168"/>
+      <c r="F14" s="168"/>
+      <c r="G14" s="168"/>
+      <c r="H14" s="168"/>
+      <c r="I14" s="168"/>
+      <c r="J14" s="168"/>
+      <c r="K14" s="168"/>
+      <c r="L14" s="168"/>
+      <c r="M14" s="168"/>
+      <c r="N14" s="164"/>
+    </row>
+  </sheetData>
+  <printOptions headings="0" gridLines="0"/>
+  <pageMargins left="0.70078740157480324" right="0.70078740157480324" top="0.75196850393700787" bottom="0.75196850393700787" header="0.29999999999999999" footer="0.29999999999999999"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" cellComments="none" useFirstPageNumber="0" errors="displayed" horizontalDpi="600" verticalDpi="600" copies="1"/>
+  <headerFooter/>
+  <legacyDrawing r:id="rId3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
+  <sheetPr>
+    <outlinePr applyStyles="0" summaryBelow="1" summaryRight="1" showOutlineSymbols="1"/>
+    <pageSetUpPr autoPageBreaks="1" fitToPage="0"/>
+  </sheetPr>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15.050000000000001" customHeight="1"/>
+  <sheetData>
+    <row r="1" ht="15.050000000000001">
+      <c r="A1" s="25" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="3" ht="15.050000000000001" customHeight="1">
+      <c r="A3" s="26"/>
+    </row>
+  </sheetData>
+  <printOptions headings="0" gridLines="0"/>
+  <pageMargins left="0.69999999999999996" right="0.69999999999999996" top="0.75" bottom="0.75" header="0.29999999999999999" footer="0.29999999999999999"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" cellComments="none" useFirstPageNumber="0" errors="displayed" horizontalDpi="600" verticalDpi="600" copies="1"/>
+  <headerFooter/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
+  <sheetPr>
+    <outlinePr applyStyles="0" summaryBelow="1" summaryRight="1" showOutlineSymbols="1"/>
+    <pageSetUpPr autoPageBreaks="1" fitToPage="0"/>
+  </sheetPr>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15.050000000000001" customHeight="1"/>
+  <cols>
+    <col customWidth="1" min="1" max="1" width="44.816400000000002"/>
+    <col customWidth="1" min="2" max="2" width="20.99609375"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="15.050000000000001">
+      <c r="A1" s="27" t="s">
+        <v>65</v>
+      </c>
+      <c r="B1" s="27" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="2" ht="15.050000000000001">
+      <c r="A2" s="11" t="s">
+        <v>67</v>
+      </c>
+      <c r="B2" s="11" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="3" ht="30">
+      <c r="A3" s="11" t="s">
+        <v>69</v>
+      </c>
+      <c r="B3" s="11" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="4" ht="30">
+      <c r="A4" s="11" t="s">
+        <v>71</v>
+      </c>
+      <c r="B4" s="11" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="5" ht="45">
+      <c r="A5" s="11" t="s">
+        <v>73</v>
+      </c>
+      <c r="B5" s="11" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="6" ht="30">
+      <c r="A6" s="11" t="s">
+        <v>75</v>
+      </c>
+      <c r="B6" s="11" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="7" ht="30">
+      <c r="A7" s="11" t="s">
+        <v>77</v>
+      </c>
+      <c r="B7" s="11" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="8" ht="30">
+      <c r="A8" s="11" t="s">
+        <v>79</v>
+      </c>
+      <c r="B8" s="11" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="9" ht="30">
+      <c r="A9" s="11" t="s">
+        <v>81</v>
+      </c>
+      <c r="B9" s="11" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="10" ht="30">
+      <c r="A10" s="11" t="s">
+        <v>83</v>
+      </c>
+      <c r="B10" s="11" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="11" ht="30">
+      <c r="A11" s="11" t="s">
+        <v>85</v>
+      </c>
+      <c r="B11" s="11" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="12" ht="30">
+      <c r="A12" s="11" t="s">
+        <v>87</v>
+      </c>
+      <c r="B12" s="11" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="13" ht="30">
+      <c r="A13" s="11" t="s">
+        <v>89</v>
+      </c>
+      <c r="B13" s="11" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="14" ht="15.050000000000001">
+      <c r="A14" s="27"/>
+      <c r="B14" s="27"/>
+    </row>
+    <row r="15" ht="15.050000000000001">
+      <c r="A15" s="27"/>
+      <c r="B15" s="27"/>
+    </row>
+    <row r="16" ht="15.050000000000001">
+      <c r="A16" s="27"/>
+      <c r="B16" s="27"/>
+    </row>
+    <row r="17" ht="15.050000000000001">
+      <c r="A17" s="27"/>
+      <c r="B17" s="27"/>
+    </row>
+    <row r="18" ht="15.050000000000001">
+      <c r="A18" s="27"/>
+      <c r="B18" s="27"/>
+    </row>
+    <row r="19" ht="15.050000000000001">
+      <c r="A19" s="27"/>
+      <c r="B19" s="27"/>
+    </row>
+  </sheetData>
+  <printOptions headings="0" gridLines="0"/>
+  <pageMargins left="0.69999999999999996" right="0.69999999999999996" top="0.75" bottom="0.75" header="0.29999999999999999" footer="0.29999999999999999"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" cellComments="none" useFirstPageNumber="0" errors="displayed" horizontalDpi="600" verticalDpi="600" copies="1"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
+  <sheetPr>
+    <outlinePr applyStyles="0" summaryBelow="1" summaryRight="1" showOutlineSymbols="1"/>
+    <pageSetUpPr autoPageBreaks="1" fitToPage="0"/>
+  </sheetPr>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15.050000000000001" customHeight="1"/>
+  <cols>
+    <col customWidth="1" min="1" max="1" width="4.0898399999999997"/>
+    <col bestFit="1" customWidth="1" min="2" max="2" width="20.265625"/>
+    <col bestFit="1" min="3" max="3" width="10.1640625"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="15.050000000000001">
+      <c r="A1" s="27" t="s">
+        <v>91</v>
+      </c>
+      <c r="B1" s="27" t="s">
+        <v>92</v>
+      </c>
+      <c r="C1" s="27" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="2" ht="60">
+      <c r="A2" s="11">
+        <v>1</v>
+      </c>
+      <c r="B2" s="11" t="s">
+        <v>94</v>
+      </c>
+      <c r="C2" s="11" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="3" ht="75">
+      <c r="A3" s="11">
+        <v>2</v>
+      </c>
+      <c r="B3" s="11" t="s">
+        <v>96</v>
+      </c>
+      <c r="C3" s="11" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="4" ht="105">
+      <c r="A4" s="11">
+        <v>3</v>
+      </c>
+      <c r="B4" s="11" t="s">
+        <v>98</v>
+      </c>
+      <c r="C4" s="11" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="5" ht="75">
+      <c r="A5" s="11">
+        <v>4</v>
+      </c>
+      <c r="B5" s="11" t="s">
+        <v>100</v>
+      </c>
+      <c r="C5" s="11" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="6" ht="75">
+      <c r="A6" s="11">
+        <v>5</v>
+      </c>
+      <c r="B6" s="11" t="s">
+        <v>102</v>
+      </c>
+      <c r="C6" s="11" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="7" ht="75">
+      <c r="A7" s="11">
+        <v>6</v>
+      </c>
+      <c r="B7" s="11" t="s">
+        <v>104</v>
+      </c>
+      <c r="C7" s="11" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="8" ht="62.25" customHeight="1">
+      <c r="A8" s="11">
+        <v>7</v>
+      </c>
+      <c r="B8" s="11" t="s">
+        <v>106</v>
+      </c>
+      <c r="C8" s="28">
+        <v>46203</v>
+      </c>
+    </row>
+  </sheetData>
+  <printOptions headings="0" gridLines="0"/>
+  <pageMargins left="0.69999999999999996" right="0.69999999999999996" top="0.75" bottom="0.75" header="0.29999999999999999" footer="0.29999999999999999"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" cellComments="none" useFirstPageNumber="0" errors="displayed" horizontalDpi="600" verticalDpi="600" copies="1"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
+  <sheetPr>
+    <outlinePr applyStyles="0" summaryBelow="1" summaryRight="1" showOutlineSymbols="1"/>
+    <pageSetUpPr autoPageBreaks="1" fitToPage="0"/>
+  </sheetPr>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15.050000000000001" customHeight="1"/>
+  <cols>
+    <col customWidth="1" min="1" max="1" width="4.3632799999999996"/>
+    <col customWidth="1" min="2" max="2" width="32.363300000000002"/>
+    <col customWidth="1" min="3" max="3" width="18.906199999999998"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="15.050000000000001">
+      <c r="A1" s="27" t="s">
+        <v>91</v>
+      </c>
+      <c r="B1" s="27" t="s">
+        <v>92</v>
+      </c>
+      <c r="C1" s="27" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="2" ht="45">
+      <c r="A2" s="11">
+        <v>1</v>
+      </c>
+      <c r="B2" s="11" t="s">
+        <v>107</v>
+      </c>
+      <c r="C2" s="11" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="3" ht="45">
+      <c r="A3" s="11">
+        <v>2</v>
+      </c>
+      <c r="B3" s="11" t="s">
+        <v>108</v>
+      </c>
+      <c r="C3" s="11" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="4" ht="60">
+      <c r="A4" s="11">
+        <v>3</v>
+      </c>
+      <c r="B4" s="11" t="s">
+        <v>109</v>
+      </c>
+      <c r="C4" s="11" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="5" ht="45">
+      <c r="A5" s="11">
+        <v>4</v>
+      </c>
+      <c r="B5" s="11" t="s">
+        <v>110</v>
+      </c>
+      <c r="C5" s="11" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="6" ht="60">
+      <c r="A6" s="11">
+        <v>5</v>
+      </c>
+      <c r="B6" s="11" t="s">
+        <v>111</v>
+      </c>
+      <c r="C6" s="11" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="7" ht="45">
+      <c r="A7" s="11">
+        <v>6</v>
+      </c>
+      <c r="B7" s="11" t="s">
+        <v>112</v>
+      </c>
+      <c r="C7" s="28">
+        <v>46203</v>
+      </c>
+    </row>
+    <row r="8" ht="78.75" customHeight="1">
+      <c r="A8" s="11">
+        <v>7</v>
+      </c>
+      <c r="B8" s="11" t="s">
+        <v>113</v>
+      </c>
+      <c r="C8" s="28">
+        <v>46203</v>
+      </c>
+    </row>
+  </sheetData>
+  <printOptions headings="0" gridLines="0"/>
+  <pageMargins left="0.69999999999999996" right="0.69999999999999996" top="0.75" bottom="0.75" header="0.29999999999999999" footer="0.29999999999999999"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" cellComments="none" useFirstPageNumber="0" errors="displayed" horizontalDpi="600" verticalDpi="600" copies="1"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
+  <sheetPr>
+    <outlinePr applyStyles="0" summaryBelow="1" summaryRight="1" showOutlineSymbols="1"/>
+    <pageSetUpPr autoPageBreaks="1" fitToPage="0"/>
+  </sheetPr>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15.050000000000001" customHeight="1"/>
+  <cols>
+    <col customWidth="1" min="1" max="1" width="11.9062"/>
+    <col customWidth="1" min="2" max="2" width="40.906199999999998"/>
+    <col customWidth="1" min="3" max="3" width="29.0898"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="15.65">
+      <c r="A1" s="29" t="s">
+        <v>114</v>
+      </c>
+      <c r="B1" s="29" t="s">
+        <v>115</v>
+      </c>
+      <c r="C1" s="29" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="2" ht="47">
+      <c r="A2" s="30">
+        <v>1</v>
+      </c>
+      <c r="B2" s="30" t="s">
+        <v>117</v>
+      </c>
+      <c r="C2" s="30" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="3" ht="15.65">
+      <c r="A3" s="31">
+        <v>2</v>
+      </c>
+      <c r="B3" s="31" t="s">
+        <v>119</v>
+      </c>
+      <c r="C3" s="31" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="4" ht="15.65">
+      <c r="A4" s="31">
+        <v>3</v>
+      </c>
+      <c r="B4" s="31" t="s">
+        <v>121</v>
+      </c>
+      <c r="C4" s="31" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="5" ht="15.65">
+      <c r="A5" s="31">
+        <v>4</v>
+      </c>
+      <c r="B5" s="31" t="s">
+        <v>123</v>
+      </c>
+      <c r="C5" s="31" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="6" ht="15.65">
+      <c r="A6" s="32">
+        <v>5</v>
+      </c>
+      <c r="B6" s="32" t="s">
+        <v>125</v>
+      </c>
+      <c r="C6" s="32" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="7" ht="15.65">
+      <c r="A7" s="33"/>
+      <c r="B7" s="33"/>
+      <c r="C7" s="33"/>
+    </row>
+    <row r="8" ht="15.65">
+      <c r="A8" s="33"/>
+      <c r="B8" s="33"/>
+      <c r="C8" s="33"/>
+    </row>
+    <row r="9" ht="15.65">
+      <c r="A9" s="33"/>
+      <c r="B9" s="33"/>
+      <c r="C9" s="33"/>
+    </row>
+    <row r="10" ht="15.65">
+      <c r="A10" s="33"/>
+      <c r="B10" s="33"/>
+      <c r="C10" s="33"/>
+    </row>
+    <row r="11" ht="15.050000000000001">
+      <c r="A11" s="3"/>
+      <c r="B11" s="3"/>
+      <c r="C11" s="3"/>
+    </row>
+    <row r="12" ht="15.050000000000001">
+      <c r="A12" s="3"/>
+      <c r="B12" s="3"/>
+      <c r="C12" s="3"/>
+    </row>
+    <row r="13" ht="15.050000000000001">
+      <c r="A13" s="3"/>
+      <c r="B13" s="3"/>
+      <c r="C13" s="3"/>
+    </row>
+    <row r="14" ht="15.050000000000001">
+      <c r="A14" s="3"/>
+      <c r="B14" s="3"/>
+      <c r="C14" s="3"/>
+    </row>
+    <row r="15" ht="15.050000000000001">
+      <c r="A15" s="3"/>
+      <c r="B15" s="3"/>
+      <c r="C15" s="3"/>
+    </row>
+    <row r="16" ht="15.050000000000001">
+      <c r="A16" s="3"/>
+      <c r="B16" s="3"/>
+      <c r="C16" s="3"/>
+    </row>
+    <row r="17" ht="15.050000000000001">
+      <c r="A17" s="3"/>
+      <c r="B17" s="3"/>
+      <c r="C17" s="3"/>
+    </row>
+    <row r="18" ht="15.050000000000001">
+      <c r="A18" s="3"/>
+      <c r="B18" s="3"/>
+      <c r="C18" s="3"/>
+    </row>
+    <row r="19" ht="15.050000000000001">
+      <c r="A19" s="3"/>
+      <c r="B19" s="3"/>
+      <c r="C19" s="3"/>
+    </row>
+    <row r="20" ht="15.050000000000001">
+      <c r="A20" s="3"/>
+      <c r="B20" s="3"/>
+      <c r="C20" s="3"/>
+    </row>
+  </sheetData>
+  <printOptions headings="0" gridLines="0"/>
+  <pageMargins left="0.69999999999999996" right="0.69999999999999996" top="0.75" bottom="0.75" header="0.29999999999999999" footer="0.29999999999999999"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" cellComments="none" useFirstPageNumber="0" errors="displayed" horizontalDpi="600" verticalDpi="600" copies="1"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
+  <sheetPr>
+    <outlinePr applyStyles="0" summaryBelow="1" summaryRight="1" showOutlineSymbols="1"/>
+    <pageSetUpPr autoPageBreaks="1" fitToPage="0"/>
+  </sheetPr>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15.050000000000001" customHeight="1"/>
+  <cols>
+    <col customWidth="1" min="1" max="1" style="34" width="3.8164099999999999"/>
+    <col customWidth="1" min="2" max="2" style="34" width="19.726600000000001"/>
+    <col customWidth="1" min="3" max="3" style="34" width="24.4453125"/>
+    <col customWidth="1" min="4" max="4" style="34" width="18"/>
+    <col customWidth="1" min="5" max="5" style="34" width="17"/>
+    <col customWidth="1" min="6" max="6" style="34" width="8.7265599999999992"/>
+    <col bestFit="1" min="9" max="9" width="11.1953125"/>
+    <col customWidth="1" min="10" max="10" width="41.6640625"/>
+    <col bestFit="1" customWidth="1" min="11" max="11" width="12.3046875"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="30">
+      <c r="A1" s="35" t="s">
+        <v>91</v>
+      </c>
+      <c r="B1" s="35" t="s">
+        <v>127</v>
+      </c>
+      <c r="C1" s="35" t="s">
+        <v>128</v>
+      </c>
+      <c r="D1" s="35" t="s">
+        <v>129</v>
+      </c>
+      <c r="E1" s="35" t="s">
+        <v>130</v>
+      </c>
+      <c r="H1" s="36"/>
+      <c r="I1" s="37" t="s">
+        <v>131</v>
+      </c>
+      <c r="J1" s="37" t="s">
+        <v>132</v>
+      </c>
+      <c r="K1" s="37" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="2" ht="90">
+      <c r="A2" s="30">
+        <v>1</v>
+      </c>
+      <c r="B2" s="30" t="s">
+        <v>134</v>
+      </c>
+      <c r="C2" s="30">
+        <v>1</v>
+      </c>
+      <c r="D2" s="30">
+        <v>100</v>
+      </c>
+      <c r="E2" s="38">
+        <v>2.5</v>
+      </c>
+      <c r="H2" s="39">
+        <v>1</v>
+      </c>
+      <c r="I2" s="40" t="s">
+        <v>135</v>
+      </c>
+      <c r="J2" s="40" t="s">
+        <v>136</v>
+      </c>
+      <c r="K2" s="40" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="3" ht="135">
+      <c r="A3" s="31">
+        <v>2</v>
+      </c>
+      <c r="B3" s="31" t="s">
+        <v>138</v>
+      </c>
+      <c r="C3" s="31">
+        <v>1</v>
+      </c>
+      <c r="D3" s="31">
+        <v>90</v>
+      </c>
+      <c r="E3" s="41">
+        <v>1</v>
+      </c>
+      <c r="H3" s="39">
+        <v>2</v>
+      </c>
+      <c r="I3" s="40" t="s">
+        <v>134</v>
+      </c>
+      <c r="J3" s="40" t="s">
+        <v>139</v>
+      </c>
+      <c r="K3" s="40" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="4" ht="90">
+      <c r="A4" s="31">
+        <v>3</v>
+      </c>
+      <c r="B4" s="31" t="s">
+        <v>140</v>
+      </c>
+      <c r="C4" s="31">
+        <v>1</v>
+      </c>
+      <c r="D4" s="31">
+        <v>140</v>
+      </c>
+      <c r="E4" s="41">
+        <v>1.5</v>
+      </c>
+      <c r="H4" s="39">
+        <v>3</v>
+      </c>
+      <c r="I4" s="40" t="s">
+        <v>138</v>
+      </c>
+      <c r="J4" s="40" t="s">
+        <v>141</v>
+      </c>
+      <c r="K4" s="40" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="5" ht="105">
+      <c r="A5" s="31">
+        <v>4</v>
+      </c>
+      <c r="B5" s="31" t="s">
+        <v>142</v>
+      </c>
+      <c r="C5" s="31">
+        <v>1</v>
+      </c>
+      <c r="D5" s="31">
+        <v>130</v>
+      </c>
+      <c r="E5" s="41">
+        <v>1.5</v>
+      </c>
+      <c r="H5" s="39">
+        <v>4</v>
+      </c>
+      <c r="I5" s="40" t="s">
+        <v>140</v>
+      </c>
+      <c r="J5" s="40" t="s">
+        <v>143</v>
+      </c>
+      <c r="K5" s="40" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="6" ht="105">
+      <c r="A6" s="31">
+        <v>5</v>
+      </c>
+      <c r="B6" s="31" t="s">
+        <v>144</v>
+      </c>
+      <c r="C6" s="31">
+        <v>1</v>
+      </c>
+      <c r="D6" s="31">
+        <v>160</v>
+      </c>
+      <c r="E6" s="41">
+        <v>2</v>
+      </c>
+      <c r="H6" s="39">
+        <v>5</v>
+      </c>
+      <c r="I6" s="40" t="s">
+        <v>142</v>
+      </c>
+      <c r="J6" s="40" t="s">
+        <v>145</v>
+      </c>
+      <c r="K6" s="40" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="7" ht="120">
+      <c r="A7" s="31">
+        <v>6</v>
+      </c>
+      <c r="B7" s="31" t="s">
+        <v>146</v>
+      </c>
+      <c r="C7" s="31">
+        <v>1</v>
+      </c>
+      <c r="D7" s="31">
+        <v>100</v>
+      </c>
+      <c r="E7" s="41">
+        <v>1</v>
+      </c>
+      <c r="H7" s="39">
+        <v>6</v>
+      </c>
+      <c r="I7" s="40" t="s">
+        <v>144</v>
+      </c>
+      <c r="J7" s="40" t="s">
+        <v>147</v>
+      </c>
+      <c r="K7" s="40" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="8" ht="105">
+      <c r="A8" s="32">
+        <v>7</v>
+      </c>
+      <c r="B8" s="32" t="s">
+        <v>148</v>
+      </c>
+      <c r="C8" s="32">
+        <v>1</v>
+      </c>
+      <c r="D8" s="32">
+        <v>90</v>
+      </c>
+      <c r="E8" s="42">
+        <v>1</v>
+      </c>
+      <c r="H8" s="39">
+        <v>7</v>
+      </c>
+      <c r="I8" s="40" t="s">
+        <v>146</v>
+      </c>
+      <c r="J8" s="40" t="s">
+        <v>149</v>
+      </c>
+      <c r="K8" s="40" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="9" ht="105">
+      <c r="H9" s="39">
+        <v>8</v>
+      </c>
+      <c r="I9" s="40" t="s">
+        <v>148</v>
+      </c>
+      <c r="J9" s="40" t="s">
+        <v>150</v>
+      </c>
+      <c r="K9" s="40" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="10" ht="15.65">
+      <c r="A10" s="43"/>
+      <c r="B10" s="43"/>
+      <c r="C10" s="43"/>
+      <c r="D10" s="43"/>
+      <c r="E10" s="43"/>
+      <c r="H10" s="44"/>
+      <c r="I10" s="44"/>
+      <c r="J10" s="44"/>
+      <c r="K10" s="44"/>
+    </row>
+    <row r="11" ht="15.65">
+      <c r="A11" s="45"/>
+      <c r="B11" s="45"/>
+      <c r="C11" s="45"/>
+      <c r="D11" s="45"/>
+      <c r="E11" s="45"/>
+      <c r="H11" s="46"/>
+      <c r="I11" s="46"/>
+      <c r="J11" s="46"/>
+      <c r="K11" s="46"/>
+    </row>
+    <row r="12" ht="15.65">
+      <c r="A12" s="45"/>
+      <c r="B12" s="45"/>
+      <c r="C12" s="45"/>
+      <c r="D12" s="45"/>
+      <c r="E12" s="45"/>
+      <c r="H12" s="46"/>
+      <c r="I12" s="46"/>
+      <c r="J12" s="46"/>
+      <c r="K12" s="46"/>
+    </row>
+    <row r="13" ht="15.65">
+      <c r="A13" s="46"/>
+      <c r="B13" s="47"/>
+      <c r="C13" s="47"/>
+      <c r="D13" s="47"/>
+      <c r="E13" s="45"/>
+      <c r="H13" s="46"/>
+      <c r="I13" s="46"/>
+      <c r="J13" s="46"/>
+      <c r="K13" s="46"/>
+    </row>
+    <row r="14" ht="15.65">
+      <c r="A14" s="48"/>
+      <c r="B14" s="49"/>
+      <c r="C14" s="50"/>
+      <c r="E14" s="45"/>
+      <c r="H14" s="46"/>
+      <c r="I14" s="46"/>
+      <c r="J14" s="46"/>
+      <c r="K14" s="46"/>
+    </row>
+    <row r="15" ht="15.65">
+      <c r="A15" s="48"/>
+      <c r="B15" s="49"/>
+      <c r="C15" s="50"/>
+      <c r="E15" s="45"/>
+      <c r="H15" s="46"/>
+      <c r="I15" s="46"/>
+      <c r="J15" s="46"/>
+      <c r="K15" s="46"/>
+    </row>
+    <row r="16" ht="15.65">
+      <c r="A16" s="48"/>
+      <c r="B16" s="49"/>
+      <c r="C16" s="50"/>
+      <c r="E16" s="45"/>
+      <c r="H16" s="46"/>
+      <c r="I16" s="46"/>
+      <c r="J16" s="46"/>
+      <c r="K16" s="46"/>
+    </row>
+    <row r="17" ht="15.65">
+      <c r="A17" s="48"/>
+      <c r="B17" s="49"/>
+      <c r="C17" s="50"/>
+      <c r="E17" s="45"/>
+    </row>
+    <row r="18" ht="15.65">
+      <c r="A18" s="48"/>
+      <c r="B18" s="51"/>
+      <c r="C18" s="50"/>
+      <c r="E18" s="45"/>
+    </row>
+    <row r="19" ht="15.65">
+      <c r="A19" s="48"/>
+      <c r="B19" s="48"/>
+      <c r="C19" s="50"/>
+      <c r="E19" s="45"/>
+    </row>
+    <row r="20" ht="15.65">
+      <c r="A20" s="48"/>
+      <c r="B20" s="48"/>
+      <c r="C20" s="50"/>
+      <c r="E20" s="45"/>
+    </row>
+    <row r="21" ht="15.65">
+      <c r="A21" s="48"/>
+      <c r="B21" s="48"/>
+      <c r="C21" s="50"/>
+      <c r="E21" s="45"/>
+    </row>
+    <row r="22" ht="15.65">
+      <c r="A22" s="48"/>
+      <c r="B22" s="48"/>
+      <c r="C22" s="50"/>
+      <c r="E22" s="45"/>
+    </row>
+    <row r="23" ht="15.65">
+      <c r="A23" s="48"/>
+      <c r="B23" s="48"/>
+      <c r="C23" s="50"/>
+      <c r="E23" s="45"/>
+    </row>
+    <row r="24" ht="15.050000000000001" customHeight="1">
+      <c r="A24" s="48"/>
+      <c r="B24" s="52"/>
+      <c r="C24" s="50"/>
+    </row>
+    <row r="25" ht="15.050000000000001" customHeight="1">
+      <c r="A25" s="48"/>
+      <c r="B25" s="53"/>
+    </row>
+    <row r="26" ht="15.050000000000001" customHeight="1">
+      <c r="A26" s="48"/>
+      <c r="B26" s="53"/>
+    </row>
+    <row r="27" ht="15.050000000000001" customHeight="1">
+      <c r="A27" s="48"/>
+      <c r="B27" s="53"/>
+    </row>
+    <row r="28" ht="15.050000000000001" customHeight="1">
+      <c r="A28" s="48"/>
+      <c r="B28" s="53"/>
+    </row>
+  </sheetData>
+  <printOptions headings="0" gridLines="0"/>
+  <pageMargins left="0.69999999999999996" right="0.69999999999999996" top="0.75" bottom="0.75" header="0.29999999999999999" footer="0.29999999999999999"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" cellComments="none" useFirstPageNumber="0" errors="displayed" horizontalDpi="600" verticalDpi="600" copies="1"/>
+  <headerFooter/>
+  <legacyDrawing r:id="rId3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="36"/>
+      <c r="B1" s="37" t="s">
+        <v>131</v>
+      </c>
+      <c r="C1" s="37" t="s">
+        <v>132</v>
+      </c>
+      <c r="D1" s="37" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="54">
+        <v>1</v>
+      </c>
+      <c r="B2" s="55" t="s">
+        <v>135</v>
+      </c>
+      <c r="C2" s="56" t="s">
+        <v>151</v>
+      </c>
+      <c r="D2" s="57"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="58"/>
+      <c r="B3" s="59"/>
+      <c r="C3" s="50" t="s">
+        <v>152</v>
+      </c>
+      <c r="D3" s="34"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="58"/>
+      <c r="B4" s="59"/>
+      <c r="C4" s="50" t="s">
+        <v>153</v>
+      </c>
+      <c r="D4" s="34"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="58"/>
+      <c r="B5" s="59"/>
+      <c r="C5" s="50" t="s">
+        <v>154</v>
+      </c>
+      <c r="D5" s="34"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="58">
+        <v>2</v>
+      </c>
+      <c r="B6" s="58" t="s">
+        <v>134</v>
+      </c>
+      <c r="C6" s="50" t="s">
+        <v>155</v>
+      </c>
+      <c r="D6" s="34"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="58"/>
+      <c r="B7" s="58"/>
+      <c r="C7" s="50" t="s">
+        <v>156</v>
+      </c>
+      <c r="D7" s="34"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="58"/>
+      <c r="B8" s="58"/>
+      <c r="C8" s="50" t="s">
+        <v>157</v>
+      </c>
+      <c r="D8" s="34"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="58"/>
+      <c r="B9" s="58"/>
+      <c r="C9" s="50" t="s">
+        <v>158</v>
+      </c>
+      <c r="D9" s="34"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="58"/>
+      <c r="B10" s="58"/>
+      <c r="C10" s="50" t="s">
+        <v>159</v>
+      </c>
+      <c r="D10" s="34"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="58"/>
+      <c r="B11" s="58"/>
+      <c r="C11" s="50" t="s">
+        <v>160</v>
+      </c>
+      <c r="D11" s="34"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="58">
+        <v>3</v>
+      </c>
+      <c r="B12" s="60" t="s">
+        <v>138</v>
+      </c>
+      <c r="C12" s="50" t="s">
+        <v>161</v>
+      </c>
+      <c r="D12" s="34"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="58"/>
+      <c r="B13" s="60"/>
+      <c r="C13" s="34"/>
+      <c r="D13" s="34"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="58"/>
+      <c r="B14" s="60"/>
+      <c r="C14" s="34"/>
+      <c r="D14" s="34"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="58"/>
+      <c r="B15" s="60"/>
+      <c r="C15" s="34"/>
+      <c r="D15" s="34"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="58"/>
+      <c r="B16" s="60"/>
+      <c r="C16" s="34"/>
+      <c r="D16" s="34"/>
+    </row>
+  </sheetData>
+  <mergeCells count="6">
+    <mergeCell ref="A2:A5"/>
+    <mergeCell ref="B2:B5"/>
+    <mergeCell ref="A6:A11"/>
+    <mergeCell ref="B6:B11"/>
+    <mergeCell ref="A12:A16"/>
+    <mergeCell ref="B12:B16"/>
+  </mergeCells>
+  <printOptions headings="0" gridLines="0"/>
+  <pageMargins left="0.70078740157480324" right="0.70078740157480324" top="0.75196850393700787" bottom="0.75196850393700787" header="0.29999999999999999" footer="0.29999999999999999"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" cellComments="none" useFirstPageNumber="0" errors="displayed" horizontalDpi="600" verticalDpi="600" copies="1"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
+  <sheetPr>
+    <outlinePr applyStyles="0" summaryBelow="1" summaryRight="1" showOutlineSymbols="1"/>
+    <pageSetUpPr autoPageBreaks="1" fitToPage="0"/>
+  </sheetPr>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15.050000000000001" customHeight="1"/>
+  <cols>
+    <col customWidth="1" min="1" max="1" width="5.5429700000000004"/>
+    <col customWidth="1" min="2" max="2" width="27.453099999999999"/>
+    <col customWidth="1" min="3" max="4" width="18.542999999999999"/>
+    <col customWidth="1" min="5" max="5" width="22.1797"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="52" customHeight="1">
+      <c r="A1" s="61" t="s">
+        <v>162</v>
+      </c>
+      <c r="B1" s="61"/>
+      <c r="C1" s="61"/>
+      <c r="D1" s="61"/>
+      <c r="E1" s="61"/>
+    </row>
+    <row r="2" ht="52.600000000000001" customHeight="1">
+      <c r="A2" s="35" t="s">
+        <v>91</v>
+      </c>
+      <c r="B2" s="35" t="s">
+        <v>163</v>
+      </c>
+      <c r="C2" s="35" t="s">
+        <v>164</v>
+      </c>
+      <c r="D2" s="35" t="s">
+        <v>165</v>
+      </c>
+      <c r="E2" s="62" t="s">
+        <v>166</v>
+      </c>
+      <c r="F2" s="34"/>
+    </row>
+    <row r="3" ht="30">
+      <c r="A3" s="63">
+        <v>1</v>
+      </c>
+      <c r="B3" s="63" t="s">
+        <v>167</v>
+      </c>
+      <c r="C3" s="63">
+        <v>1</v>
+      </c>
+      <c r="D3" s="63">
+        <v>120000</v>
+      </c>
+      <c r="E3" s="31">
+        <v>144000</v>
+      </c>
+      <c r="F3" s="34"/>
+    </row>
+    <row r="4" ht="15.65">
+      <c r="A4" s="31">
+        <v>2</v>
+      </c>
+      <c r="B4" s="31" t="s">
+        <v>168</v>
+      </c>
+      <c r="C4" s="31">
+        <v>2</v>
+      </c>
+      <c r="D4" s="31">
+        <v>80000</v>
+      </c>
+      <c r="E4" s="31">
+        <v>192000</v>
+      </c>
+      <c r="F4" s="34"/>
+    </row>
+    <row r="5" ht="15.65">
+      <c r="A5" s="31">
+        <v>3</v>
+      </c>
+      <c r="B5" s="31" t="s">
+        <v>169</v>
+      </c>
+      <c r="C5" s="31" t="s">
+        <v>170</v>
+      </c>
+      <c r="D5" s="31">
+        <v>25000</v>
+      </c>
+      <c r="E5" s="31">
+        <v>60000</v>
+      </c>
+      <c r="F5" s="34"/>
+    </row>
+    <row r="6" ht="15.65">
+      <c r="A6" s="31">
+        <v>4</v>
+      </c>
+      <c r="B6" s="31" t="s">
+        <v>171</v>
+      </c>
+      <c r="C6" s="31" t="s">
+        <v>172</v>
+      </c>
+      <c r="D6" s="31">
+        <v>5000</v>
+      </c>
+      <c r="E6" s="31">
+        <v>18000</v>
+      </c>
+      <c r="F6" s="34"/>
+    </row>
+    <row r="7" ht="15.65">
+      <c r="A7" s="31">
+        <v>5</v>
+      </c>
+      <c r="B7" s="31" t="s">
+        <v>173</v>
+      </c>
+      <c r="C7" s="31" t="s">
+        <v>172</v>
+      </c>
+      <c r="D7" s="31">
+        <v>3000</v>
+      </c>
+      <c r="E7" s="31">
+        <v>10800</v>
+      </c>
+      <c r="F7" s="34"/>
+    </row>
+    <row r="8" ht="15.65">
+      <c r="A8" s="31">
+        <v>6</v>
+      </c>
+      <c r="B8" s="31" t="s">
+        <v>174</v>
+      </c>
+      <c r="C8" s="31">
+        <v>1</v>
+      </c>
+      <c r="D8" s="31">
+        <v>3000</v>
+      </c>
+      <c r="E8" s="31">
+        <v>3600</v>
+      </c>
+      <c r="F8" s="34"/>
+    </row>
+    <row r="9" ht="15.65">
+      <c r="A9" s="31">
+        <v>7</v>
+      </c>
+      <c r="B9" s="31" t="s">
+        <v>175</v>
+      </c>
+      <c r="C9" s="31">
+        <v>1</v>
+      </c>
+      <c r="D9" s="31">
+        <v>5000</v>
+      </c>
+      <c r="E9" s="31">
+        <v>6000</v>
+      </c>
+      <c r="F9" s="34"/>
+    </row>
+    <row r="10" ht="15.65">
+      <c r="A10" s="32">
+        <v>8</v>
+      </c>
+      <c r="B10" s="32" t="s">
+        <v>176</v>
+      </c>
+      <c r="C10" s="32">
+        <v>1</v>
+      </c>
+      <c r="D10" s="32">
+        <v>10000</v>
+      </c>
+      <c r="E10" s="32">
+        <v>12000</v>
+      </c>
+      <c r="F10" s="34"/>
+    </row>
+    <row r="11" ht="15.65">
+      <c r="A11" s="64" t="s">
+        <v>177</v>
+      </c>
+      <c r="B11" s="65"/>
+      <c r="C11" s="65"/>
+      <c r="D11" s="66"/>
+      <c r="E11" s="33">
+        <f>SUM(E3:E10)</f>
+        <v>446400</v>
+      </c>
+      <c r="F11" s="34"/>
+    </row>
+    <row r="12" ht="15.65">
+      <c r="A12" s="67"/>
+      <c r="B12" s="68"/>
+      <c r="C12" s="68"/>
+      <c r="D12" s="69"/>
+      <c r="E12" s="70"/>
+      <c r="F12" s="34"/>
+    </row>
+    <row r="13" ht="15.050000000000001">
+      <c r="A13" s="34"/>
+      <c r="B13" s="34"/>
+      <c r="C13" s="34"/>
+      <c r="D13" s="34"/>
+      <c r="E13" s="34"/>
+      <c r="F13" s="34"/>
+    </row>
+    <row r="14" ht="15.050000000000001">
+      <c r="A14" s="34"/>
+      <c r="B14" s="34"/>
+      <c r="C14" s="34"/>
+      <c r="D14" s="34"/>
+      <c r="E14" s="34"/>
+      <c r="F14" s="34"/>
+    </row>
+    <row r="15" ht="15.050000000000001">
+      <c r="A15" s="34"/>
+      <c r="B15" s="34"/>
+      <c r="C15" s="34"/>
+      <c r="D15" s="34"/>
+      <c r="E15" s="34"/>
+      <c r="F15" s="34"/>
+    </row>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="A11:D11"/>
+    <mergeCell ref="A12:D12"/>
+  </mergeCells>
+  <printOptions headings="0" gridLines="0"/>
+  <pageMargins left="0.69999999999999996" right="0.69999999999999996" top="0.75" bottom="0.75" header="0.29999999999999999" footer="0.29999999999999999"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" cellComments="none" useFirstPageNumber="0" errors="displayed" horizontalDpi="600" verticalDpi="600" copies="1"/>
+  <headerFooter/>
+  <legacyDrawing r:id="rId3"/>
+</worksheet>
 </file>